--- a/Data_Set_(A+B).xlsx
+++ b/Data_Set_(A+B).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Александра\PycharmProjects\ML_robot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Александра\PycharmProjects\ML_robots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C24C9A3A-5205-4572-AF57-E5AAF1335280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831C603A-DEF2-4971-AA4F-B31013F5433C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="828" yWindow="3144" windowWidth="17280" windowHeight="10044" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист 1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>I1</t>
   </si>
@@ -79,39 +79,6 @@
   </si>
   <si>
     <t>Type</t>
-  </si>
-  <si>
-    <t>Tx</t>
-  </si>
-  <si>
-    <t>Ty</t>
-  </si>
-  <si>
-    <t>Tphi</t>
-  </si>
-  <si>
-    <t>Tz</t>
-  </si>
-  <si>
-    <t>Vx</t>
-  </si>
-  <si>
-    <t>Vy</t>
-  </si>
-  <si>
-    <t>Omega</t>
-  </si>
-  <si>
-    <t>Ix</t>
-  </si>
-  <si>
-    <t>Iy</t>
-  </si>
-  <si>
-    <t>Iphi</t>
-  </si>
-  <si>
-    <t>Isum</t>
   </si>
 </sst>
 </file>
@@ -375,10 +342,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA177"/>
+  <dimension ref="A1:P177"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -425,43 +392,10 @@
         <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>21</v>
-      </c>
-      <c r="R1" t="s">
-        <v>22</v>
-      </c>
-      <c r="S1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T1" t="s">
-        <v>24</v>
-      </c>
-      <c r="U1" t="s">
-        <v>25</v>
-      </c>
-      <c r="V1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W1" t="s">
-        <v>16</v>
-      </c>
-      <c r="X1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1.1266970000000001</v>
       </c>
@@ -508,54 +442,10 @@
         <v>5239</v>
       </c>
       <c r="P2">
-        <f>(4*(L2+J2)*COS(RADIANS(30)))/15</f>
-        <v>3.6678722983810457</v>
-      </c>
-      <c r="Q2">
-        <f>(4*(L2+J2)*SIN(RADIANS(30))-4*K2)/15</f>
-        <v>0.84705882352935025</v>
-      </c>
-      <c r="R2">
-        <f>(J2+K2+L2)/6</f>
-        <v>3.441176470588156</v>
-      </c>
-      <c r="S2">
-        <f>(2*(A2+C2)*COS(RADIANS(30)))/3</f>
-        <v>1.1860495372574902</v>
-      </c>
-      <c r="T2">
-        <f>(2*(A2+C2)*SIN(RADIANS(30))-2*B2)/3</f>
-        <v>0.67068860784313689</v>
-      </c>
-      <c r="U2">
-        <f>(A2+B2+C2)/3</f>
-        <v>0.69180472549019589</v>
-      </c>
-      <c r="V2">
-        <f>A2+B2+C2</f>
-        <v>2.0754141764705878</v>
-      </c>
-      <c r="W2">
-        <f>P2/S2</f>
-        <v>3.092511891925096</v>
-      </c>
-      <c r="X2">
-        <f>Q2/T2</f>
-        <v>1.26296885562646</v>
-      </c>
-      <c r="Y2">
-        <f>R2/U2</f>
-        <v>4.9742020309991704</v>
-      </c>
-      <c r="Z2">
-        <f>F2/U2</f>
-        <v>1.5636850487192584</v>
-      </c>
-      <c r="AA2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1.03921505882353</v>
       </c>
@@ -602,54 +492,10 @@
         <v>5391</v>
       </c>
       <c r="P3">
-        <f t="shared" ref="P3:P66" si="0">(4*(L3+J3)*COS(RADIANS(30)))/15</f>
-        <v>0.73357445967616708</v>
-      </c>
-      <c r="Q3">
-        <f t="shared" ref="Q3:Q66" si="1">(4*(L3+J3)*SIN(RADIANS(30))-4*K3)/15</f>
-        <v>0.42352941176466924</v>
-      </c>
-      <c r="R3">
-        <f t="shared" ref="R3:R66" si="2">(J3+K3+L3)/6</f>
-        <v>0.52941176470583662</v>
-      </c>
-      <c r="S3">
-        <f t="shared" ref="S3:S66" si="3">(2*(A3+C3)*COS(RADIANS(30)))/3</f>
-        <v>1.1503460607636822</v>
-      </c>
-      <c r="T3">
-        <f t="shared" ref="T3:T66" si="4">(2*(A3+C3)*SIN(RADIANS(30))-2*B3)/3</f>
-        <v>0.65409730980392167</v>
-      </c>
-      <c r="U3">
-        <f t="shared" ref="U3:U66" si="5">(A3+B3+C3)/3</f>
-        <v>0.66918025686274518</v>
-      </c>
-      <c r="V3">
-        <f t="shared" ref="V3:V66" si="6">A3+B3+C3</f>
-        <v>2.0075407705882355</v>
-      </c>
-      <c r="W3">
-        <f t="shared" ref="W3:W66" si="7">P3/S3</f>
-        <v>0.63769893660449251</v>
-      </c>
-      <c r="X3">
-        <f t="shared" ref="X3:X66" si="8">Q3/T3</f>
-        <v>0.64750214595994959</v>
-      </c>
-      <c r="Y3">
-        <f t="shared" ref="Y3:Y66" si="9">R3/U3</f>
-        <v>0.79113476417823203</v>
-      </c>
-      <c r="Z3">
-        <f t="shared" ref="Z3:Z66" si="10">F3/U3</f>
-        <v>0.72520686716344218</v>
-      </c>
-      <c r="AA3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.91101076470588305</v>
       </c>
@@ -696,54 +542,10 @@
         <v>4786</v>
       </c>
       <c r="P4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <f t="shared" si="3"/>
-        <v>1.0728441907931328</v>
-      </c>
-      <c r="T4">
-        <f t="shared" si="4"/>
-        <v>0.61639029019607861</v>
-      </c>
-      <c r="U4">
-        <f t="shared" si="5"/>
-        <v>0.62091517843137278</v>
-      </c>
-      <c r="V4">
-        <f t="shared" si="6"/>
-        <v>1.8627455352941182</v>
-      </c>
-      <c r="W4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <f t="shared" si="10"/>
-        <v>1.069578696298896</v>
-      </c>
-      <c r="AA4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.69230800000000003</v>
       </c>
@@ -790,54 +592,10 @@
         <v>2875</v>
       </c>
       <c r="P5">
-        <f t="shared" si="0"/>
-        <v>70.056360899080104</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" si="1"/>
-        <v>122.18823529411773</v>
-      </c>
-      <c r="R5">
-        <f t="shared" si="2"/>
-        <v>-0.52941176470583662</v>
-      </c>
-      <c r="S5">
-        <f t="shared" si="3"/>
-        <v>0.71755169915855788</v>
-      </c>
-      <c r="T5">
-        <f t="shared" si="4"/>
-        <v>-0.35696274509803999</v>
-      </c>
-      <c r="U5">
-        <f t="shared" si="5"/>
-        <v>0.79989937254901999</v>
-      </c>
-      <c r="V5">
-        <f t="shared" si="6"/>
-        <v>2.39969811764706</v>
-      </c>
-      <c r="W5">
-        <f t="shared" si="7"/>
-        <v>97.632492517587508</v>
-      </c>
-      <c r="X5">
-        <f t="shared" si="8"/>
-        <v>-342.29968525303298</v>
-      </c>
-      <c r="Y5">
-        <f t="shared" si="9"/>
-        <v>-0.66184795597322821</v>
-      </c>
-      <c r="Z5">
-        <f t="shared" si="10"/>
-        <v>-4.2777439554406635</v>
-      </c>
-      <c r="AA5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.52941182352941196</v>
       </c>
@@ -884,54 +642,10 @@
         <v>2967</v>
       </c>
       <c r="P6">
-        <f t="shared" si="0"/>
-        <v>75.191382116813472</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="1"/>
-        <v>127.270588235294</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="2"/>
-        <v>1.8529411764705042</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="3"/>
-        <v>0.56777124710281768</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="4"/>
-        <v>-0.35495276470588538</v>
-      </c>
-      <c r="U6">
-        <f t="shared" si="5"/>
-        <v>0.66918070588235457</v>
-      </c>
-      <c r="V6">
-        <f t="shared" si="6"/>
-        <v>2.0075421176470636</v>
-      </c>
-      <c r="W6">
-        <f t="shared" si="7"/>
-        <v>132.43252894628716</v>
-      </c>
-      <c r="X6">
-        <f t="shared" si="8"/>
-        <v>-358.55640775400263</v>
-      </c>
-      <c r="Y6">
-        <f t="shared" si="9"/>
-        <v>2.7689698166465977</v>
-      </c>
-      <c r="Z6">
-        <f t="shared" si="10"/>
-        <v>-2.1659497232436555</v>
-      </c>
-      <c r="AA6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0.60181017647058799</v>
       </c>
@@ -978,54 +692,10 @@
         <v>2910</v>
       </c>
       <c r="P7">
-        <f t="shared" si="0"/>
-        <v>67.488850290213193</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="1"/>
-        <v>122.82352941176465</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="2"/>
-        <v>-3.7058823529411598</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="3"/>
-        <v>0.67401096445474407</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="4"/>
-        <v>-0.32378158823529435</v>
-      </c>
-      <c r="U7">
-        <f t="shared" si="5"/>
-        <v>0.74560141176470562</v>
-      </c>
-      <c r="V7">
-        <f t="shared" si="6"/>
-        <v>2.2368042352941169</v>
-      </c>
-      <c r="W7">
-        <f t="shared" si="7"/>
-        <v>100.13019646469665</v>
-      </c>
-      <c r="X7">
-        <f t="shared" si="8"/>
-        <v>-379.34068481530807</v>
-      </c>
-      <c r="Y7">
-        <f t="shared" si="9"/>
-        <v>-4.9703263626741219</v>
-      </c>
-      <c r="Z7">
-        <f t="shared" si="10"/>
-        <v>-3.1746973465715467</v>
-      </c>
-      <c r="AA7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>0.37707382941176498</v>
       </c>
@@ -1072,54 +742,10 @@
         <v>8079</v>
       </c>
       <c r="P8">
-        <f t="shared" si="0"/>
-        <v>78.125679955518578</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="1"/>
-        <v>130.23529411764704</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="2"/>
-        <v>3.1764705882353326</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="3"/>
-        <v>0.81247036224880731</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="4"/>
-        <v>-0.15032644901960776</v>
-      </c>
-      <c r="U8">
-        <f t="shared" si="5"/>
-        <v>0.77878319803921636</v>
-      </c>
-      <c r="V8">
-        <f t="shared" si="6"/>
-        <v>2.3363495941176491</v>
-      </c>
-      <c r="W8">
-        <f t="shared" si="7"/>
-        <v>96.158190606826977</v>
-      </c>
-      <c r="X8">
-        <f t="shared" si="8"/>
-        <v>-866.34983375852812</v>
-      </c>
-      <c r="Y8">
-        <f t="shared" si="9"/>
-        <v>4.07876106756399</v>
-      </c>
-      <c r="Z8">
-        <f t="shared" si="10"/>
-        <v>-5.159632750468389</v>
-      </c>
-      <c r="AA8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>0.276017882352941</v>
       </c>
@@ -1166,54 +792,10 @@
         <v>8250</v>
       </c>
       <c r="P9">
-        <f t="shared" si="0"/>
-        <v>81.059977794223457</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="1"/>
-        <v>135.74117647058827</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="2"/>
-        <v>2.9117647058823288</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="3"/>
-        <v>0.63917809820509286</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="4"/>
-        <v>-0.116641647058824</v>
-      </c>
-      <c r="U9">
-        <f t="shared" si="5"/>
-        <v>0.61186529411764701</v>
-      </c>
-      <c r="V9">
-        <f t="shared" si="6"/>
-        <v>1.835595882352941</v>
-      </c>
-      <c r="W9">
-        <f t="shared" si="7"/>
-        <v>126.8190790983795</v>
-      </c>
-      <c r="X9">
-        <f t="shared" si="8"/>
-        <v>-1163.7453679141904</v>
-      </c>
-      <c r="Y9">
-        <f t="shared" si="9"/>
-        <v>4.7588329226636388</v>
-      </c>
-      <c r="Z9">
-        <f t="shared" si="10"/>
-        <v>-5.2558665930890225</v>
-      </c>
-      <c r="AA9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>0.34238282352941202</v>
       </c>
@@ -1260,54 +842,10 @@
         <v>8464</v>
       </c>
       <c r="P10">
-        <f t="shared" si="0"/>
-        <v>79.959616104709113</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" si="1"/>
-        <v>133.83529411764707</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="2"/>
-        <v>2.9117647058823386</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="3"/>
-        <v>0.72625973742162309</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="4"/>
-        <v>-0.12267476470588241</v>
-      </c>
-      <c r="U10">
-        <f t="shared" si="5"/>
-        <v>0.69029676470588264</v>
-      </c>
-      <c r="V10">
-        <f t="shared" si="6"/>
-        <v>2.0708902941176479</v>
-      </c>
-      <c r="W10">
-        <f t="shared" si="7"/>
-        <v>110.09782311295791</v>
-      </c>
-      <c r="X10">
-        <f t="shared" si="8"/>
-        <v>-1090.9765707602737</v>
-      </c>
-      <c r="Y10">
-        <f t="shared" si="9"/>
-        <v>4.2181346556404113</v>
-      </c>
-      <c r="Z10">
-        <f t="shared" si="10"/>
-        <v>-6.1584765972350386</v>
-      </c>
-      <c r="AA10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.37278076923076903</v>
       </c>
@@ -1354,54 +892,10 @@
         <v>3136</v>
       </c>
       <c r="P11">
-        <f t="shared" si="0"/>
-        <v>73.8653052089374</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="1"/>
-        <v>-0.55384615384613578</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="2"/>
-        <v>80.307692307692335</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="3"/>
-        <v>0.41109124510979927</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="4"/>
-        <v>-7.4293384615384997E-2</v>
-      </c>
-      <c r="U11">
-        <f t="shared" si="5"/>
-        <v>0.39316215384615399</v>
-      </c>
-      <c r="V11">
-        <f t="shared" si="6"/>
-        <v>1.1794864615384619</v>
-      </c>
-      <c r="W11">
-        <f t="shared" si="7"/>
-        <v>179.68104669611378</v>
-      </c>
-      <c r="X11">
-        <f t="shared" si="8"/>
-        <v>7.4548515552681245</v>
-      </c>
-      <c r="Y11">
-        <f t="shared" si="9"/>
-        <v>204.26099389799629</v>
-      </c>
-      <c r="Z11">
-        <f t="shared" si="10"/>
-        <v>43.010243571452591</v>
-      </c>
-      <c r="AA11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>0.36291892307692297</v>
       </c>
@@ -1448,54 +942,10 @@
         <v>2881</v>
       </c>
       <c r="P12">
-        <f t="shared" si="0"/>
-        <v>75.783884565013608</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="1"/>
-        <v>2.2153846153845205</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="2"/>
-        <v>80.653846153846175</v>
-      </c>
-      <c r="S12">
-        <f t="shared" si="3"/>
-        <v>0.39970372163498075</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="4"/>
-        <v>-8.6127666666666672E-2</v>
-      </c>
-      <c r="U12">
-        <f t="shared" si="5"/>
-        <v>0.38921741025641032</v>
-      </c>
-      <c r="V12">
-        <f t="shared" si="6"/>
-        <v>1.167652230769231</v>
-      </c>
-      <c r="W12">
-        <f t="shared" si="7"/>
-        <v>189.60014746678118</v>
-      </c>
-      <c r="X12">
-        <f t="shared" si="8"/>
-        <v>-25.722101864881054</v>
-      </c>
-      <c r="Y12">
-        <f t="shared" si="9"/>
-        <v>207.22055085026307</v>
-      </c>
-      <c r="Z12">
-        <f t="shared" si="10"/>
-        <v>43.869094584866872</v>
-      </c>
-      <c r="AA12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>0.42209038461538501</v>
       </c>
@@ -1542,54 +992,10 @@
         <v>2839</v>
       </c>
       <c r="P13">
-        <f t="shared" si="0"/>
-        <v>77.702463921089844</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" si="1"/>
-        <v>-1.6615384615384072</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="2"/>
-        <v>85.153846153846004</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="3"/>
-        <v>0.44980897592348396</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="4"/>
-        <v>3.7475282051281956E-2</v>
-      </c>
-      <c r="U13">
-        <f t="shared" si="5"/>
-        <v>0.37080835897435899</v>
-      </c>
-      <c r="V13">
-        <f t="shared" si="6"/>
-        <v>1.112425076923077</v>
-      </c>
-      <c r="W13">
-        <f t="shared" si="7"/>
-        <v>172.74547214528604</v>
-      </c>
-      <c r="X13">
-        <f t="shared" si="8"/>
-        <v>-44.336916777963765</v>
-      </c>
-      <c r="Y13">
-        <f t="shared" si="9"/>
-        <v>229.64381490584009</v>
-      </c>
-      <c r="Z13">
-        <f t="shared" si="10"/>
-        <v>42.339930101429125</v>
-      </c>
-      <c r="AA13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>0.43076893333333299</v>
       </c>
@@ -1636,54 +1042,10 @@
         <v>5639</v>
       </c>
       <c r="P14">
-        <f t="shared" si="0"/>
-        <v>161.28857120081386</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="1"/>
-        <v>1.4399999999999789</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="2"/>
-        <v>173.69999999999996</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="3"/>
-        <v>0.45398445005029903</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="4"/>
-        <v>-2.279288888889027E-3</v>
-      </c>
-      <c r="U14">
-        <f t="shared" si="5"/>
-        <v>0.39430171111111095</v>
-      </c>
-      <c r="V14">
-        <f t="shared" si="6"/>
-        <v>1.1829051333333329</v>
-      </c>
-      <c r="W14">
-        <f t="shared" si="7"/>
-        <v>355.27333850959866</v>
-      </c>
-      <c r="X14">
-        <f t="shared" si="8"/>
-        <v>-631.77599251223694</v>
-      </c>
-      <c r="Y14">
-        <f t="shared" si="9"/>
-        <v>440.52560540639587</v>
-      </c>
-      <c r="Z14">
-        <f t="shared" si="10"/>
-        <v>93.084387663209</v>
-      </c>
-      <c r="AA14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>0.43931599999999998</v>
       </c>
@@ -1730,54 +1092,10 @@
         <v>5995</v>
       </c>
       <c r="P15">
-        <f t="shared" si="0"/>
-        <v>163.78272436371304</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="1"/>
-        <v>0.95999999999999086</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="2"/>
-        <v>176.69999999999996</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="3"/>
-        <v>0.43622000195662353</v>
-      </c>
-      <c r="T15">
-        <f t="shared" si="4"/>
-        <v>-3.6467242222222383E-2</v>
-      </c>
-      <c r="U15">
-        <f t="shared" si="5"/>
-        <v>0.3960112244444447</v>
-      </c>
-      <c r="V15">
-        <f t="shared" si="6"/>
-        <v>1.1880336733333341</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="7"/>
-        <v>375.4589969031249</v>
-      </c>
-      <c r="X15">
-        <f t="shared" si="8"/>
-        <v>-26.324995845586226</v>
-      </c>
-      <c r="Y15">
-        <f t="shared" si="9"/>
-        <v>446.19947388584364</v>
-      </c>
-      <c r="Z15">
-        <f t="shared" si="10"/>
-        <v>84.282122845103899</v>
-      </c>
-      <c r="AA15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0.38632460000000002</v>
       </c>
@@ -1824,54 +1142,10 @@
         <v>5881</v>
       </c>
       <c r="P16">
-        <f t="shared" si="0"/>
-        <v>160.04149461936427</v>
-      </c>
-      <c r="Q16">
-        <f t="shared" si="1"/>
-        <v>-3.1200000000000121</v>
-      </c>
-      <c r="R16">
-        <f t="shared" si="2"/>
-        <v>175.20000000000002</v>
-      </c>
-      <c r="S16">
-        <f t="shared" si="3"/>
-        <v>0.44510222407896061</v>
-      </c>
-      <c r="T16">
-        <f t="shared" si="4"/>
-        <v>1.7094000000003051E-3</v>
-      </c>
-      <c r="U16">
-        <f t="shared" si="5"/>
-        <v>0.38461513333333336</v>
-      </c>
-      <c r="V16">
-        <f t="shared" si="6"/>
-        <v>1.1538454</v>
-      </c>
-      <c r="W16">
-        <f t="shared" si="7"/>
-        <v>359.56121079946143</v>
-      </c>
-      <c r="X16">
-        <f t="shared" si="8"/>
-        <v>-1825.2018252015064</v>
-      </c>
-      <c r="Y16">
-        <f t="shared" si="9"/>
-        <v>455.52029760659445</v>
-      </c>
-      <c r="Z16">
-        <f t="shared" si="10"/>
-        <v>99.176198128449528</v>
-      </c>
-      <c r="AA16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>0.42948674999999997</v>
       </c>
@@ -1918,54 +1192,10 @@
         <v>13062</v>
       </c>
       <c r="P17">
-        <f t="shared" si="0"/>
-        <v>347.62259707907373</v>
-      </c>
-      <c r="Q17">
-        <f t="shared" si="1"/>
-        <v>-0.90000000000003033</v>
-      </c>
-      <c r="R17">
-        <f t="shared" si="2"/>
-        <v>376.875</v>
-      </c>
-      <c r="S17">
-        <f t="shared" si="3"/>
-        <v>0.48482585431698233</v>
-      </c>
-      <c r="T17">
-        <f t="shared" si="4"/>
-        <v>-5.9828995833333377E-2</v>
-      </c>
-      <c r="U17">
-        <f t="shared" si="5"/>
-        <v>0.44978600416666675</v>
-      </c>
-      <c r="V17">
-        <f t="shared" si="6"/>
-        <v>1.3493580125000002</v>
-      </c>
-      <c r="W17">
-        <f t="shared" si="7"/>
-        <v>717.00507302524295</v>
-      </c>
-      <c r="X17">
-        <f t="shared" si="8"/>
-        <v>15.042873233359543</v>
-      </c>
-      <c r="Y17">
-        <f t="shared" si="9"/>
-        <v>837.89845950909171</v>
-      </c>
-      <c r="Z17">
-        <f t="shared" si="10"/>
-        <v>170.26013324243698</v>
-      </c>
-      <c r="AA17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>0.40384606249999999</v>
       </c>
@@ -2012,54 +1242,10 @@
         <v>14157</v>
       </c>
       <c r="P18">
-        <f t="shared" si="0"/>
-        <v>349.18144280588569</v>
-      </c>
-      <c r="Q18">
-        <f t="shared" si="1"/>
-        <v>2.2499999999999698</v>
-      </c>
-      <c r="R18">
-        <f t="shared" si="2"/>
-        <v>376.59375</v>
-      </c>
-      <c r="S18">
-        <f t="shared" si="3"/>
-        <v>0.38767569465383483</v>
-      </c>
-      <c r="T18">
-        <f t="shared" si="4"/>
-        <v>-0.11057708333333334</v>
-      </c>
-      <c r="U18">
-        <f t="shared" si="5"/>
-        <v>0.39102554166666664</v>
-      </c>
-      <c r="V18">
-        <f t="shared" si="6"/>
-        <v>1.173076625</v>
-      </c>
-      <c r="W18">
-        <f t="shared" si="7"/>
-        <v>900.70501612869589</v>
-      </c>
-      <c r="X18">
-        <f t="shared" si="8"/>
-        <v>-20.347796597395963</v>
-      </c>
-      <c r="Y18">
-        <f t="shared" si="9"/>
-        <v>963.09245783496885</v>
-      </c>
-      <c r="Z18">
-        <f t="shared" si="10"/>
-        <v>190.13463847683437</v>
-      </c>
-      <c r="AA18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>0.42467931250000002</v>
       </c>
@@ -2106,54 +1292,10 @@
         <v>13251</v>
       </c>
       <c r="P19">
-        <f t="shared" si="0"/>
-        <v>348.79173137418269</v>
-      </c>
-      <c r="Q19">
-        <f t="shared" si="1"/>
-        <v>-0.22500000000003031</v>
-      </c>
-      <c r="R19">
-        <f t="shared" si="2"/>
-        <v>377.71875</v>
-      </c>
-      <c r="S19">
-        <f t="shared" si="3"/>
-        <v>0.46724643351307549</v>
-      </c>
-      <c r="T19">
-        <f t="shared" si="4"/>
-        <v>-7.3183854166666687E-2</v>
-      </c>
-      <c r="U19">
-        <f t="shared" si="5"/>
-        <v>0.44123920833333335</v>
-      </c>
-      <c r="V19">
-        <f t="shared" si="6"/>
-        <v>1.323717625</v>
-      </c>
-      <c r="W19">
-        <f t="shared" si="7"/>
-        <v>746.48345360654753</v>
-      </c>
-      <c r="X19">
-        <f t="shared" si="8"/>
-        <v>3.0744486275295388</v>
-      </c>
-      <c r="Y19">
-        <f t="shared" si="9"/>
-        <v>856.04076624725758</v>
-      </c>
-      <c r="Z19">
-        <f t="shared" si="10"/>
-        <v>169.48856445119856</v>
-      </c>
-      <c r="AA19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>0.49914520000000001</v>
       </c>
@@ -2200,54 +1342,10 @@
         <v>4811</v>
       </c>
       <c r="P20">
-        <f t="shared" si="0"/>
-        <v>2.9098453567157061</v>
-      </c>
-      <c r="Q20">
-        <f t="shared" si="1"/>
-        <v>1.6799999999999953</v>
-      </c>
-      <c r="R20">
-        <f t="shared" si="2"/>
-        <v>2.0999999999999943</v>
-      </c>
-      <c r="S20">
-        <f t="shared" si="3"/>
-        <v>0.49148769940619347</v>
-      </c>
-      <c r="T20">
-        <f t="shared" si="4"/>
-        <v>0.26438735555555559</v>
-      </c>
-      <c r="U20">
-        <f t="shared" si="5"/>
-        <v>0.29344715555555567</v>
-      </c>
-      <c r="V20">
-        <f t="shared" si="6"/>
-        <v>0.88034146666666702</v>
-      </c>
-      <c r="W20">
-        <f t="shared" si="7"/>
-        <v>5.9204846026285676</v>
-      </c>
-      <c r="X20">
-        <f t="shared" si="8"/>
-        <v>6.3543129605038073</v>
-      </c>
-      <c r="Y20">
-        <f t="shared" si="9"/>
-        <v>7.15631404238444</v>
-      </c>
-      <c r="Z20">
-        <f t="shared" si="10"/>
-        <v>5.8159250630172235</v>
-      </c>
-      <c r="AA20">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>0.48205113333333299</v>
       </c>
@@ -2294,54 +1392,10 @@
         <v>5071</v>
       </c>
       <c r="P21">
-        <f t="shared" si="0"/>
-        <v>2.9098453567157194</v>
-      </c>
-      <c r="Q21">
-        <f t="shared" si="1"/>
-        <v>1.2000000000000028</v>
-      </c>
-      <c r="R21">
-        <f t="shared" si="2"/>
-        <v>2.4000000000000057</v>
-      </c>
-      <c r="S21">
-        <f t="shared" si="3"/>
-        <v>0.4569453370198131</v>
-      </c>
-      <c r="T21">
-        <f t="shared" si="4"/>
-        <v>0.25925910888888887</v>
-      </c>
-      <c r="U21">
-        <f t="shared" si="5"/>
-        <v>0.26609671555555553</v>
-      </c>
-      <c r="V21">
-        <f t="shared" si="6"/>
-        <v>0.79829014666666664</v>
-      </c>
-      <c r="W21">
-        <f t="shared" si="7"/>
-        <v>6.3680381896304343</v>
-      </c>
-      <c r="X21">
-        <f t="shared" si="8"/>
-        <v>4.6285741131444258</v>
-      </c>
-      <c r="Y21">
-        <f t="shared" si="9"/>
-        <v>9.0192770511627565</v>
-      </c>
-      <c r="Z21">
-        <f t="shared" si="10"/>
-        <v>1.8088660946518691</v>
-      </c>
-      <c r="AA21">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>0.51623946666666698</v>
       </c>
@@ -2388,54 +1442,10 @@
         <v>4860</v>
       </c>
       <c r="P22">
-        <f t="shared" si="0"/>
-        <v>0.83138438763306644</v>
-      </c>
-      <c r="Q22">
-        <f t="shared" si="1"/>
-        <v>0.48000000000000298</v>
-      </c>
-      <c r="R22">
-        <f t="shared" si="2"/>
-        <v>0.60000000000000375</v>
-      </c>
-      <c r="S22">
-        <f t="shared" si="3"/>
-        <v>0.51122630436932037</v>
-      </c>
-      <c r="T22">
-        <f t="shared" si="4"/>
-        <v>0.28490024444444462</v>
-      </c>
-      <c r="U22">
-        <f t="shared" si="5"/>
-        <v>0.30028484444444464</v>
-      </c>
-      <c r="V22">
-        <f t="shared" si="6"/>
-        <v>0.90085453333333398</v>
-      </c>
-      <c r="W22">
-        <f t="shared" si="7"/>
-        <v>1.6262551056693226</v>
-      </c>
-      <c r="X22">
-        <f t="shared" si="8"/>
-        <v>1.6848002392416435</v>
-      </c>
-      <c r="Y22">
-        <f t="shared" si="9"/>
-        <v>1.9981028383568957</v>
-      </c>
-      <c r="Z22">
-        <f t="shared" si="10"/>
-        <v>1.31208753052102</v>
-      </c>
-      <c r="AA22">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>0.253204875</v>
       </c>
@@ -2482,54 +1492,10 @@
         <v>3002</v>
       </c>
       <c r="P23">
-        <f t="shared" si="0"/>
-        <v>78.331997772302472</v>
-      </c>
-      <c r="Q23">
-        <f t="shared" si="1"/>
-        <v>140.625</v>
-      </c>
-      <c r="R23">
-        <f t="shared" si="2"/>
-        <v>-3.09375</v>
-      </c>
-      <c r="S23">
-        <f t="shared" si="3"/>
-        <v>0.23408570679811125</v>
-      </c>
-      <c r="T23">
-        <f t="shared" si="4"/>
-        <v>-8.8141095833333349E-2</v>
-      </c>
-      <c r="U23">
-        <f t="shared" si="5"/>
-        <v>0.24679471666666664</v>
-      </c>
-      <c r="V23">
-        <f t="shared" si="6"/>
-        <v>0.74038414999999991</v>
-      </c>
-      <c r="W23">
-        <f t="shared" si="7"/>
-        <v>334.62956300813539</v>
-      </c>
-      <c r="X23">
-        <f t="shared" si="8"/>
-        <v>-1595.4532748935735</v>
-      </c>
-      <c r="Y23">
-        <f t="shared" si="9"/>
-        <v>-12.535722165311077</v>
-      </c>
-      <c r="Z23">
-        <f t="shared" si="10"/>
-        <v>0.22032481381455832</v>
-      </c>
-      <c r="AA23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>0.20833313749999999</v>
       </c>
@@ -2576,54 +1542,10 @@
         <v>3043</v>
       </c>
       <c r="P24">
-        <f t="shared" si="0"/>
-        <v>78.331997772302472</v>
-      </c>
-      <c r="Q24">
-        <f t="shared" si="1"/>
-        <v>140.17500000000001</v>
-      </c>
-      <c r="R24">
-        <f t="shared" si="2"/>
-        <v>-2.8125</v>
-      </c>
-      <c r="S24">
-        <f t="shared" si="3"/>
-        <v>0.2183566394803694</v>
-      </c>
-      <c r="T24">
-        <f t="shared" si="4"/>
-        <v>-7.1581152083333335E-2</v>
-      </c>
-      <c r="U24">
-        <f t="shared" si="5"/>
-        <v>0.22489297291666666</v>
-      </c>
-      <c r="V24">
-        <f t="shared" si="6"/>
-        <v>0.67467891874999997</v>
-      </c>
-      <c r="W24">
-        <f t="shared" si="7"/>
-        <v>358.73421554165583</v>
-      </c>
-      <c r="X24">
-        <f t="shared" si="8"/>
-        <v>-1958.2668889823274</v>
-      </c>
-      <c r="Y24">
-        <f t="shared" si="9"/>
-        <v>-12.505948778764921</v>
-      </c>
-      <c r="Z24">
-        <f t="shared" si="10"/>
-        <v>0.60306458552733599</v>
-      </c>
-      <c r="AA24">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>0.18269213749999999</v>
       </c>
@@ -2670,54 +1592,10 @@
         <v>3050</v>
       </c>
       <c r="P25">
-        <f t="shared" si="0"/>
-        <v>79.501132067411461</v>
-      </c>
-      <c r="Q25">
-        <f t="shared" si="1"/>
-        <v>139.94999999999999</v>
-      </c>
-      <c r="R25">
-        <f t="shared" si="2"/>
-        <v>-1.40625</v>
-      </c>
-      <c r="S25">
-        <f t="shared" si="3"/>
-        <v>0.21373042559277167</v>
-      </c>
-      <c r="T25">
-        <f t="shared" si="4"/>
-        <v>-5.6089722916666675E-2</v>
-      </c>
-      <c r="U25">
-        <f t="shared" si="5"/>
-        <v>0.21314083958333332</v>
-      </c>
-      <c r="V25">
-        <f t="shared" si="6"/>
-        <v>0.63942251875</v>
-      </c>
-      <c r="W25">
-        <f t="shared" si="7"/>
-        <v>371.96918429801781</v>
-      </c>
-      <c r="X25">
-        <f t="shared" si="8"/>
-        <v>-2495.1094910546403</v>
-      </c>
-      <c r="Y25">
-        <f t="shared" si="9"/>
-        <v>-6.5977501202916464</v>
-      </c>
-      <c r="Z25">
-        <f t="shared" si="10"/>
-        <v>2.3751900433049928</v>
-      </c>
-      <c r="AA25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>0.227350213333333</v>
       </c>
@@ -2764,54 +1642,10 @@
         <v>8140</v>
       </c>
       <c r="P26">
-        <f t="shared" si="0"/>
-        <v>88.126745089104489</v>
-      </c>
-      <c r="Q26">
-        <f t="shared" si="1"/>
-        <v>145.44</v>
-      </c>
-      <c r="R26">
-        <f t="shared" si="2"/>
-        <v>4.5</v>
-      </c>
-      <c r="S26">
-        <f t="shared" si="3"/>
-        <v>0.32864549017799516</v>
-      </c>
-      <c r="T26">
-        <f t="shared" si="4"/>
-        <v>-1.4244926666666694E-2</v>
-      </c>
-      <c r="U26">
-        <f t="shared" si="5"/>
-        <v>0.29173780666666632</v>
-      </c>
-      <c r="V26">
-        <f t="shared" si="6"/>
-        <v>0.87521341999999902</v>
-      </c>
-      <c r="W26">
-        <f t="shared" si="7"/>
-        <v>268.15139024538217</v>
-      </c>
-      <c r="X26">
-        <f t="shared" si="8"/>
-        <v>-10209.950770777319</v>
-      </c>
-      <c r="Y26">
-        <f t="shared" si="9"/>
-        <v>15.424809185398479</v>
-      </c>
-      <c r="Z26">
-        <f t="shared" si="10"/>
-        <v>2.0223638709744671</v>
-      </c>
-      <c r="AA26">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>0.222222</v>
       </c>
@@ -2858,54 +1692,10 @@
         <v>7984</v>
       </c>
       <c r="P27">
-        <f t="shared" si="0"/>
-        <v>86.879668507654898</v>
-      </c>
-      <c r="Q27">
-        <f t="shared" si="1"/>
-        <v>147.12</v>
-      </c>
-      <c r="R27">
-        <f t="shared" si="2"/>
-        <v>2.0999999999999943</v>
-      </c>
-      <c r="S27">
-        <f t="shared" si="3"/>
-        <v>0.30397214544704593</v>
-      </c>
-      <c r="T27">
-        <f t="shared" si="4"/>
-        <v>-2.279204444444701E-3</v>
-      </c>
-      <c r="U27">
-        <f t="shared" si="5"/>
-        <v>0.26438720222222234</v>
-      </c>
-      <c r="V27">
-        <f t="shared" si="6"/>
-        <v>0.79316160666666702</v>
-      </c>
-      <c r="W27">
-        <f t="shared" si="7"/>
-        <v>285.81457152885724</v>
-      </c>
-      <c r="X27">
-        <f t="shared" si="8"/>
-        <v>-64548.838678595988</v>
-      </c>
-      <c r="Y27">
-        <f t="shared" si="9"/>
-        <v>7.9428958071688562</v>
-      </c>
-      <c r="Z27">
-        <f t="shared" si="10"/>
-        <v>5.3961260404258535</v>
-      </c>
-      <c r="AA27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>0.25299120000000003</v>
       </c>
@@ -2952,54 +1742,10 @@
         <v>8006</v>
       </c>
       <c r="P28">
-        <f t="shared" si="0"/>
-        <v>89.789513864370605</v>
-      </c>
-      <c r="Q28">
-        <f t="shared" si="1"/>
-        <v>148.32000000000002</v>
-      </c>
-      <c r="R28">
-        <f t="shared" si="2"/>
-        <v>4.5</v>
-      </c>
-      <c r="S28">
-        <f t="shared" si="3"/>
-        <v>0.29903753654528414</v>
-      </c>
-      <c r="T28">
-        <f t="shared" si="4"/>
-        <v>3.8176588888888953E-2</v>
-      </c>
-      <c r="U28">
-        <f t="shared" si="5"/>
-        <v>0.239885808888889</v>
-      </c>
-      <c r="V28">
-        <f t="shared" si="6"/>
-        <v>0.71965742666666699</v>
-      </c>
-      <c r="W28">
-        <f t="shared" si="7"/>
-        <v>300.26168253554187</v>
-      </c>
-      <c r="X28">
-        <f t="shared" si="8"/>
-        <v>3885.1035233052889</v>
-      </c>
-      <c r="Y28">
-        <f t="shared" si="9"/>
-        <v>18.758925427240772</v>
-      </c>
-      <c r="Z28">
-        <f t="shared" si="10"/>
-        <v>2.8180074363900562</v>
-      </c>
-      <c r="AA28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>0.19316222</v>
       </c>
@@ -3046,54 +1792,10 @@
         <v>2846</v>
       </c>
       <c r="P29">
-        <f t="shared" si="0"/>
-        <v>81.059977794223457</v>
-      </c>
-      <c r="Q29">
-        <f t="shared" si="1"/>
-        <v>4.5599999999999907</v>
-      </c>
-      <c r="R29">
-        <f t="shared" si="2"/>
-        <v>84.899999999999991</v>
-      </c>
-      <c r="S29">
-        <f t="shared" si="3"/>
-        <v>0.19837145182571081</v>
-      </c>
-      <c r="T29">
-        <f t="shared" si="4"/>
-        <v>-3.9316193333333672E-2</v>
-      </c>
-      <c r="U29">
-        <f t="shared" si="5"/>
-        <v>0.19145281333333333</v>
-      </c>
-      <c r="V29">
-        <f t="shared" si="6"/>
-        <v>0.57435844000000003</v>
-      </c>
-      <c r="W29">
-        <f t="shared" si="7"/>
-        <v>408.62723465593609</v>
-      </c>
-      <c r="X29">
-        <f t="shared" si="8"/>
-        <v>-115.98274434503455</v>
-      </c>
-      <c r="Y29">
-        <f t="shared" si="9"/>
-        <v>443.45130542523231</v>
-      </c>
-      <c r="Z29">
-        <f t="shared" si="10"/>
-        <v>111.57144308700347</v>
-      </c>
-      <c r="AA29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>0.140170826666667</v>
       </c>
@@ -3140,54 +1842,10 @@
         <v>2659</v>
       </c>
       <c r="P30">
-        <f t="shared" si="0"/>
-        <v>81.475669988039996</v>
-      </c>
-      <c r="Q30">
-        <f t="shared" si="1"/>
-        <v>-0.48000000000000304</v>
-      </c>
-      <c r="R30">
-        <f t="shared" si="2"/>
-        <v>88.5</v>
-      </c>
-      <c r="S30">
-        <f t="shared" si="3"/>
-        <v>0.21613605387945881</v>
-      </c>
-      <c r="T30">
-        <f t="shared" si="4"/>
-        <v>1.7094000000003051E-3</v>
-      </c>
-      <c r="U30">
-        <f t="shared" si="5"/>
-        <v>0.18632461333333331</v>
-      </c>
-      <c r="V30">
-        <f t="shared" si="6"/>
-        <v>0.55897383999999994</v>
-      </c>
-      <c r="W30">
-        <f t="shared" si="7"/>
-        <v>376.96473367409482</v>
-      </c>
-      <c r="X30">
-        <f t="shared" si="8"/>
-        <v>-280.80028080023243</v>
-      </c>
-      <c r="Y30">
-        <f t="shared" si="9"/>
-        <v>474.97750520847279</v>
-      </c>
-      <c r="Z30">
-        <f t="shared" si="10"/>
-        <v>105.51119887828725</v>
-      </c>
-      <c r="AA30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>0.227350206666667</v>
       </c>
@@ -3234,54 +1892,10 @@
         <v>3053</v>
       </c>
       <c r="P31">
-        <f t="shared" si="0"/>
-        <v>80.644285600406945</v>
-      </c>
-      <c r="Q31">
-        <f t="shared" si="1"/>
-        <v>-0.95999999999999852</v>
-      </c>
-      <c r="R31">
-        <f t="shared" si="2"/>
-        <v>87.899999999999991</v>
-      </c>
-      <c r="S31">
-        <f t="shared" si="3"/>
-        <v>0.22008374408006978</v>
-      </c>
-      <c r="T31">
-        <f t="shared" si="4"/>
-        <v>-3.8176635555555692E-2</v>
-      </c>
-      <c r="U31">
-        <f t="shared" si="5"/>
-        <v>0.20968643111111132</v>
-      </c>
-      <c r="V31">
-        <f t="shared" si="6"/>
-        <v>0.62905929333333399</v>
-      </c>
-      <c r="W31">
-        <f t="shared" si="7"/>
-        <v>366.42545289972594</v>
-      </c>
-      <c r="X31">
-        <f t="shared" si="8"/>
-        <v>25.146270383176645</v>
-      </c>
-      <c r="Y31">
-        <f t="shared" si="9"/>
-        <v>419.19736787080143</v>
-      </c>
-      <c r="Z31">
-        <f t="shared" si="10"/>
-        <v>85.785236100796098</v>
-      </c>
-      <c r="AA31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>0.19316227999999999</v>
       </c>
@@ -3328,54 +1942,10 @@
         <v>6001</v>
       </c>
       <c r="P32">
-        <f t="shared" si="0"/>
-        <v>167.93964630187835</v>
-      </c>
-      <c r="Q32">
-        <f t="shared" si="1"/>
-        <v>0.95999999999999086</v>
-      </c>
-      <c r="R32">
-        <f t="shared" si="2"/>
-        <v>181.19999999999996</v>
-      </c>
-      <c r="S32">
-        <f t="shared" si="3"/>
-        <v>0.28324689891089744</v>
-      </c>
-      <c r="T32">
-        <f t="shared" si="4"/>
-        <v>-5.1282288888886973E-3</v>
-      </c>
-      <c r="U32">
-        <f t="shared" si="5"/>
-        <v>0.24786312444444433</v>
-      </c>
-      <c r="V32">
-        <f t="shared" si="6"/>
-        <v>0.74358937333333297</v>
-      </c>
-      <c r="W32">
-        <f t="shared" si="7"/>
-        <v>592.90903783101282</v>
-      </c>
-      <c r="X32">
-        <f t="shared" si="8"/>
-        <v>-187.19913264402396</v>
-      </c>
-      <c r="Y32">
-        <f t="shared" si="9"/>
-        <v>731.04863987387466</v>
-      </c>
-      <c r="Z32">
-        <f t="shared" si="10"/>
-        <v>162.34766704483843</v>
-      </c>
-      <c r="AA32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>0.27863228000000001</v>
       </c>
@@ -3422,54 +1992,10 @@
         <v>6367</v>
       </c>
       <c r="P33">
-        <f t="shared" si="0"/>
-        <v>166.69256972042876</v>
-      </c>
-      <c r="Q33">
-        <f t="shared" si="1"/>
-        <v>0.71999999999998177</v>
-      </c>
-      <c r="R33">
-        <f t="shared" si="2"/>
-        <v>180</v>
-      </c>
-      <c r="S33">
-        <f t="shared" si="3"/>
-        <v>0.23390070212122779</v>
-      </c>
-      <c r="T33">
-        <f t="shared" si="4"/>
-        <v>-2.5640971111111355E-2</v>
-      </c>
-      <c r="U33">
-        <f t="shared" si="5"/>
-        <v>0.21538443555555567</v>
-      </c>
-      <c r="V33">
-        <f t="shared" si="6"/>
-        <v>0.64615330666666704</v>
-      </c>
-      <c r="W33">
-        <f t="shared" si="7"/>
-        <v>712.66382789237673</v>
-      </c>
-      <c r="X33">
-        <f t="shared" si="8"/>
-        <v>-28.080059716926019</v>
-      </c>
-      <c r="Y33">
-        <f t="shared" si="9"/>
-        <v>835.71498346996987</v>
-      </c>
-      <c r="Z33">
-        <f t="shared" si="10"/>
-        <v>201.72302556557361</v>
-      </c>
-      <c r="AA33">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>0.20170920000000001</v>
       </c>
@@ -3516,54 +2042,10 @@
         <v>5859</v>
       </c>
       <c r="P34">
-        <f t="shared" si="0"/>
-        <v>166.69256972042876</v>
-      </c>
-      <c r="Q34">
-        <f t="shared" si="1"/>
-        <v>-0.72000000000002728</v>
-      </c>
-      <c r="R34">
-        <f t="shared" si="2"/>
-        <v>180.9</v>
-      </c>
-      <c r="S34">
-        <f t="shared" si="3"/>
-        <v>0.26350832473978525</v>
-      </c>
-      <c r="T34">
-        <f t="shared" si="4"/>
-        <v>-1.709446666666355E-3</v>
-      </c>
-      <c r="U34">
-        <f t="shared" si="5"/>
-        <v>0.22905962666666668</v>
-      </c>
-      <c r="V34">
-        <f t="shared" si="6"/>
-        <v>0.68717888000000005</v>
-      </c>
-      <c r="W34">
-        <f t="shared" si="7"/>
-        <v>632.58938739426105</v>
-      </c>
-      <c r="X34">
-        <f t="shared" si="8"/>
-        <v>421.1889227314249</v>
-      </c>
-      <c r="Y34">
-        <f t="shared" si="9"/>
-        <v>789.75069780957176</v>
-      </c>
-      <c r="Z34">
-        <f t="shared" si="10"/>
-        <v>165.74723600352792</v>
-      </c>
-      <c r="AA34">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>0.41025667999999998</v>
       </c>
@@ -3610,54 +2092,10 @@
         <v>12340</v>
       </c>
       <c r="P35">
-        <f t="shared" si="0"/>
-        <v>351.67559596878488</v>
-      </c>
-      <c r="Q35">
-        <f t="shared" si="1"/>
-        <v>3.3599999999999759</v>
-      </c>
-      <c r="R35">
-        <f t="shared" si="2"/>
-        <v>378.59999999999997</v>
-      </c>
-      <c r="S35">
-        <f t="shared" si="3"/>
-        <v>0.41253413403208489</v>
-      </c>
-      <c r="T35">
-        <f t="shared" si="4"/>
-        <v>-0.12193695111111136</v>
-      </c>
-      <c r="U35">
-        <f t="shared" si="5"/>
-        <v>0.41823351555555566</v>
-      </c>
-      <c r="V35">
-        <f t="shared" si="6"/>
-        <v>1.254700546666667</v>
-      </c>
-      <c r="W35">
-        <f t="shared" si="7"/>
-        <v>852.47635760834589</v>
-      </c>
-      <c r="X35">
-        <f t="shared" si="8"/>
-        <v>-27.555223985699605</v>
-      </c>
-      <c r="Y35">
-        <f t="shared" si="9"/>
-        <v>905.23591706200546</v>
-      </c>
-      <c r="Z35">
-        <f t="shared" si="10"/>
-        <v>191.3970633375352</v>
-      </c>
-      <c r="AA35">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>0.26495707333333302</v>
       </c>
@@ -3704,54 +2142,10 @@
         <v>11980</v>
       </c>
       <c r="P36">
-        <f t="shared" si="0"/>
-        <v>355.83251790695027</v>
-      </c>
-      <c r="Q36">
-        <f t="shared" si="1"/>
-        <v>0.47999999999998788</v>
-      </c>
-      <c r="R36">
-        <f t="shared" si="2"/>
-        <v>384.90000000000003</v>
-      </c>
-      <c r="S36">
-        <f t="shared" si="3"/>
-        <v>0.31285465239551552</v>
-      </c>
-      <c r="T36">
-        <f t="shared" si="4"/>
-        <v>-3.9886688888890092E-3</v>
-      </c>
-      <c r="U36">
-        <f t="shared" si="5"/>
-        <v>0.272934411111111</v>
-      </c>
-      <c r="V36">
-        <f t="shared" si="6"/>
-        <v>0.81880323333333305</v>
-      </c>
-      <c r="W36">
-        <f t="shared" si="7"/>
-        <v>1137.3732664109514</v>
-      </c>
-      <c r="X36">
-        <f t="shared" si="8"/>
-        <v>-120.34089902450778</v>
-      </c>
-      <c r="Y36">
-        <f t="shared" si="9"/>
-        <v>1410.2289206885976</v>
-      </c>
-      <c r="Z36">
-        <f t="shared" si="10"/>
-        <v>314.02416298877193</v>
-      </c>
-      <c r="AA36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>0.252991353333333</v>
       </c>
@@ -3798,54 +2192,10 @@
         <v>13343</v>
       </c>
       <c r="P37">
-        <f t="shared" si="0"/>
-        <v>358.74236326366588</v>
-      </c>
-      <c r="Q37">
-        <f t="shared" si="1"/>
-        <v>3.1199999999999819</v>
-      </c>
-      <c r="R37">
-        <f t="shared" si="2"/>
-        <v>386.40000000000003</v>
-      </c>
-      <c r="S37">
-        <f t="shared" si="3"/>
-        <v>0.27436459980852412</v>
-      </c>
-      <c r="T37">
-        <f t="shared" si="4"/>
-        <v>7.9772222222219882E-3</v>
-      </c>
-      <c r="U37">
-        <f t="shared" si="5"/>
-        <v>0.23361810222222198</v>
-      </c>
-      <c r="V37">
-        <f t="shared" si="6"/>
-        <v>0.70085430666666593</v>
-      </c>
-      <c r="W37">
-        <f t="shared" si="7"/>
-        <v>1307.5388133674244</v>
-      </c>
-      <c r="X37">
-        <f t="shared" si="8"/>
-        <v>391.11358729717477</v>
-      </c>
-      <c r="Y37">
-        <f t="shared" si="9"/>
-        <v>1653.9814180685751</v>
-      </c>
-      <c r="Z37">
-        <f t="shared" si="10"/>
-        <v>375.94404071389243</v>
-      </c>
-      <c r="AA37">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>0.63905376923076895</v>
       </c>
@@ -3892,54 +2242,10 @@
         <v>4645</v>
       </c>
       <c r="P38">
-        <f t="shared" si="0"/>
-        <v>1.4389345170571677</v>
-      </c>
-      <c r="Q38">
-        <f t="shared" si="1"/>
-        <v>0.83076923076919973</v>
-      </c>
-      <c r="R38">
-        <f t="shared" si="2"/>
-        <v>1.0384615384614999</v>
-      </c>
-      <c r="S38">
-        <f t="shared" si="3"/>
-        <v>0.72766652058228631</v>
-      </c>
-      <c r="T38">
-        <f t="shared" si="4"/>
-        <v>0.40828414871794849</v>
-      </c>
-      <c r="U38">
-        <f t="shared" si="5"/>
-        <v>0.42603561794871769</v>
-      </c>
-      <c r="V38">
-        <f t="shared" si="6"/>
-        <v>1.2781068538461531</v>
-      </c>
-      <c r="W38">
-        <f t="shared" si="7"/>
-        <v>1.9774642317001438</v>
-      </c>
-      <c r="X38">
-        <f t="shared" si="8"/>
-        <v>2.0347819854821574</v>
-      </c>
-      <c r="Y38">
-        <f t="shared" si="9"/>
-        <v>2.4374993421007831</v>
-      </c>
-      <c r="Z38">
-        <f t="shared" si="10"/>
-        <v>1.9644439142264818</v>
-      </c>
-      <c r="AA38">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>0.60946761538461502</v>
       </c>
@@ -3986,54 +2292,10 @@
         <v>4435</v>
       </c>
       <c r="P39">
-        <f t="shared" si="0"/>
-        <v>1.4389345170571677</v>
-      </c>
-      <c r="Q39">
-        <f t="shared" si="1"/>
-        <v>0.27692307692304502</v>
-      </c>
-      <c r="R39">
-        <f t="shared" si="2"/>
-        <v>1.3846153846153488</v>
-      </c>
-      <c r="S39">
-        <f t="shared" si="3"/>
-        <v>0.65364724049771195</v>
-      </c>
-      <c r="T39">
-        <f t="shared" si="4"/>
-        <v>0.36160432820512795</v>
-      </c>
-      <c r="U39">
-        <f t="shared" si="5"/>
-        <v>0.38527295128205102</v>
-      </c>
-      <c r="V39">
-        <f t="shared" si="6"/>
-        <v>1.1558188538461531</v>
-      </c>
-      <c r="W39">
-        <f t="shared" si="7"/>
-        <v>2.2013930877479235</v>
-      </c>
-      <c r="X39">
-        <f t="shared" si="8"/>
-        <v>0.76581792673110471</v>
-      </c>
-      <c r="Y39">
-        <f t="shared" si="9"/>
-        <v>3.5938556807786335</v>
-      </c>
-      <c r="Z39">
-        <f t="shared" si="10"/>
-        <v>3.2244871802542399</v>
-      </c>
-      <c r="AA39">
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>0.63708115384615405</v>
       </c>
@@ -4080,54 +2342,10 @@
         <v>4087</v>
       </c>
       <c r="P40">
-        <f t="shared" si="0"/>
-        <v>0.47964483901906463</v>
-      </c>
-      <c r="Q40">
-        <f t="shared" si="1"/>
-        <v>0.83076923076922637</v>
-      </c>
-      <c r="R40">
-        <f t="shared" si="2"/>
-        <v>-9.473903143468002E-15</v>
-      </c>
-      <c r="S40">
-        <f t="shared" si="3"/>
-        <v>0.68553256381424799</v>
-      </c>
-      <c r="T40">
-        <f t="shared" si="4"/>
-        <v>0.38527301538461539</v>
-      </c>
-      <c r="U40">
-        <f t="shared" si="5"/>
-        <v>0.40105210769230776</v>
-      </c>
-      <c r="V40">
-        <f t="shared" si="6"/>
-        <v>1.2031563230769233</v>
-      </c>
-      <c r="W40">
-        <f t="shared" si="7"/>
-        <v>0.69966747655335204</v>
-      </c>
-      <c r="X40">
-        <f t="shared" si="8"/>
-        <v>2.1563130496950977</v>
-      </c>
-      <c r="Y40">
-        <f t="shared" si="9"/>
-        <v>-2.3622623997619034E-14</v>
-      </c>
-      <c r="Z40">
-        <f t="shared" si="10"/>
-        <v>-0.13809832192532667</v>
-      </c>
-      <c r="AA40">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>0.39458666666666697</v>
       </c>
@@ -4174,54 +2392,10 @@
         <v>3040</v>
       </c>
       <c r="P41">
-        <f t="shared" si="0"/>
-        <v>72.399723756379075</v>
-      </c>
-      <c r="Q41">
-        <f t="shared" si="1"/>
-        <v>122.6</v>
-      </c>
-      <c r="R41">
-        <f t="shared" si="2"/>
-        <v>1.75</v>
-      </c>
-      <c r="S41">
-        <f t="shared" si="3"/>
-        <v>0.4432929045603653</v>
-      </c>
-      <c r="T41">
-        <f t="shared" si="4"/>
-        <v>-0.2255463888888887</v>
-      </c>
-      <c r="U41">
-        <f t="shared" si="5"/>
-        <v>0.49667611111111132</v>
-      </c>
-      <c r="V41">
-        <f t="shared" si="6"/>
-        <v>1.490028333333334</v>
-      </c>
-      <c r="W41">
-        <f t="shared" si="7"/>
-        <v>163.32254139772738</v>
-      </c>
-      <c r="X41">
-        <f t="shared" si="8"/>
-        <v>-543.56888888341564</v>
-      </c>
-      <c r="Y41">
-        <f t="shared" si="9"/>
-        <v>3.5234229326735385</v>
-      </c>
-      <c r="Z41">
-        <f t="shared" si="10"/>
-        <v>2.2605834117248369</v>
-      </c>
-      <c r="AA41">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>0.3148145</v>
       </c>
@@ -4268,54 +2442,10 @@
         <v>3516</v>
       </c>
       <c r="P42">
-        <f t="shared" si="0"/>
-        <v>73.092544079406636</v>
-      </c>
-      <c r="Q42">
-        <f t="shared" si="1"/>
-        <v>130.19999999999999</v>
-      </c>
-      <c r="R42">
-        <f t="shared" si="2"/>
-        <v>-2.25</v>
-      </c>
-      <c r="S42">
-        <f t="shared" si="3"/>
-        <v>0.3388434088857763</v>
-      </c>
-      <c r="T42">
-        <f t="shared" si="4"/>
-        <v>-0.16714181481481469</v>
-      </c>
-      <c r="U42">
-        <f t="shared" si="5"/>
-        <v>0.37701790740740732</v>
-      </c>
-      <c r="V42">
-        <f t="shared" si="6"/>
-        <v>1.1310537222222219</v>
-      </c>
-      <c r="W42">
-        <f t="shared" si="7"/>
-        <v>215.7118661973031</v>
-      </c>
-      <c r="X42">
-        <f t="shared" si="8"/>
-        <v>-778.97921680613251</v>
-      </c>
-      <c r="Y42">
-        <f t="shared" si="9"/>
-        <v>-5.9678862881402592</v>
-      </c>
-      <c r="Z42">
-        <f t="shared" si="10"/>
-        <v>1.0948492622440038</v>
-      </c>
-      <c r="AA42">
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>0.30484299999999998</v>
       </c>
@@ -4362,54 +2492,10 @@
         <v>3126</v>
       </c>
       <c r="P43">
-        <f t="shared" si="0"/>
-        <v>73.785364402434183</v>
-      </c>
-      <c r="Q43">
-        <f t="shared" si="1"/>
-        <v>127</v>
-      </c>
-      <c r="R43">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="S43">
-        <f t="shared" si="3"/>
-        <v>0.32486200609194565</v>
-      </c>
-      <c r="T43">
-        <f t="shared" si="4"/>
-        <v>-0.23409346296296338</v>
-      </c>
-      <c r="U43">
-        <f t="shared" si="5"/>
-        <v>0.39838548148148162</v>
-      </c>
-      <c r="V43">
-        <f t="shared" si="6"/>
-        <v>1.1951564444444449</v>
-      </c>
-      <c r="W43">
-        <f t="shared" si="7"/>
-        <v>227.1283283941512</v>
-      </c>
-      <c r="X43">
-        <f t="shared" si="8"/>
-        <v>-542.51835310793388</v>
-      </c>
-      <c r="Y43">
-        <f t="shared" si="9"/>
-        <v>1.2550658175108267</v>
-      </c>
-      <c r="Z43">
-        <f t="shared" si="10"/>
-        <v>2.5296548671266406</v>
-      </c>
-      <c r="AA43">
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>0.38119633333333303</v>
       </c>
@@ -4456,54 +2542,10 @@
         <v>7247</v>
       </c>
       <c r="P44">
-        <f t="shared" si="0"/>
-        <v>83.554130957122652</v>
-      </c>
-      <c r="Q44">
-        <f t="shared" si="1"/>
-        <v>137.04</v>
-      </c>
-      <c r="R44">
-        <f t="shared" si="2"/>
-        <v>4.8000000000000016</v>
-      </c>
-      <c r="S44">
-        <f t="shared" si="3"/>
-        <v>0.60893198324460318</v>
-      </c>
-      <c r="T44">
-        <f t="shared" si="4"/>
-        <v>-3.9886444444444296E-3</v>
-      </c>
-      <c r="U44">
-        <f t="shared" si="5"/>
-        <v>0.52934488888888864</v>
-      </c>
-      <c r="V44">
-        <f t="shared" si="6"/>
-        <v>1.588034666666666</v>
-      </c>
-      <c r="W44">
-        <f t="shared" si="7"/>
-        <v>137.21422631131466</v>
-      </c>
-      <c r="X44">
-        <f t="shared" si="8"/>
-        <v>-34357.537230693932</v>
-      </c>
-      <c r="Y44">
-        <f t="shared" si="9"/>
-        <v>9.0678121216497445</v>
-      </c>
-      <c r="Z44">
-        <f t="shared" si="10"/>
-        <v>4.681258007801679</v>
-      </c>
-      <c r="AA44">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>0.35384579999999999</v>
       </c>
@@ -4550,54 +2592,10 @@
         <v>8092</v>
       </c>
       <c r="P45">
-        <f t="shared" si="0"/>
-        <v>84.801207538572257</v>
-      </c>
-      <c r="Q45">
-        <f t="shared" si="1"/>
-        <v>137.76000000000002</v>
-      </c>
-      <c r="R45">
-        <f t="shared" si="2"/>
-        <v>5.6999999999999984</v>
-      </c>
-      <c r="S45">
-        <f t="shared" si="3"/>
-        <v>0.47174924840313864</v>
-      </c>
-      <c r="T45">
-        <f t="shared" si="4"/>
-        <v>2.3931711111110993E-2</v>
-      </c>
-      <c r="U45">
-        <f t="shared" si="5"/>
-        <v>0.39658097777777801</v>
-      </c>
-      <c r="V45">
-        <f t="shared" si="6"/>
-        <v>1.189742933333334</v>
-      </c>
-      <c r="W45">
-        <f t="shared" si="7"/>
-        <v>179.75907290922578</v>
-      </c>
-      <c r="X45">
-        <f t="shared" si="8"/>
-        <v>5756.3790303335618</v>
-      </c>
-      <c r="Y45">
-        <f t="shared" si="9"/>
-        <v>14.372852757435991</v>
-      </c>
-      <c r="Z45">
-        <f t="shared" si="10"/>
-        <v>4.2748730482058086</v>
-      </c>
-      <c r="AA45">
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>0.2427348</v>
       </c>
@@ -4644,54 +2642,10 @@
         <v>7755</v>
       </c>
       <c r="P46">
-        <f t="shared" si="0"/>
-        <v>79.812901212773866</v>
-      </c>
-      <c r="Q46">
-        <f t="shared" si="1"/>
-        <v>136.32</v>
-      </c>
-      <c r="R46">
-        <f t="shared" si="2"/>
-        <v>1.1999999999999982</v>
-      </c>
-      <c r="S46">
-        <f t="shared" si="3"/>
-        <v>0.457932448171054</v>
-      </c>
-      <c r="T46">
-        <f t="shared" si="4"/>
-        <v>1.1396222222222288E-2</v>
-      </c>
-      <c r="U46">
-        <f t="shared" si="5"/>
-        <v>0.39088302222222238</v>
-      </c>
-      <c r="V46">
-        <f t="shared" si="6"/>
-        <v>1.1726490666666671</v>
-      </c>
-      <c r="W46">
-        <f t="shared" si="7"/>
-        <v>174.28968296861314</v>
-      </c>
-      <c r="X46">
-        <f t="shared" si="8"/>
-        <v>11961.858705613877</v>
-      </c>
-      <c r="Y46">
-        <f t="shared" si="9"/>
-        <v>3.0699721701337586</v>
-      </c>
-      <c r="Z46">
-        <f t="shared" si="10"/>
-        <v>3.2575815805308181</v>
-      </c>
-      <c r="AA46">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>0.28044849999999999</v>
       </c>
@@ -4738,54 +2692,10 @@
         <v>2575</v>
       </c>
       <c r="P47">
-        <f t="shared" si="0"/>
-        <v>72.486326296757525</v>
-      </c>
-      <c r="Q47">
-        <f t="shared" si="1"/>
-        <v>-2.7000000000000077</v>
-      </c>
-      <c r="R47">
-        <f t="shared" si="2"/>
-        <v>80.15625</v>
-      </c>
-      <c r="S47">
-        <f t="shared" si="3"/>
-        <v>0.41358241159534437</v>
-      </c>
-      <c r="T47">
-        <f t="shared" si="4"/>
-        <v>0.11698715416666662</v>
-      </c>
-      <c r="U47">
-        <f t="shared" si="5"/>
-        <v>0.29967929791666664</v>
-      </c>
-      <c r="V47">
-        <f t="shared" si="6"/>
-        <v>0.89903789374999998</v>
-      </c>
-      <c r="W47">
-        <f t="shared" si="7"/>
-        <v>175.26452833704954</v>
-      </c>
-      <c r="X47">
-        <f t="shared" si="8"/>
-        <v>-23.079457050074339</v>
-      </c>
-      <c r="Y47">
-        <f t="shared" si="9"/>
-        <v>267.47343095514543</v>
-      </c>
-      <c r="Z47">
-        <f t="shared" si="10"/>
-        <v>56.032816136233087</v>
-      </c>
-      <c r="AA47">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>0.1025640375</v>
       </c>
@@ -4832,54 +2742,10 @@
         <v>2617</v>
       </c>
       <c r="P48">
-        <f t="shared" si="0"/>
-        <v>75.993729182084493</v>
-      </c>
-      <c r="Q48">
-        <f t="shared" si="1"/>
-        <v>1.5749999999999924</v>
-      </c>
-      <c r="R48">
-        <f t="shared" si="2"/>
-        <v>81.28125</v>
-      </c>
-      <c r="S48">
-        <f t="shared" si="3"/>
-        <v>0.30717984580763652</v>
-      </c>
-      <c r="T48">
-        <f t="shared" si="4"/>
-        <v>-5.0213508333333379E-2</v>
-      </c>
-      <c r="U48">
-        <f t="shared" si="5"/>
-        <v>0.29113230416666669</v>
-      </c>
-      <c r="V48">
-        <f t="shared" si="6"/>
-        <v>0.87339691250000007</v>
-      </c>
-      <c r="W48">
-        <f t="shared" si="7"/>
-        <v>247.39165091473356</v>
-      </c>
-      <c r="X48">
-        <f t="shared" si="8"/>
-        <v>-31.36606168891122</v>
-      </c>
-      <c r="Y48">
-        <f t="shared" si="9"/>
-        <v>279.19007556601588</v>
-      </c>
-      <c r="Z48">
-        <f t="shared" si="10"/>
-        <v>65.107855530689193</v>
-      </c>
-      <c r="AA48">
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>0.12019223749999999</v>
       </c>
@@ -4926,54 +2792,10 @@
         <v>3012</v>
       </c>
       <c r="P49">
-        <f t="shared" si="0"/>
-        <v>78.721709204005478</v>
-      </c>
-      <c r="Q49">
-        <f t="shared" si="1"/>
-        <v>3.1499999999999924</v>
-      </c>
-      <c r="R49">
-        <f t="shared" si="2"/>
-        <v>83.25</v>
-      </c>
-      <c r="S49">
-        <f t="shared" si="3"/>
-        <v>0.23593623709779621</v>
-      </c>
-      <c r="T49">
-        <f t="shared" si="4"/>
-        <v>-4.540590000000002E-2</v>
-      </c>
-      <c r="U49">
-        <f t="shared" si="5"/>
-        <v>0.22702972500000004</v>
-      </c>
-      <c r="V49">
-        <f t="shared" si="6"/>
-        <v>0.6810891750000001</v>
-      </c>
-      <c r="W49">
-        <f t="shared" si="7"/>
-        <v>333.65671239121747</v>
-      </c>
-      <c r="X49">
-        <f t="shared" si="8"/>
-        <v>-69.374244316267067</v>
-      </c>
-      <c r="Y49">
-        <f t="shared" si="9"/>
-        <v>366.69207082905103</v>
-      </c>
-      <c r="Z49">
-        <f t="shared" si="10"/>
-        <v>95.301397206907581</v>
-      </c>
-      <c r="AA49">
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>0.20879107142857101</v>
       </c>
@@ -5020,54 +2842,10 @@
         <v>5840</v>
       </c>
       <c r="P50">
-        <f t="shared" si="0"/>
-        <v>163.01072457519666</v>
-      </c>
-      <c r="Q50">
-        <f t="shared" si="1"/>
-        <v>4.6285714285713162</v>
-      </c>
-      <c r="R50">
-        <f t="shared" si="2"/>
-        <v>173.57142857142867</v>
-      </c>
-      <c r="S50">
-        <f t="shared" si="3"/>
-        <v>0.34683294686804161</v>
-      </c>
-      <c r="T50">
-        <f t="shared" si="4"/>
-        <v>-8.5470000000000379E-2</v>
-      </c>
-      <c r="U50">
-        <f t="shared" si="5"/>
-        <v>0.34310114285714266</v>
-      </c>
-      <c r="V50">
-        <f t="shared" si="6"/>
-        <v>1.029303428571428</v>
-      </c>
-      <c r="W50">
-        <f t="shared" si="7"/>
-        <v>469.99780743787534</v>
-      </c>
-      <c r="X50">
-        <f t="shared" si="8"/>
-        <v>-54.154339868624028</v>
-      </c>
-      <c r="Y50">
-        <f t="shared" si="9"/>
-        <v>505.88997496781514</v>
-      </c>
-      <c r="Z50">
-        <f t="shared" si="10"/>
-        <v>112.7676636793483</v>
-      </c>
-      <c r="AA50">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>0.22893752142857099</v>
       </c>
@@ -5114,54 +2892,10 @@
         <v>5448</v>
       </c>
       <c r="P51">
-        <f t="shared" si="0"/>
-        <v>163.45610906857166</v>
-      </c>
-      <c r="Q51">
-        <f t="shared" si="1"/>
-        <v>6.4285714285715887</v>
-      </c>
-      <c r="R51">
-        <f t="shared" si="2"/>
-        <v>172.92857142857147</v>
-      </c>
-      <c r="S51">
-        <f t="shared" si="3"/>
-        <v>0.28127298040462861</v>
-      </c>
-      <c r="T51">
-        <f t="shared" si="4"/>
-        <v>-0.130647211904762</v>
-      </c>
-      <c r="U51">
-        <f t="shared" si="5"/>
-        <v>0.30891315238095202</v>
-      </c>
-      <c r="V51">
-        <f t="shared" si="6"/>
-        <v>0.92673945714285599</v>
-      </c>
-      <c r="W51">
-        <f t="shared" si="7"/>
-        <v>581.12979367385344</v>
-      </c>
-      <c r="X51">
-        <f t="shared" si="8"/>
-        <v>-49.205576872607352</v>
-      </c>
-      <c r="Y51">
-        <f t="shared" si="9"/>
-        <v>559.79672634759095</v>
-      </c>
-      <c r="Z51">
-        <f t="shared" si="10"/>
-        <v>134.17779526321496</v>
-      </c>
-      <c r="AA51">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>0.155677507142857</v>
       </c>
@@ -5208,54 +2942,10 @@
         <v>5002</v>
       </c>
       <c r="P52">
-        <f t="shared" si="0"/>
-        <v>160.33841761494745</v>
-      </c>
-      <c r="Q52">
-        <f t="shared" si="1"/>
-        <v>2.05714285714292</v>
-      </c>
-      <c r="R52">
-        <f t="shared" si="2"/>
-        <v>172.28571428571414</v>
-      </c>
-      <c r="S52">
-        <f t="shared" si="3"/>
-        <v>0.38067037804724824</v>
-      </c>
-      <c r="T52">
-        <f t="shared" si="4"/>
-        <v>-8.7912188095238042E-2</v>
-      </c>
-      <c r="U52">
-        <f t="shared" si="5"/>
-        <v>0.37362631190476198</v>
-      </c>
-      <c r="V52">
-        <f t="shared" si="6"/>
-        <v>1.1208789357142859</v>
-      </c>
-      <c r="W52">
-        <f t="shared" si="7"/>
-        <v>421.20014285704804</v>
-      </c>
-      <c r="X52">
-        <f t="shared" si="8"/>
-        <v>-23.399973333781119</v>
-      </c>
-      <c r="Y52">
-        <f t="shared" si="9"/>
-        <v>461.11772323366262</v>
-      </c>
-      <c r="Z52">
-        <f t="shared" si="10"/>
-        <v>100.32178127864734</v>
-      </c>
-      <c r="AA52">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>0.39262793750000002</v>
       </c>
@@ -5302,54 +2992,10 @@
         <v>14064</v>
       </c>
       <c r="P53">
-        <f t="shared" si="0"/>
-        <v>341.38721417182575</v>
-      </c>
-      <c r="Q53">
-        <f t="shared" si="1"/>
-        <v>-0.45000000000003032</v>
-      </c>
-      <c r="R53">
-        <f t="shared" si="2"/>
-        <v>369.84375</v>
-      </c>
-      <c r="S53">
-        <f t="shared" si="3"/>
-        <v>0.46724647320590645</v>
-      </c>
-      <c r="T53">
-        <f t="shared" si="4"/>
-        <v>5.288445208333329E-2</v>
-      </c>
-      <c r="U53">
-        <f t="shared" si="5"/>
-        <v>0.37820508958333338</v>
-      </c>
-      <c r="V53">
-        <f t="shared" si="6"/>
-        <v>1.1346152687500002</v>
-      </c>
-      <c r="W53">
-        <f t="shared" si="7"/>
-        <v>730.63625676931122</v>
-      </c>
-      <c r="X53">
-        <f t="shared" si="8"/>
-        <v>-8.5091171842139453</v>
-      </c>
-      <c r="Y53">
-        <f t="shared" si="9"/>
-        <v>977.89204901355231</v>
-      </c>
-      <c r="Z53">
-        <f t="shared" si="10"/>
-        <v>213.08709803135196</v>
-      </c>
-      <c r="AA53">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>0.29647424999999999</v>
       </c>
@@ -5396,54 +3042,10 @@
         <v>13431</v>
       </c>
       <c r="P54">
-        <f t="shared" si="0"/>
-        <v>345.67403992055876</v>
-      </c>
-      <c r="Q54">
-        <f t="shared" si="1"/>
-        <v>3.3749999999999698</v>
-      </c>
-      <c r="R54">
-        <f t="shared" si="2"/>
-        <v>372.09375</v>
-      </c>
-      <c r="S54">
-        <f t="shared" si="3"/>
-        <v>0.347890415435194</v>
-      </c>
-      <c r="T54">
-        <f t="shared" si="4"/>
-        <v>-9.6152916666667112E-3</v>
-      </c>
-      <c r="U54">
-        <f t="shared" si="5"/>
-        <v>0.3060895833333333</v>
-      </c>
-      <c r="V54">
-        <f t="shared" si="6"/>
-        <v>0.91826874999999997</v>
-      </c>
-      <c r="W54">
-        <f t="shared" si="7"/>
-        <v>993.62909865779818</v>
-      </c>
-      <c r="X54">
-        <f t="shared" si="8"/>
-        <v>-351.00339303279458</v>
-      </c>
-      <c r="Y54">
-        <f t="shared" si="9"/>
-        <v>1215.6367621134882</v>
-      </c>
-      <c r="Z54">
-        <f t="shared" si="10"/>
-        <v>278.23553834321382</v>
-      </c>
-      <c r="AA54">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>0.27403832500000003</v>
       </c>
@@ -5490,54 +3092,10 @@
         <v>14554</v>
       </c>
       <c r="P55">
-        <f t="shared" si="0"/>
-        <v>345.28432848885575</v>
-      </c>
-      <c r="Q55">
-        <f t="shared" si="1"/>
-        <v>-0.90000000000003033</v>
-      </c>
-      <c r="R55">
-        <f t="shared" si="2"/>
-        <v>374.34375</v>
-      </c>
-      <c r="S55">
-        <f t="shared" si="3"/>
-        <v>0.39877865272871521</v>
-      </c>
-      <c r="T55">
-        <f t="shared" si="4"/>
-        <v>8.7072662499999967E-2</v>
-      </c>
-      <c r="U55">
-        <f t="shared" si="5"/>
-        <v>0.30181611250000001</v>
-      </c>
-      <c r="V55">
-        <f t="shared" si="6"/>
-        <v>0.90544833749999998</v>
-      </c>
-      <c r="W55">
-        <f t="shared" si="7"/>
-        <v>865.85459408668225</v>
-      </c>
-      <c r="X55">
-        <f t="shared" si="8"/>
-        <v>-10.336194784442599</v>
-      </c>
-      <c r="Y55">
-        <f t="shared" si="9"/>
-        <v>1240.3040609702373</v>
-      </c>
-      <c r="Z55">
-        <f t="shared" si="10"/>
-        <v>273.27691128484736</v>
-      </c>
-      <c r="AA55">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1.3650078235294101</v>
       </c>
@@ -5584,54 +3142,10 @@
         <v>4091</v>
       </c>
       <c r="P56">
-        <f t="shared" si="0"/>
-        <v>7.3357445967620913</v>
-      </c>
-      <c r="Q56">
-        <f t="shared" si="1"/>
-        <v>4.2352941176469354</v>
-      </c>
-      <c r="R56">
-        <f t="shared" si="2"/>
-        <v>5.2941176470586697</v>
-      </c>
-      <c r="S56">
-        <f t="shared" si="3"/>
-        <v>1.3802418776496905</v>
-      </c>
-      <c r="T56">
-        <f t="shared" si="4"/>
-        <v>0.79688301960784313</v>
-      </c>
-      <c r="U56">
-        <f t="shared" si="5"/>
-        <v>0.79688301960784325</v>
-      </c>
-      <c r="V56">
-        <f t="shared" si="6"/>
-        <v>2.3906490588235298</v>
-      </c>
-      <c r="W56">
-        <f t="shared" si="7"/>
-        <v>5.3148254052786577</v>
-      </c>
-      <c r="X56">
-        <f t="shared" si="8"/>
-        <v>5.3148254052786577</v>
-      </c>
-      <c r="Y56">
-        <f t="shared" si="9"/>
-        <v>6.6435317565983221</v>
-      </c>
-      <c r="Z56">
-        <f t="shared" si="10"/>
-        <v>0.62153930433955018</v>
-      </c>
-      <c r="AA56">
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1.2488694117647099</v>
       </c>
@@ -5678,54 +3192,10 @@
         <v>4438</v>
       </c>
       <c r="P57">
-        <f t="shared" si="0"/>
-        <v>1.8339361491905164</v>
-      </c>
-      <c r="Q57">
-        <f t="shared" si="1"/>
-        <v>1.0588235294117301</v>
-      </c>
-      <c r="R57">
-        <f t="shared" si="2"/>
-        <v>1.3235294117646628</v>
-      </c>
-      <c r="S57">
-        <f t="shared" si="3"/>
-        <v>1.3053519742587349</v>
-      </c>
-      <c r="T57">
-        <f t="shared" si="4"/>
-        <v>0.75364531372548982</v>
-      </c>
-      <c r="U57">
-        <f t="shared" si="5"/>
-        <v>0.75364531372549004</v>
-      </c>
-      <c r="V57">
-        <f t="shared" si="6"/>
-        <v>2.26093594117647</v>
-      </c>
-      <c r="W57">
-        <f t="shared" si="7"/>
-        <v>1.4049361286115543</v>
-      </c>
-      <c r="X57">
-        <f t="shared" si="8"/>
-        <v>1.4049361286115545</v>
-      </c>
-      <c r="Y57">
-        <f t="shared" si="9"/>
-        <v>1.7561701607644429</v>
-      </c>
-      <c r="Z57">
-        <f t="shared" si="10"/>
-        <v>0.73056678687803256</v>
-      </c>
-      <c r="AA57">
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1.18401223529412</v>
       </c>
@@ -5772,54 +3242,10 @@
         <v>4322</v>
       </c>
       <c r="P58">
-        <f t="shared" si="0"/>
-        <v>0.73357445967616708</v>
-      </c>
-      <c r="Q58">
-        <f t="shared" si="1"/>
-        <v>0.42352941176466924</v>
-      </c>
-      <c r="R58">
-        <f t="shared" si="2"/>
-        <v>0.52941176470583662</v>
-      </c>
-      <c r="S58">
-        <f t="shared" si="3"/>
-        <v>1.2792273840046116</v>
-      </c>
-      <c r="T58">
-        <f t="shared" si="4"/>
-        <v>0.73856227450980316</v>
-      </c>
-      <c r="U58">
-        <f t="shared" si="5"/>
-        <v>0.73856227450980327</v>
-      </c>
-      <c r="V58">
-        <f t="shared" si="6"/>
-        <v>2.2156868235294098</v>
-      </c>
-      <c r="W58">
-        <f t="shared" si="7"/>
-        <v>0.57345118533948036</v>
-      </c>
-      <c r="X58">
-        <f t="shared" si="8"/>
-        <v>0.57345118533948025</v>
-      </c>
-      <c r="Y58">
-        <f t="shared" si="9"/>
-        <v>0.71681398167435029</v>
-      </c>
-      <c r="Z58">
-        <f t="shared" si="10"/>
-        <v>0.70884938187803004</v>
-      </c>
-      <c r="AA58">
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1.0307691999999999</v>
       </c>
@@ -5866,54 +3292,10 @@
         <v>1986</v>
       </c>
       <c r="P59">
-        <f t="shared" si="0"/>
-        <v>44.47906473836877</v>
-      </c>
-      <c r="Q59">
-        <f t="shared" si="1"/>
-        <v>91.44</v>
-      </c>
-      <c r="R59">
-        <f t="shared" si="2"/>
-        <v>-9.0000000000000018</v>
-      </c>
-      <c r="S59">
-        <f t="shared" si="3"/>
-        <v>1.1803604092131692</v>
-      </c>
-      <c r="T59">
-        <f t="shared" si="4"/>
-        <v>-0.3418799333333335</v>
-      </c>
-      <c r="U59">
-        <f t="shared" si="5"/>
-        <v>1.1931620666666667</v>
-      </c>
-      <c r="V59">
-        <f t="shared" si="6"/>
-        <v>3.5794861999999998</v>
-      </c>
-      <c r="W59">
-        <f t="shared" si="7"/>
-        <v>37.682613201182008</v>
-      </c>
-      <c r="X59">
-        <f t="shared" si="8"/>
-        <v>-267.46231961747179</v>
-      </c>
-      <c r="Y59">
-        <f t="shared" si="9"/>
-        <v>-7.5429820067472271</v>
-      </c>
-      <c r="Z59">
-        <f t="shared" si="10"/>
-        <v>2.489742801634494</v>
-      </c>
-      <c r="AA59">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1.0717949333333301</v>
       </c>
@@ -5960,54 +3342,10 @@
         <v>1542</v>
       </c>
       <c r="P60">
-        <f t="shared" si="0"/>
-        <v>42.816295963102654</v>
-      </c>
-      <c r="Q60">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="R60">
-        <f t="shared" si="2"/>
-        <v>-9.9</v>
-      </c>
-      <c r="S60">
-        <f t="shared" si="3"/>
-        <v>1.2889225825502943</v>
-      </c>
-      <c r="T60">
-        <f t="shared" si="4"/>
-        <v>-0.18119753333333355</v>
-      </c>
-      <c r="U60">
-        <f t="shared" si="5"/>
-        <v>1.2068384666666667</v>
-      </c>
-      <c r="V60">
-        <f t="shared" si="6"/>
-        <v>3.6205153999999999</v>
-      </c>
-      <c r="W60">
-        <f t="shared" si="7"/>
-        <v>33.218671581023322</v>
-      </c>
-      <c r="X60">
-        <f t="shared" si="8"/>
-        <v>-496.69550321325141</v>
-      </c>
-      <c r="Y60">
-        <f t="shared" si="9"/>
-        <v>-8.2032519458417443</v>
-      </c>
-      <c r="Z60">
-        <f t="shared" si="10"/>
-        <v>3.7525044086264647</v>
-      </c>
-      <c r="AA60">
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1.04273453333333</v>
       </c>
@@ -6054,54 +3392,10 @@
         <v>1770</v>
       </c>
       <c r="P61">
-        <f t="shared" si="0"/>
-        <v>41.984911575469589</v>
-      </c>
-      <c r="Q61">
-        <f t="shared" si="1"/>
-        <v>85.68</v>
-      </c>
-      <c r="R61">
-        <f t="shared" si="2"/>
-        <v>-8.1000000000000014</v>
-      </c>
-      <c r="S61">
-        <f t="shared" si="3"/>
-        <v>1.2247720394400965</v>
-      </c>
-      <c r="T61">
-        <f t="shared" si="4"/>
-        <v>-0.28660953333333355</v>
-      </c>
-      <c r="U61">
-        <f t="shared" si="5"/>
-        <v>1.2039884666666667</v>
-      </c>
-      <c r="V61">
-        <f t="shared" si="6"/>
-        <v>3.6119653999999999</v>
-      </c>
-      <c r="W61">
-        <f t="shared" si="7"/>
-        <v>34.279776336715649</v>
-      </c>
-      <c r="X61">
-        <f t="shared" si="8"/>
-        <v>-298.94330102534366</v>
-      </c>
-      <c r="Y61">
-        <f t="shared" si="9"/>
-        <v>-6.7276391961008271</v>
-      </c>
-      <c r="Z61">
-        <f t="shared" si="10"/>
-        <v>3.4884055090893176</v>
-      </c>
-      <c r="AA61">
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>0.93514352941176504</v>
       </c>
@@ -6148,54 +3442,10 @@
         <v>7451</v>
       </c>
       <c r="P62">
-        <f t="shared" si="0"/>
-        <v>81.793552253899634</v>
-      </c>
-      <c r="Q62">
-        <f t="shared" si="1"/>
-        <v>110.75294117647053</v>
-      </c>
-      <c r="R62">
-        <f t="shared" si="2"/>
-        <v>19.323529411764678</v>
-      </c>
-      <c r="S62">
-        <f t="shared" si="3"/>
-        <v>1.2461371985998422</v>
-      </c>
-      <c r="T62">
-        <f t="shared" si="4"/>
-        <v>-0.23579647058823516</v>
-      </c>
-      <c r="U62">
-        <f t="shared" si="5"/>
-        <v>1.1970847058823548</v>
-      </c>
-      <c r="V62">
-        <f t="shared" si="6"/>
-        <v>3.5912541176470647</v>
-      </c>
-      <c r="W62">
-        <f t="shared" si="7"/>
-        <v>65.637678054874485</v>
-      </c>
-      <c r="X62">
-        <f t="shared" si="8"/>
-        <v>-469.69719648550347</v>
-      </c>
-      <c r="Y62">
-        <f t="shared" si="9"/>
-        <v>16.142157122892627</v>
-      </c>
-      <c r="Z62">
-        <f t="shared" si="10"/>
-        <v>-0.46485481394996786</v>
-      </c>
-      <c r="AA62">
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1.05882347058824</v>
       </c>
@@ -6242,54 +3492,10 @@
         <v>7617</v>
       </c>
       <c r="P63">
-        <f t="shared" si="0"/>
-        <v>86.194999011957037</v>
-      </c>
-      <c r="Q63">
-        <f t="shared" si="1"/>
-        <v>114.56470588235291</v>
-      </c>
-      <c r="R63">
-        <f t="shared" si="2"/>
-        <v>21.705882352941149</v>
-      </c>
-      <c r="S63">
-        <f t="shared" si="3"/>
-        <v>1.200852967968417</v>
-      </c>
-      <c r="T63">
-        <f t="shared" si="4"/>
-        <v>-0.34741074509804032</v>
-      </c>
-      <c r="U63">
-        <f t="shared" si="5"/>
-        <v>1.2136745490196101</v>
-      </c>
-      <c r="V63">
-        <f t="shared" si="6"/>
-        <v>3.6410236470588302</v>
-      </c>
-      <c r="W63">
-        <f t="shared" si="7"/>
-        <v>71.778145460872111</v>
-      </c>
-      <c r="X63">
-        <f t="shared" si="8"/>
-        <v>-329.76730713962928</v>
-      </c>
-      <c r="Y63">
-        <f t="shared" si="9"/>
-        <v>17.884433986421538</v>
-      </c>
-      <c r="Z63">
-        <f t="shared" si="10"/>
-        <v>-1.5155724952720908</v>
-      </c>
-      <c r="AA63">
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1.0316747647058799</v>
       </c>
@@ -6336,54 +3542,10 @@
         <v>7952</v>
       </c>
       <c r="P64">
-        <f t="shared" si="0"/>
-        <v>83.994275632928321</v>
-      </c>
-      <c r="Q64">
-        <f t="shared" si="1"/>
-        <v>114.56470588235291</v>
-      </c>
-      <c r="R64">
-        <f t="shared" si="2"/>
-        <v>19.32352941176465</v>
-      </c>
-      <c r="S64">
-        <f t="shared" si="3"/>
-        <v>1.1581837265150516</v>
-      </c>
-      <c r="T64">
-        <f t="shared" si="4"/>
-        <v>-0.33081996078431786</v>
-      </c>
-      <c r="U64">
-        <f t="shared" si="5"/>
-        <v>1.1684265098039222</v>
-      </c>
-      <c r="V64">
-        <f t="shared" si="6"/>
-        <v>3.5052795294117667</v>
-      </c>
-      <c r="W64">
-        <f t="shared" si="7"/>
-        <v>72.522410486344143</v>
-      </c>
-      <c r="X64">
-        <f t="shared" si="8"/>
-        <v>-346.30530035352001</v>
-      </c>
-      <c r="Y64">
-        <f t="shared" si="9"/>
-        <v>16.538078560890749</v>
-      </c>
-      <c r="Z64">
-        <f t="shared" si="10"/>
-        <v>-1.0829043222062751</v>
-      </c>
-      <c r="AA64">
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>0.84935893750000002</v>
       </c>
@@ -6430,54 +3592,10 @@
         <v>1671</v>
       </c>
       <c r="P65">
-        <f t="shared" si="0"/>
-        <v>47.544794667765686</v>
-      </c>
-      <c r="Q65">
-        <f t="shared" si="1"/>
-        <v>0.44999999999999624</v>
-      </c>
-      <c r="R65">
-        <f t="shared" si="2"/>
-        <v>51.1875</v>
-      </c>
-      <c r="S65">
-        <f t="shared" si="3"/>
-        <v>1.1176911592548746</v>
-      </c>
-      <c r="T65">
-        <f t="shared" si="4"/>
-        <v>-5.3419458333333315E-2</v>
-      </c>
-      <c r="U65">
-        <f t="shared" si="5"/>
-        <v>0.99465866666666669</v>
-      </c>
-      <c r="V65">
-        <f t="shared" si="6"/>
-        <v>2.9839760000000002</v>
-      </c>
-      <c r="W65">
-        <f t="shared" si="7"/>
-        <v>42.538400947415681</v>
-      </c>
-      <c r="X65">
-        <f t="shared" si="8"/>
-        <v>-8.4238967230261075</v>
-      </c>
-      <c r="Y65">
-        <f t="shared" si="9"/>
-        <v>51.462377713493673</v>
-      </c>
-      <c r="Z65">
-        <f t="shared" si="10"/>
-        <v>7.8356025651680845</v>
-      </c>
-      <c r="AA65">
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>0.91506399999999999</v>
       </c>
@@ -6524,54 +3642,10 @@
         <v>1844</v>
       </c>
       <c r="P66">
-        <f t="shared" si="0"/>
-        <v>47.544794667765686</v>
-      </c>
-      <c r="Q66">
-        <f t="shared" si="1"/>
-        <v>2.6999999999999962</v>
-      </c>
-      <c r="R66">
-        <f t="shared" si="2"/>
-        <v>49.78125</v>
-      </c>
-      <c r="S66">
-        <f t="shared" si="3"/>
-        <v>1.1047380533748625</v>
-      </c>
-      <c r="T66">
-        <f t="shared" si="4"/>
-        <v>-0.12927264583333345</v>
-      </c>
-      <c r="U66">
-        <f t="shared" si="5"/>
-        <v>1.0213675416666668</v>
-      </c>
-      <c r="V66">
-        <f t="shared" si="6"/>
-        <v>3.0641026250000003</v>
-      </c>
-      <c r="W66">
-        <f t="shared" si="7"/>
-        <v>43.037165708668375</v>
-      </c>
-      <c r="X66">
-        <f t="shared" si="8"/>
-        <v>-20.886089107211504</v>
-      </c>
-      <c r="Y66">
-        <f t="shared" si="9"/>
-        <v>48.739800286552082</v>
-      </c>
-      <c r="Z66">
-        <f t="shared" si="10"/>
-        <v>10.037400428126977</v>
-      </c>
-      <c r="AA66">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>0.91185831250000005</v>
       </c>
@@ -6618,54 +3692,10 @@
         <v>1953</v>
       </c>
       <c r="P67">
-        <f t="shared" ref="P67:P130" si="11">(4*(L67+J67)*COS(RADIANS(30)))/15</f>
-        <v>52.221331848201658</v>
-      </c>
-      <c r="Q67">
-        <f t="shared" ref="Q67:Q130" si="12">(4*(L67+J67)*SIN(RADIANS(30))-4*K67)/15</f>
-        <v>6.7499999999999964</v>
-      </c>
-      <c r="R67">
-        <f t="shared" ref="R67:R130" si="13">(J67+K67+L67)/6</f>
-        <v>52.3125</v>
-      </c>
-      <c r="S67">
-        <f t="shared" ref="S67:S130" si="14">(2*(A67+C67)*COS(RADIANS(30)))/3</f>
-        <v>1.0492225773970159</v>
-      </c>
-      <c r="T67">
-        <f t="shared" ref="T67:T130" si="15">(2*(A67+C67)*SIN(RADIANS(30))-2*B67)/3</f>
-        <v>-0.12179489583333332</v>
-      </c>
-      <c r="U67">
-        <f t="shared" ref="U67:U130" si="16">(A67+B67+C67)/3</f>
-        <v>0.96955085416666664</v>
-      </c>
-      <c r="V67">
-        <f t="shared" ref="V67:V130" si="17">A67+B67+C67</f>
-        <v>2.9086525624999999</v>
-      </c>
-      <c r="W67">
-        <f t="shared" ref="W67:W130" si="18">P67/S67</f>
-        <v>49.771452667131847</v>
-      </c>
-      <c r="X67">
-        <f t="shared" ref="X67:X130" si="19">Q67/T67</f>
-        <v>-55.421041693215436</v>
-      </c>
-      <c r="Y67">
-        <f t="shared" ref="Y67:Y130" si="20">R67/U67</f>
-        <v>53.95539571254654</v>
-      </c>
-      <c r="Z67">
-        <f t="shared" ref="Z67:Z130" si="21">F67/U67</f>
-        <v>10.53322778904433</v>
-      </c>
-      <c r="AA67">
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>0.92649599999999999</v>
       </c>
@@ -6712,54 +3742,10 @@
         <v>4753</v>
       </c>
       <c r="P68">
-        <f t="shared" si="11"/>
-        <v>139.67257712235426</v>
-      </c>
-      <c r="Q68">
-        <f t="shared" si="12"/>
-        <v>7.1999999999999851</v>
-      </c>
-      <c r="R68">
-        <f t="shared" si="13"/>
-        <v>146.69999999999999</v>
-      </c>
-      <c r="S68">
-        <f t="shared" si="14"/>
-        <v>1.0520608241034737</v>
-      </c>
-      <c r="T68">
-        <f t="shared" si="15"/>
-        <v>-0.19145364444444671</v>
-      </c>
-      <c r="U68">
-        <f t="shared" si="16"/>
-        <v>1.0068382222222232</v>
-      </c>
-      <c r="V68">
-        <f t="shared" si="17"/>
-        <v>3.0205146666666698</v>
-      </c>
-      <c r="W68">
-        <f t="shared" si="18"/>
-        <v>132.76093351482595</v>
-      </c>
-      <c r="X68">
-        <f t="shared" si="19"/>
-        <v>-37.607014590360428</v>
-      </c>
-      <c r="Y68">
-        <f t="shared" si="20"/>
-        <v>145.70364608945215</v>
-      </c>
-      <c r="Z68">
-        <f t="shared" si="21"/>
-        <v>25.130816558414335</v>
-      </c>
-      <c r="AA68">
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>0.818803533333333</v>
       </c>
@@ -6806,54 +3792,10 @@
         <v>5042</v>
       </c>
       <c r="P69">
-        <f t="shared" si="11"/>
-        <v>140.50396150998733</v>
-      </c>
-      <c r="Q69">
-        <f t="shared" si="12"/>
-        <v>5.2800000000000029</v>
-      </c>
-      <c r="R69">
-        <f t="shared" si="13"/>
-        <v>148.79999999999998</v>
-      </c>
-      <c r="S69">
-        <f t="shared" si="14"/>
-        <v>0.93757753885562922</v>
-      </c>
-      <c r="T69">
-        <f t="shared" si="15"/>
-        <v>-0.19259224444444242</v>
-      </c>
-      <c r="U69">
-        <f t="shared" si="16"/>
-        <v>0.9082620888888876</v>
-      </c>
-      <c r="V69">
-        <f t="shared" si="17"/>
-        <v>2.7247862666666629</v>
-      </c>
-      <c r="W69">
-        <f t="shared" si="18"/>
-        <v>149.85849776380203</v>
-      </c>
-      <c r="X69">
-        <f t="shared" si="19"/>
-        <v>-27.415434174054386</v>
-      </c>
-      <c r="Y69">
-        <f t="shared" si="20"/>
-        <v>163.8293635948549</v>
-      </c>
-      <c r="Z69">
-        <f t="shared" si="21"/>
-        <v>31.853507580313217</v>
-      </c>
-      <c r="AA69">
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>0.7760686</v>
       </c>
@@ -6900,54 +3842,10 @@
         <v>5306</v>
       </c>
       <c r="P70">
-        <f t="shared" si="11"/>
-        <v>139.67257712235426</v>
-      </c>
-      <c r="Q70">
-        <f t="shared" si="12"/>
-        <v>3.3599999999999759</v>
-      </c>
-      <c r="R70">
-        <f t="shared" si="13"/>
-        <v>149.1</v>
-      </c>
-      <c r="S70">
-        <f t="shared" si="14"/>
-        <v>0.90599605574075948</v>
-      </c>
-      <c r="T70">
-        <f t="shared" si="15"/>
-        <v>-0.17321893333333338</v>
-      </c>
-      <c r="U70">
-        <f t="shared" si="16"/>
-        <v>0.87122506666666666</v>
-      </c>
-      <c r="V70">
-        <f t="shared" si="17"/>
-        <v>2.6136751999999999</v>
-      </c>
-      <c r="W70">
-        <f t="shared" si="18"/>
-        <v>154.16466356264135</v>
-      </c>
-      <c r="X70">
-        <f t="shared" si="19"/>
-        <v>-19.397417680284228</v>
-      </c>
-      <c r="Y70">
-        <f t="shared" si="20"/>
-        <v>171.13832659850007</v>
-      </c>
-      <c r="Z70">
-        <f t="shared" si="21"/>
-        <v>33.957547594284129</v>
-      </c>
-      <c r="AA70">
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>0.93956057142857097</v>
       </c>
@@ -6994,54 +3892,10 @@
         <v>10755</v>
       </c>
       <c r="P71">
-        <f t="shared" si="11"/>
-        <v>322.90375769676933</v>
-      </c>
-      <c r="Q71">
-        <f t="shared" si="12"/>
-        <v>6.4285714285714368</v>
-      </c>
-      <c r="R71">
-        <f t="shared" si="13"/>
-        <v>345.53571428571439</v>
-      </c>
-      <c r="S71">
-        <f t="shared" si="14"/>
-        <v>1.0426144581869614</v>
-      </c>
-      <c r="T71">
-        <f t="shared" si="15"/>
-        <v>-0.16361388095238208</v>
-      </c>
-      <c r="U71">
-        <f t="shared" si="16"/>
-        <v>0.98473754761904797</v>
-      </c>
-      <c r="V71">
-        <f t="shared" si="17"/>
-        <v>2.954212642857144</v>
-      </c>
-      <c r="W71">
-        <f t="shared" si="18"/>
-        <v>309.70581230791475</v>
-      </c>
-      <c r="X71">
-        <f t="shared" si="19"/>
-        <v>-39.291112655914553</v>
-      </c>
-      <c r="Y71">
-        <f t="shared" si="20"/>
-        <v>350.89117412164228</v>
-      </c>
-      <c r="Z71">
-        <f t="shared" si="21"/>
-        <v>61.159152945199772</v>
-      </c>
-      <c r="AA71">
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>0.89926757142857106</v>
       </c>
@@ -7088,54 +3942,10 @@
         <v>10441</v>
       </c>
       <c r="P72">
-        <f t="shared" si="11"/>
-        <v>323.79452668351911</v>
-      </c>
-      <c r="Q72">
-        <f t="shared" si="12"/>
-        <v>10.542857142857155</v>
-      </c>
-      <c r="R72">
-        <f t="shared" si="13"/>
-        <v>343.9285714285715</v>
-      </c>
-      <c r="S72">
-        <f t="shared" si="14"/>
-        <v>1.0056044501631842</v>
-      </c>
-      <c r="T72">
-        <f t="shared" si="15"/>
-        <v>-0.20329590476190673</v>
-      </c>
-      <c r="U72">
-        <f t="shared" si="16"/>
-        <v>0.97252695238095332</v>
-      </c>
-      <c r="V72">
-        <f t="shared" si="17"/>
-        <v>2.9175808571428599</v>
-      </c>
-      <c r="W72">
-        <f t="shared" si="18"/>
-        <v>321.98995005538751</v>
-      </c>
-      <c r="X72">
-        <f t="shared" si="19"/>
-        <v>-51.859663160478277</v>
-      </c>
-      <c r="Y72">
-        <f t="shared" si="20"/>
-        <v>353.64425693967763</v>
-      </c>
-      <c r="Z72">
-        <f t="shared" si="21"/>
-        <v>68.134725706708281</v>
-      </c>
-      <c r="AA72">
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>0.94688614285714301</v>
       </c>
@@ -7182,54 +3992,10 @@
         <v>10849</v>
       </c>
       <c r="P73">
-        <f t="shared" si="11"/>
-        <v>321.56760421664461</v>
-      </c>
-      <c r="Q73">
-        <f t="shared" si="12"/>
-        <v>6.1714285714283807</v>
-      </c>
-      <c r="R73">
-        <f t="shared" si="13"/>
-        <v>344.25</v>
-      </c>
-      <c r="S73">
-        <f t="shared" si="14"/>
-        <v>1.0500164185524123</v>
-      </c>
-      <c r="T73">
-        <f t="shared" si="15"/>
-        <v>-0.20695988095237813</v>
-      </c>
-      <c r="U73">
-        <f t="shared" si="16"/>
-        <v>1.0128208333333319</v>
-      </c>
-      <c r="V73">
-        <f t="shared" si="17"/>
-        <v>3.0384624999999961</v>
-      </c>
-      <c r="W73">
-        <f t="shared" si="18"/>
-        <v>306.25007241312323</v>
-      </c>
-      <c r="X73">
-        <f t="shared" si="19"/>
-        <v>-29.819443957104124</v>
-      </c>
-      <c r="Y73">
-        <f t="shared" si="20"/>
-        <v>339.89229750243794</v>
-      </c>
-      <c r="Z73">
-        <f t="shared" si="21"/>
-        <v>64.524880123229735</v>
-      </c>
-      <c r="AA73">
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>0.7076926</v>
       </c>
@@ -7276,54 +4042,10 @@
         <v>4378</v>
       </c>
       <c r="P74">
-        <f t="shared" si="11"/>
-        <v>0.83138438763305322</v>
-      </c>
-      <c r="Q74">
-        <f t="shared" si="12"/>
-        <v>0.47999999999999537</v>
-      </c>
-      <c r="R74">
-        <f t="shared" si="13"/>
-        <v>0.59999999999999432</v>
-      </c>
-      <c r="S74">
-        <f t="shared" si="14"/>
-        <v>0.84776754830171175</v>
-      </c>
-      <c r="T74">
-        <f t="shared" si="15"/>
-        <v>0.4826212222222222</v>
-      </c>
-      <c r="U74">
-        <f t="shared" si="16"/>
-        <v>0.49287762222222237</v>
-      </c>
-      <c r="V74">
-        <f t="shared" si="17"/>
-        <v>1.478632866666667</v>
-      </c>
-      <c r="W74">
-        <f t="shared" si="18"/>
-        <v>0.98067493772145675</v>
-      </c>
-      <c r="X74">
-        <f t="shared" si="19"/>
-        <v>0.99456877961114631</v>
-      </c>
-      <c r="Y74">
-        <f t="shared" si="20"/>
-        <v>1.2173407209984348</v>
-      </c>
-      <c r="Z74">
-        <f t="shared" si="21"/>
-        <v>1.7597336422433087</v>
-      </c>
-      <c r="AA74">
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>0.78803440000000002</v>
       </c>
@@ -7370,54 +4092,10 @@
         <v>4311</v>
       </c>
       <c r="P75">
-        <f t="shared" si="11"/>
-        <v>1.6627687752661198</v>
-      </c>
-      <c r="Q75">
-        <f t="shared" si="12"/>
-        <v>0.95999999999999841</v>
-      </c>
-      <c r="R75">
-        <f t="shared" si="13"/>
-        <v>1.1999999999999982</v>
-      </c>
-      <c r="S75">
-        <f t="shared" si="14"/>
-        <v>0.89612683023923212</v>
-      </c>
-      <c r="T75">
-        <f t="shared" si="15"/>
-        <v>0.51054146666666655</v>
-      </c>
-      <c r="U75">
-        <f t="shared" si="16"/>
-        <v>0.52079786666666672</v>
-      </c>
-      <c r="V75">
-        <f t="shared" si="17"/>
-        <v>1.5623936</v>
-      </c>
-      <c r="W75">
-        <f t="shared" si="18"/>
-        <v>1.8555060725301831</v>
-      </c>
-      <c r="X75">
-        <f t="shared" si="19"/>
-        <v>1.8803565678373861</v>
-      </c>
-      <c r="Y75">
-        <f t="shared" si="20"/>
-        <v>2.3041569038685221</v>
-      </c>
-      <c r="Z75">
-        <f t="shared" si="21"/>
-        <v>1.8241242155625828</v>
-      </c>
-      <c r="AA75">
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>0.7623934</v>
       </c>
@@ -7464,54 +4142,10 @@
         <v>4133</v>
       </c>
       <c r="P76">
-        <f t="shared" si="11"/>
-        <v>0.41569219381653322</v>
-      </c>
-      <c r="Q76">
-        <f t="shared" si="12"/>
-        <v>0.72000000000000142</v>
-      </c>
-      <c r="R76">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="S76">
-        <f t="shared" si="14"/>
-        <v>0.86947992138510788</v>
-      </c>
-      <c r="T76">
-        <f t="shared" si="15"/>
-        <v>0.49857566666666653</v>
-      </c>
-      <c r="U76">
-        <f t="shared" si="16"/>
-        <v>0.50370386666666667</v>
-      </c>
-      <c r="V76">
-        <f t="shared" si="17"/>
-        <v>1.5111116</v>
-      </c>
-      <c r="W76">
-        <f t="shared" si="18"/>
-        <v>0.47809291921810332</v>
-      </c>
-      <c r="X76">
-        <f t="shared" si="19"/>
-        <v>1.4441137988416368</v>
-      </c>
-      <c r="Y76">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Z76">
-        <f t="shared" si="21"/>
-        <v>1.3460289762847431</v>
-      </c>
-      <c r="AA76">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>0.46495700000000001</v>
       </c>
@@ -7558,54 +4192,10 @@
         <v>2490</v>
       </c>
       <c r="P77">
-        <f t="shared" si="11"/>
-        <v>66.510751010644896</v>
-      </c>
-      <c r="Q77">
-        <f t="shared" si="12"/>
-        <v>118.07999999999998</v>
-      </c>
-      <c r="R77">
-        <f t="shared" si="13"/>
-        <v>-1.8000000000000018</v>
-      </c>
-      <c r="S77">
-        <f t="shared" si="14"/>
-        <v>0.52504302762136879</v>
-      </c>
-      <c r="T77">
-        <f t="shared" si="15"/>
-        <v>-0.30883195555555537</v>
-      </c>
-      <c r="U77">
-        <f t="shared" si="16"/>
-        <v>0.60911657777777772</v>
-      </c>
-      <c r="V77">
-        <f t="shared" si="17"/>
-        <v>1.8273497333333331</v>
-      </c>
-      <c r="W77">
-        <f t="shared" si="18"/>
-        <v>126.67676268735954</v>
-      </c>
-      <c r="X77">
-        <f t="shared" si="19"/>
-        <v>-382.34385359373448</v>
-      </c>
-      <c r="Y77">
-        <f t="shared" si="20"/>
-        <v>-2.9550993449675746</v>
-      </c>
-      <c r="Z77">
-        <f t="shared" si="21"/>
-        <v>-1.2772596167141301</v>
-      </c>
-      <c r="AA77">
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>0.42905959999999999</v>
       </c>
@@ -7652,54 +4242,10 @@
         <v>2485</v>
       </c>
       <c r="P78">
-        <f t="shared" si="11"/>
-        <v>69.004904173544077</v>
-      </c>
-      <c r="Q78">
-        <f t="shared" si="12"/>
-        <v>124.32</v>
-      </c>
-      <c r="R78">
-        <f t="shared" si="13"/>
-        <v>-3</v>
-      </c>
-      <c r="S78">
-        <f t="shared" si="14"/>
-        <v>0.48852689326571713</v>
-      </c>
-      <c r="T78">
-        <f t="shared" si="15"/>
-        <v>-0.2022795333333334</v>
-      </c>
-      <c r="U78">
-        <f t="shared" si="16"/>
-        <v>0.52421646666666666</v>
-      </c>
-      <c r="V78">
-        <f t="shared" si="17"/>
-        <v>1.5726494</v>
-      </c>
-      <c r="W78">
-        <f t="shared" si="18"/>
-        <v>141.25098356870043</v>
-      </c>
-      <c r="X78">
-        <f t="shared" si="19"/>
-        <v>-614.59505047964956</v>
-      </c>
-      <c r="Y78">
-        <f t="shared" si="20"/>
-        <v>-5.7228267152233681</v>
-      </c>
-      <c r="Z78">
-        <f t="shared" si="21"/>
-        <v>-1.3836523385313981</v>
-      </c>
-      <c r="AA78">
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>0.47350419999999999</v>
       </c>
@@ -7746,54 +4292,10 @@
         <v>2639</v>
       </c>
       <c r="P79">
-        <f t="shared" si="11"/>
-        <v>67.342135398277961</v>
-      </c>
-      <c r="Q79">
-        <f t="shared" si="12"/>
-        <v>119.51999999999998</v>
-      </c>
-      <c r="R79">
-        <f t="shared" si="13"/>
-        <v>-1.7999999999999972</v>
-      </c>
-      <c r="S79">
-        <f t="shared" si="14"/>
-        <v>0.53984709681376764</v>
-      </c>
-      <c r="T79">
-        <f t="shared" si="15"/>
-        <v>-0.24330468888888868</v>
-      </c>
-      <c r="U79">
-        <f t="shared" si="16"/>
-        <v>0.58917364444444431</v>
-      </c>
-      <c r="V79">
-        <f t="shared" si="17"/>
-        <v>1.767520933333333</v>
-      </c>
-      <c r="W79">
-        <f t="shared" si="18"/>
-        <v>124.74297962467165</v>
-      </c>
-      <c r="X79">
-        <f t="shared" si="19"/>
-        <v>-491.23590895768496</v>
-      </c>
-      <c r="Y79">
-        <f t="shared" si="20"/>
-        <v>-3.055126475824101</v>
-      </c>
-      <c r="Z79">
-        <f t="shared" si="21"/>
-        <v>-2.2630679640417389E-3</v>
-      </c>
-      <c r="AA79">
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>0.33974325</v>
       </c>
@@ -7840,54 +4342,10 @@
         <v>7493</v>
       </c>
       <c r="P80">
-        <f t="shared" si="11"/>
-        <v>77.552574908896489</v>
-      </c>
-      <c r="Q80">
-        <f t="shared" si="12"/>
-        <v>129.375</v>
-      </c>
-      <c r="R80">
-        <f t="shared" si="13"/>
-        <v>3.09375</v>
-      </c>
-      <c r="S80">
-        <f t="shared" si="14"/>
-        <v>0.65322008457018543</v>
-      </c>
-      <c r="T80">
-        <f t="shared" si="15"/>
-        <v>-0.15598300000000007</v>
-      </c>
-      <c r="U80">
-        <f t="shared" si="16"/>
-        <v>0.64369668749999998</v>
-      </c>
-      <c r="V80">
-        <f t="shared" si="17"/>
-        <v>1.9310900625</v>
-      </c>
-      <c r="W80">
-        <f t="shared" si="18"/>
-        <v>118.7235003037691</v>
-      </c>
-      <c r="X80">
-        <f t="shared" si="19"/>
-        <v>-829.41730829641654</v>
-      </c>
-      <c r="Y80">
-        <f t="shared" si="20"/>
-        <v>4.8062232726652026</v>
-      </c>
-      <c r="Z80">
-        <f t="shared" si="21"/>
-        <v>1.4700246534980035</v>
-      </c>
-      <c r="AA80">
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>0.24999974999999999</v>
       </c>
@@ -7934,54 +4392,10 @@
         <v>7786</v>
       </c>
       <c r="P81">
-        <f t="shared" si="11"/>
-        <v>77.162863477193483</v>
-      </c>
-      <c r="Q81">
-        <f t="shared" si="12"/>
-        <v>127.8</v>
-      </c>
-      <c r="R81">
-        <f t="shared" si="13"/>
-        <v>3.65625</v>
-      </c>
-      <c r="S81">
-        <f t="shared" si="14"/>
-        <v>0.57920060463359491</v>
-      </c>
-      <c r="T81">
-        <f t="shared" si="15"/>
-        <v>-0.14209425000000006</v>
-      </c>
-      <c r="U81">
-        <f t="shared" si="16"/>
-        <v>0.57264956249999999</v>
-      </c>
-      <c r="V81">
-        <f t="shared" si="17"/>
-        <v>1.7179486874999998</v>
-      </c>
-      <c r="W81">
-        <f t="shared" si="18"/>
-        <v>133.22303681987191</v>
-      </c>
-      <c r="X81">
-        <f t="shared" si="19"/>
-        <v>-899.40303706870577</v>
-      </c>
-      <c r="Y81">
-        <f t="shared" si="20"/>
-        <v>6.3847948892827455</v>
-      </c>
-      <c r="Z81">
-        <f t="shared" si="21"/>
-        <v>2.346548549052633</v>
-      </c>
-      <c r="AA81">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>0.28846125</v>
       </c>
@@ -8028,54 +4442,10 @@
         <v>7840</v>
       </c>
       <c r="P82">
-        <f t="shared" si="11"/>
-        <v>78.721709204005478</v>
-      </c>
-      <c r="Q82">
-        <f t="shared" si="12"/>
-        <v>131.4</v>
-      </c>
-      <c r="R82">
-        <f t="shared" si="13"/>
-        <v>3.09375</v>
-      </c>
-      <c r="S82">
-        <f t="shared" si="14"/>
-        <v>0.58382694842500327</v>
-      </c>
-      <c r="T82">
-        <f t="shared" si="15"/>
-        <v>-9.3483104166666678E-2</v>
-      </c>
-      <c r="U82">
-        <f t="shared" si="16"/>
-        <v>0.55235052083333336</v>
-      </c>
-      <c r="V82">
-        <f t="shared" si="17"/>
-        <v>1.6570515625</v>
-      </c>
-      <c r="W82">
-        <f t="shared" si="18"/>
-        <v>134.83740244669067</v>
-      </c>
-      <c r="X82">
-        <f t="shared" si="19"/>
-        <v>-1405.6015915531973</v>
-      </c>
-      <c r="Y82">
-        <f t="shared" si="20"/>
-        <v>5.6010628818317167</v>
-      </c>
-      <c r="Z82">
-        <f t="shared" si="21"/>
-        <v>2.2981330733333771</v>
-      </c>
-      <c r="AA82">
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>0.29401687333333298</v>
       </c>
@@ -8122,54 +4492,10 @@
         <v>2423</v>
       </c>
       <c r="P83">
-        <f t="shared" si="11"/>
-        <v>71.914749530259783</v>
-      </c>
-      <c r="Q83">
-        <f t="shared" si="12"/>
-        <v>1.1999999999999924</v>
-      </c>
-      <c r="R83">
-        <f t="shared" si="13"/>
-        <v>77.100000000000009</v>
-      </c>
-      <c r="S83">
-        <f t="shared" si="14"/>
-        <v>0.40661224847200489</v>
-      </c>
-      <c r="T83">
-        <f t="shared" si="15"/>
-        <v>-5.9259331111111035E-2</v>
-      </c>
-      <c r="U83">
-        <f t="shared" si="16"/>
-        <v>0.38176620222222196</v>
-      </c>
-      <c r="V83">
-        <f t="shared" si="17"/>
-        <v>1.1452986066666659</v>
-      </c>
-      <c r="W83">
-        <f t="shared" si="18"/>
-        <v>176.86321501751584</v>
-      </c>
-      <c r="X83">
-        <f t="shared" si="19"/>
-        <v>-20.249975446904667</v>
-      </c>
-      <c r="Y83">
-        <f t="shared" si="20"/>
-        <v>201.95606512888989</v>
-      </c>
-      <c r="Z83">
-        <f t="shared" si="21"/>
-        <v>43.688169800212513</v>
-      </c>
-      <c r="AA83">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>0.31111080000000002</v>
       </c>
@@ -8216,54 +4542,10 @@
         <v>2545</v>
       </c>
       <c r="P84">
-        <f t="shared" si="11"/>
-        <v>73.161826111709388</v>
-      </c>
-      <c r="Q84">
-        <f t="shared" si="12"/>
-        <v>-7.5791225147744019E-15</v>
-      </c>
-      <c r="R84">
-        <f t="shared" si="13"/>
-        <v>79.2</v>
-      </c>
-      <c r="S84">
-        <f t="shared" si="14"/>
-        <v>0.385886755599742</v>
-      </c>
-      <c r="T84">
-        <f t="shared" si="15"/>
-        <v>-5.8689555555555696E-2</v>
-      </c>
-      <c r="U84">
-        <f t="shared" si="16"/>
-        <v>0.36353251111111134</v>
-      </c>
-      <c r="V84">
-        <f t="shared" si="17"/>
-        <v>1.090597533333334</v>
-      </c>
-      <c r="W84">
-        <f t="shared" si="18"/>
-        <v>189.59403257570187</v>
-      </c>
-      <c r="X84">
-        <f t="shared" si="19"/>
-        <v>1.2913920446373092E-13</v>
-      </c>
-      <c r="Y84">
-        <f t="shared" si="20"/>
-        <v>217.86222023975466</v>
-      </c>
-      <c r="Z84">
-        <f t="shared" si="21"/>
-        <v>52.886604120322261</v>
-      </c>
-      <c r="AA84">
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>0.45811960000000002</v>
       </c>
@@ -8310,54 +4592,10 @@
         <v>2902</v>
       </c>
       <c r="P85">
-        <f t="shared" si="11"/>
-        <v>71.914749530259783</v>
-      </c>
-      <c r="Q85">
-        <f t="shared" si="12"/>
-        <v>-1.6800000000000106</v>
-      </c>
-      <c r="R85">
-        <f t="shared" si="13"/>
-        <v>78.899999999999991</v>
-      </c>
-      <c r="S85">
-        <f t="shared" si="14"/>
-        <v>0.3888477157002897</v>
-      </c>
-      <c r="T85">
-        <f t="shared" si="15"/>
-        <v>-1.0256355555555374E-2</v>
-      </c>
-      <c r="U85">
-        <f t="shared" si="16"/>
-        <v>0.34188017777777763</v>
-      </c>
-      <c r="V85">
-        <f t="shared" si="17"/>
-        <v>1.0256405333333329</v>
-      </c>
-      <c r="W85">
-        <f t="shared" si="18"/>
-        <v>184.94322231196844</v>
-      </c>
-      <c r="X85">
-        <f t="shared" si="19"/>
-        <v>163.80087360466317</v>
-      </c>
-      <c r="Y85">
-        <f t="shared" si="20"/>
-        <v>230.78261077565324</v>
-      </c>
-      <c r="Z85">
-        <f t="shared" si="21"/>
-        <v>52.152775033332034</v>
-      </c>
-      <c r="AA85">
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>0.28376053333333301</v>
       </c>
@@ -8404,54 +4642,10 @@
         <v>4795</v>
       </c>
       <c r="P86">
-        <f t="shared" si="11"/>
-        <v>159.21011023173122</v>
-      </c>
-      <c r="Q86">
-        <f t="shared" si="12"/>
-        <v>3.6</v>
-      </c>
-      <c r="R86">
-        <f t="shared" si="13"/>
-        <v>170.1</v>
-      </c>
-      <c r="S86">
-        <f t="shared" si="14"/>
-        <v>0.47964489823448581</v>
-      </c>
-      <c r="T86">
-        <f t="shared" si="15"/>
-        <v>-1.8233377777777709E-2</v>
-      </c>
-      <c r="U86">
-        <f t="shared" si="16"/>
-        <v>0.42450135555555529</v>
-      </c>
-      <c r="V86">
-        <f t="shared" si="17"/>
-        <v>1.2735040666666659</v>
-      </c>
-      <c r="W86">
-        <f t="shared" si="18"/>
-        <v>331.93329235391468</v>
-      </c>
-      <c r="X86">
-        <f t="shared" si="19"/>
-        <v>-197.44010374136883</v>
-      </c>
-      <c r="Y86">
-        <f t="shared" si="20"/>
-        <v>400.70543420853386</v>
-      </c>
-      <c r="Z86">
-        <f t="shared" si="21"/>
-        <v>83.457919595178936</v>
-      </c>
-      <c r="AA86">
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>0.44273499999999999</v>
       </c>
@@ -8498,54 +4692,10 @@
         <v>5905</v>
       </c>
       <c r="P87">
-        <f t="shared" si="11"/>
-        <v>157.54734145646509</v>
-      </c>
-      <c r="Q87">
-        <f t="shared" si="12"/>
-        <v>-0.24000000000000909</v>
-      </c>
-      <c r="R87">
-        <f t="shared" si="13"/>
-        <v>170.69999999999996</v>
-      </c>
-      <c r="S87">
-        <f t="shared" si="14"/>
-        <v>0.39279541359890408</v>
-      </c>
-      <c r="T87">
-        <f t="shared" si="15"/>
-        <v>-1.2535551111111043E-2</v>
-      </c>
-      <c r="U87">
-        <f t="shared" si="16"/>
-        <v>0.34643858222222201</v>
-      </c>
-      <c r="V87">
-        <f t="shared" si="17"/>
-        <v>1.039315746666666</v>
-      </c>
-      <c r="W87">
-        <f t="shared" si="18"/>
-        <v>401.0926197252947</v>
-      </c>
-      <c r="X87">
-        <f t="shared" si="19"/>
-        <v>19.145548358642333</v>
-      </c>
-      <c r="Y87">
-        <f t="shared" si="20"/>
-        <v>492.72802961220106</v>
-      </c>
-      <c r="Z87">
-        <f t="shared" si="21"/>
-        <v>106.90687633316094</v>
-      </c>
-      <c r="AA87">
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>0.25128187333333302</v>
       </c>
@@ -8592,54 +4742,10 @@
         <v>5515</v>
       </c>
       <c r="P88">
-        <f t="shared" si="11"/>
-        <v>160.87287900699729</v>
-      </c>
-      <c r="Q88">
-        <f t="shared" si="12"/>
-        <v>3.1199999999999668</v>
-      </c>
-      <c r="R88">
-        <f t="shared" si="13"/>
-        <v>172.20000000000002</v>
-      </c>
-      <c r="S88">
-        <f t="shared" si="14"/>
-        <v>0.37700457196742249</v>
-      </c>
-      <c r="T88">
-        <f t="shared" si="15"/>
-        <v>-7.4074175555555691E-2</v>
-      </c>
-      <c r="U88">
-        <f t="shared" si="16"/>
-        <v>0.36353262444444434</v>
-      </c>
-      <c r="V88">
-        <f t="shared" si="17"/>
-        <v>1.090597873333333</v>
-      </c>
-      <c r="W88">
-        <f t="shared" si="18"/>
-        <v>426.71333710217857</v>
-      </c>
-      <c r="X88">
-        <f t="shared" si="19"/>
-        <v>-42.119942295678527</v>
-      </c>
-      <c r="Y88">
-        <f t="shared" si="20"/>
-        <v>473.68513421087988</v>
-      </c>
-      <c r="Z88">
-        <f t="shared" si="21"/>
-        <v>110.61272257141934</v>
-      </c>
-      <c r="AA88">
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>0.37777766666666701</v>
       </c>
@@ -8686,54 +4792,10 @@
         <v>12393</v>
       </c>
       <c r="P89">
-        <f t="shared" si="11"/>
-        <v>345.44021306153689</v>
-      </c>
-      <c r="Q89">
-        <f t="shared" si="12"/>
-        <v>0.23999999999996363</v>
-      </c>
-      <c r="R89">
-        <f t="shared" si="13"/>
-        <v>373.8</v>
-      </c>
-      <c r="S89">
-        <f t="shared" si="14"/>
-        <v>0.45201083589010183</v>
-      </c>
-      <c r="T89">
-        <f t="shared" si="15"/>
-        <v>3.418924444444619E-3</v>
-      </c>
-      <c r="U89">
-        <f t="shared" si="16"/>
-        <v>0.38974340444444472</v>
-      </c>
-      <c r="V89">
-        <f t="shared" si="17"/>
-        <v>1.1692302133333341</v>
-      </c>
-      <c r="W89">
-        <f t="shared" si="18"/>
-        <v>764.22993794229387</v>
-      </c>
-      <c r="X89">
-        <f t="shared" si="19"/>
-        <v>70.197515007954493</v>
-      </c>
-      <c r="Y89">
-        <f t="shared" si="20"/>
-        <v>959.09256125277852</v>
-      </c>
-      <c r="Z89">
-        <f t="shared" si="21"/>
-        <v>208.06851997643648</v>
-      </c>
-      <c r="AA89">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>0.44273506666666701</v>
       </c>
@@ -8780,54 +4842,10 @@
         <v>12139</v>
       </c>
       <c r="P90">
-        <f t="shared" si="11"/>
-        <v>347.10298183680305</v>
-      </c>
-      <c r="Q90">
-        <f t="shared" si="12"/>
-        <v>1.6799999999999575</v>
-      </c>
-      <c r="R90">
-        <f t="shared" si="13"/>
-        <v>374.7</v>
-      </c>
-      <c r="S90">
-        <f t="shared" si="14"/>
-        <v>0.45299783542029021</v>
-      </c>
-      <c r="T90">
-        <f t="shared" si="15"/>
-        <v>5.6974666666698148E-4</v>
-      </c>
-      <c r="U90">
-        <f t="shared" si="16"/>
-        <v>0.39202275999999997</v>
-      </c>
-      <c r="V90">
-        <f t="shared" si="17"/>
-        <v>1.17606828</v>
-      </c>
-      <c r="W90">
-        <f t="shared" si="18"/>
-        <v>766.23540930336196</v>
-      </c>
-      <c r="X90">
-        <f t="shared" si="19"/>
-        <v>2948.678945026496</v>
-      </c>
-      <c r="Y90">
-        <f t="shared" si="20"/>
-        <v>955.81185133230531</v>
-      </c>
-      <c r="Z90">
-        <f t="shared" si="21"/>
-        <v>209.80754620811635</v>
-      </c>
-      <c r="AA90">
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>0.42905974000000002</v>
       </c>
@@ -8874,54 +4892,10 @@
         <v>12125</v>
       </c>
       <c r="P91">
-        <f t="shared" si="11"/>
-        <v>339.20483015428897</v>
-      </c>
-      <c r="Q91">
-        <f t="shared" si="12"/>
-        <v>-3.0316490059097608E-14</v>
-      </c>
-      <c r="R91">
-        <f t="shared" si="13"/>
-        <v>367.2</v>
-      </c>
-      <c r="S91">
-        <f t="shared" si="14"/>
-        <v>0.43325931513520294</v>
-      </c>
-      <c r="T91">
-        <f t="shared" si="15"/>
-        <v>-3.988639999999692E-3</v>
-      </c>
-      <c r="U91">
-        <f t="shared" si="16"/>
-        <v>0.37720789333333332</v>
-      </c>
-      <c r="V91">
-        <f t="shared" si="17"/>
-        <v>1.1316236799999999</v>
-      </c>
-      <c r="W91">
-        <f t="shared" si="18"/>
-        <v>782.91410779809007</v>
-      </c>
-      <c r="X91">
-        <f t="shared" si="19"/>
-        <v>7.6007085269916435E-12</v>
-      </c>
-      <c r="Y91">
-        <f t="shared" si="20"/>
-        <v>973.46849440266215</v>
-      </c>
-      <c r="Z91">
-        <f t="shared" si="21"/>
-        <v>218.8165592293013</v>
-      </c>
-      <c r="AA91">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1.1176475882352901</v>
       </c>
@@ -8968,54 +4942,10 @@
         <v>4631</v>
       </c>
       <c r="P92">
-        <f t="shared" si="11"/>
-        <v>-0.36678722983818862</v>
-      </c>
-      <c r="Q92">
-        <f t="shared" si="12"/>
-        <v>-0.21176470588239527</v>
-      </c>
-      <c r="R92">
-        <f t="shared" si="13"/>
-        <v>-0.26470588235299414</v>
-      </c>
-      <c r="S92">
-        <f t="shared" si="14"/>
-        <v>1.2853228104142496</v>
-      </c>
-      <c r="T92">
-        <f t="shared" si="15"/>
-        <v>0.72699852941176257</v>
-      </c>
-      <c r="U92">
-        <f t="shared" si="16"/>
-        <v>0.74962294117646866</v>
-      </c>
-      <c r="V92">
-        <f t="shared" si="17"/>
-        <v>2.2488688235294059</v>
-      </c>
-      <c r="W92">
-        <f t="shared" si="18"/>
-        <v>-0.28536584495841627</v>
-      </c>
-      <c r="X92">
-        <f t="shared" si="19"/>
-        <v>-0.29128629194579081</v>
-      </c>
-      <c r="Y92">
-        <f t="shared" si="20"/>
-        <v>-0.3531187051687093</v>
-      </c>
-      <c r="Z92">
-        <f t="shared" si="21"/>
-        <v>1.1770623505621294</v>
-      </c>
-      <c r="AA92">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1.03318282352941</v>
       </c>
@@ -9062,54 +4992,10 @@
         <v>5589</v>
       </c>
       <c r="P93">
-        <f t="shared" si="11"/>
-        <v>0.36678722983818862</v>
-      </c>
-      <c r="Q93">
-        <f t="shared" si="12"/>
-        <v>-0.63529411764701538</v>
-      </c>
-      <c r="R93">
-        <f t="shared" si="13"/>
-        <v>0.79411764705887811</v>
-      </c>
-      <c r="S93">
-        <f t="shared" si="14"/>
-        <v>1.1137723476053005</v>
-      </c>
-      <c r="T93">
-        <f t="shared" si="15"/>
-        <v>0.63499252549019536</v>
-      </c>
-      <c r="U93">
-        <f t="shared" si="16"/>
-        <v>0.64705888431372482</v>
-      </c>
-      <c r="V93">
-        <f t="shared" si="17"/>
-        <v>1.9411766529411745</v>
-      </c>
-      <c r="W93">
-        <f t="shared" si="18"/>
-        <v>0.32931974889375776</v>
-      </c>
-      <c r="X93">
-        <f t="shared" si="19"/>
-        <v>-1.0004749538690825</v>
-      </c>
-      <c r="Y93">
-        <f t="shared" si="20"/>
-        <v>1.2272726119835675</v>
-      </c>
-      <c r="Z93">
-        <f t="shared" si="21"/>
-        <v>0.70727266083196227</v>
-      </c>
-      <c r="AA93">
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>0.80693823529411801</v>
       </c>
@@ -9156,54 +5042,10 @@
         <v>3611</v>
       </c>
       <c r="P94">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="Q94">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="R94">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="S94">
-        <f t="shared" si="14"/>
-        <v>0.91609770547977298</v>
-      </c>
-      <c r="T94">
-        <f t="shared" si="15"/>
-        <v>0.52589266862745121</v>
-      </c>
-      <c r="U94">
-        <f t="shared" si="16"/>
-        <v>0.53041755098039234</v>
-      </c>
-      <c r="V94">
-        <f t="shared" si="17"/>
-        <v>1.591252652941177</v>
-      </c>
-      <c r="W94">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="X94">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="Y94">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Z94">
-        <f t="shared" si="21"/>
-        <v>2.7447854058565997</v>
-      </c>
-      <c r="AA94">
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>0.53091999999999995</v>
       </c>
@@ -9250,54 +5092,10 @@
         <v>2862</v>
       </c>
       <c r="P95">
-        <f t="shared" si="11"/>
-        <v>71.156722588594221</v>
-      </c>
-      <c r="Q95">
-        <f t="shared" si="12"/>
-        <v>123.67058823529399</v>
-      </c>
-      <c r="R95">
-        <f t="shared" si="13"/>
-        <v>-0.26470588235299886</v>
-      </c>
-      <c r="S95">
-        <f t="shared" si="14"/>
-        <v>0.61914944378731895</v>
-      </c>
-      <c r="T95">
-        <f t="shared" si="15"/>
-        <v>-0.36450460784313782</v>
-      </c>
-      <c r="U95">
-        <f t="shared" si="16"/>
-        <v>0.7184514509803922</v>
-      </c>
-      <c r="V95">
-        <f t="shared" si="17"/>
-        <v>2.1553543529411767</v>
-      </c>
-      <c r="W95">
-        <f t="shared" si="18"/>
-        <v>114.92657112526928</v>
-      </c>
-      <c r="X95">
-        <f t="shared" si="19"/>
-        <v>-339.28401884158023</v>
-      </c>
-      <c r="Y95">
-        <f t="shared" si="20"/>
-        <v>-0.36843948466077098</v>
-      </c>
-      <c r="Z95">
-        <f t="shared" si="21"/>
-        <v>-2.3964941591151994</v>
-      </c>
-      <c r="AA95">
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>0.56259435294117699</v>
       </c>
@@ -9344,54 +5142,10 @@
         <v>2915</v>
       </c>
       <c r="P96">
-        <f t="shared" si="11"/>
-        <v>70.056360899079877</v>
-      </c>
-      <c r="Q96">
-        <f t="shared" si="12"/>
-        <v>125.15294117647039</v>
-      </c>
-      <c r="R96">
-        <f t="shared" si="13"/>
-        <v>-2.3823529411764972</v>
-      </c>
-      <c r="S96">
-        <f t="shared" si="14"/>
-        <v>0.59737892360740019</v>
-      </c>
-      <c r="T96">
-        <f t="shared" si="15"/>
-        <v>-0.34489703921568537</v>
-      </c>
-      <c r="U96">
-        <f t="shared" si="16"/>
-        <v>0.68979384313725467</v>
-      </c>
-      <c r="V96">
-        <f t="shared" si="17"/>
-        <v>2.0693815294117641</v>
-      </c>
-      <c r="W96">
-        <f t="shared" si="18"/>
-        <v>117.27290356350302</v>
-      </c>
-      <c r="X96">
-        <f t="shared" si="19"/>
-        <v>-362.87044232410631</v>
-      </c>
-      <c r="Y96">
-        <f t="shared" si="20"/>
-        <v>-3.4537173169614075</v>
-      </c>
-      <c r="Z96">
-        <f t="shared" si="21"/>
-        <v>-2.512259559448939</v>
-      </c>
-      <c r="AA96">
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>0.53393676470588203</v>
       </c>
@@ -9438,54 +5192,10 @@
         <v>2912</v>
       </c>
       <c r="P97">
-        <f t="shared" si="11"/>
-        <v>65.654914141022658</v>
-      </c>
-      <c r="Q97">
-        <f t="shared" si="12"/>
-        <v>115.41176470588225</v>
-      </c>
-      <c r="R97">
-        <f t="shared" si="13"/>
-        <v>-1.0588235294116639</v>
-      </c>
-      <c r="S97">
-        <f t="shared" si="14"/>
-        <v>0.62176202507514133</v>
-      </c>
-      <c r="T97">
-        <f t="shared" si="15"/>
-        <v>-0.31875344901960712</v>
-      </c>
-      <c r="U97">
-        <f t="shared" si="16"/>
-        <v>0.69783843333333306</v>
-      </c>
-      <c r="V97">
-        <f t="shared" si="17"/>
-        <v>2.0935152999999991</v>
-      </c>
-      <c r="W97">
-        <f t="shared" si="18"/>
-        <v>105.59492457437894</v>
-      </c>
-      <c r="X97">
-        <f t="shared" si="19"/>
-        <v>-362.07220678193528</v>
-      </c>
-      <c r="Y97">
-        <f t="shared" si="20"/>
-        <v>-1.5172903624038443</v>
-      </c>
-      <c r="Z97">
-        <f t="shared" si="21"/>
-        <v>-1.6513176777496734</v>
-      </c>
-      <c r="AA97">
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>0.31975847058823498</v>
       </c>
@@ -9532,54 +5242,10 @@
         <v>9816</v>
       </c>
       <c r="P98">
-        <f t="shared" si="11"/>
-        <v>79.226041645032936</v>
-      </c>
-      <c r="Q98">
-        <f t="shared" si="12"/>
-        <v>133.41176470588238</v>
-      </c>
-      <c r="R98">
-        <f t="shared" si="13"/>
-        <v>2.3823529411765016</v>
-      </c>
-      <c r="S98">
-        <f t="shared" si="14"/>
-        <v>0.74106327001788863</v>
-      </c>
-      <c r="T98">
-        <f t="shared" si="15"/>
-        <v>-6.7873588235294394E-2</v>
-      </c>
-      <c r="U98">
-        <f t="shared" si="16"/>
-        <v>0.67571641176470576</v>
-      </c>
-      <c r="V98">
-        <f t="shared" si="17"/>
-        <v>2.0271492352941172</v>
-      </c>
-      <c r="W98">
-        <f t="shared" si="18"/>
-        <v>106.9086066606978</v>
-      </c>
-      <c r="X98">
-        <f t="shared" si="19"/>
-        <v>-1965.5917445146654</v>
-      </c>
-      <c r="Y98">
-        <f t="shared" si="20"/>
-        <v>3.5256697923833635</v>
-      </c>
-      <c r="Z98">
-        <f t="shared" si="21"/>
-        <v>-4.6051341238784529</v>
-      </c>
-      <c r="AA98">
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>0.34389124705882301</v>
       </c>
@@ -9626,54 +5292,10 @@
         <v>8239</v>
       </c>
       <c r="P99">
-        <f t="shared" si="11"/>
-        <v>74.824594886975504</v>
-      </c>
-      <c r="Q99">
-        <f t="shared" si="12"/>
-        <v>124.09411764705892</v>
-      </c>
-      <c r="R99">
-        <f t="shared" si="13"/>
-        <v>3.4411764705881658</v>
-      </c>
-      <c r="S99">
-        <f t="shared" si="14"/>
-        <v>0.69142721758213288</v>
-      </c>
-      <c r="T99">
-        <f t="shared" si="15"/>
-        <v>-8.1447956862745086E-2</v>
-      </c>
-      <c r="U99">
-        <f t="shared" si="16"/>
-        <v>0.63951751372548993</v>
-      </c>
-      <c r="V99">
-        <f t="shared" si="17"/>
-        <v>1.9185525411764699</v>
-      </c>
-      <c r="W99">
-        <f t="shared" si="18"/>
-        <v>108.21760119399303</v>
-      </c>
-      <c r="X99">
-        <f t="shared" si="19"/>
-        <v>-1523.6001297881608</v>
-      </c>
-      <c r="Y99">
-        <f t="shared" si="20"/>
-        <v>5.3808948101228635</v>
-      </c>
-      <c r="Z99">
-        <f t="shared" si="21"/>
-        <v>-3.2414142411749349</v>
-      </c>
-      <c r="AA99">
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>0.38264284615384597</v>
       </c>
@@ -9720,54 +5342,10 @@
         <v>2579</v>
       </c>
       <c r="P100">
-        <f t="shared" si="11"/>
-        <v>77.222819082070785</v>
-      </c>
-      <c r="Q100">
-        <f t="shared" si="12"/>
-        <v>5.261538461538529</v>
-      </c>
-      <c r="R100">
-        <f t="shared" si="13"/>
-        <v>80.307692307692164</v>
-      </c>
-      <c r="S100">
-        <f t="shared" si="14"/>
-        <v>0.3883161981601615</v>
-      </c>
-      <c r="T100">
-        <f t="shared" si="15"/>
-        <v>-0.14398451282051339</v>
-      </c>
-      <c r="U100">
-        <f t="shared" si="16"/>
-        <v>0.4082839487179486</v>
-      </c>
-      <c r="V100">
-        <f t="shared" si="17"/>
-        <v>1.2248518461538458</v>
-      </c>
-      <c r="W100">
-        <f t="shared" si="18"/>
-        <v>198.86581978282589</v>
-      </c>
-      <c r="X100">
-        <f t="shared" si="19"/>
-        <v>-36.542391667480231</v>
-      </c>
-      <c r="Y100">
-        <f t="shared" si="20"/>
-        <v>196.69568828229998</v>
-      </c>
-      <c r="Z100">
-        <f t="shared" si="21"/>
-        <v>44.233921163715003</v>
-      </c>
-      <c r="AA100">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>0.41025623076923101</v>
       </c>
@@ -9814,54 +5392,10 @@
         <v>2297</v>
       </c>
       <c r="P101">
-        <f t="shared" si="11"/>
-        <v>75.783884565013608</v>
-      </c>
-      <c r="Q101">
-        <f t="shared" si="12"/>
-        <v>-1.1076923076922791</v>
-      </c>
-      <c r="R101">
-        <f t="shared" si="13"/>
-        <v>82.730769230769155</v>
-      </c>
-      <c r="S101">
-        <f t="shared" si="14"/>
-        <v>0.39287122531471308</v>
-      </c>
-      <c r="T101">
-        <f t="shared" si="15"/>
-        <v>4.1420153846153641E-2</v>
-      </c>
-      <c r="U101">
-        <f t="shared" si="16"/>
-        <v>0.31952638461538468</v>
-      </c>
-      <c r="V101">
-        <f t="shared" si="17"/>
-        <v>0.95857915384615411</v>
-      </c>
-      <c r="W101">
-        <f t="shared" si="18"/>
-        <v>192.89751878444707</v>
-      </c>
-      <c r="X101">
-        <f t="shared" si="19"/>
-        <v>-26.742834220427252</v>
-      </c>
-      <c r="Y101">
-        <f t="shared" si="20"/>
-        <v>258.91686325169218</v>
-      </c>
-      <c r="Z101">
-        <f t="shared" si="21"/>
-        <v>48.468370133392199</v>
-      </c>
-      <c r="AA101">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>0.23668615384615399</v>
       </c>
@@ -9908,54 +5442,10 @@
         <v>2356</v>
       </c>
       <c r="P102">
-        <f t="shared" si="11"/>
-        <v>70.028146496784942</v>
-      </c>
-      <c r="Q102">
-        <f t="shared" si="12"/>
-        <v>0.55384615384612057</v>
-      </c>
-      <c r="R102">
-        <f t="shared" si="13"/>
-        <v>75.461538461538666</v>
-      </c>
-      <c r="S102">
-        <f t="shared" si="14"/>
-        <v>0.28696671073672159</v>
-      </c>
-      <c r="T102">
-        <f t="shared" si="15"/>
-        <v>-0.14464184615384634</v>
-      </c>
-      <c r="U102">
-        <f t="shared" si="16"/>
-        <v>0.32084138461538464</v>
-      </c>
-      <c r="V102">
-        <f t="shared" si="17"/>
-        <v>0.96252415384615397</v>
-      </c>
-      <c r="W102">
-        <f t="shared" si="18"/>
-        <v>244.02881545738754</v>
-      </c>
-      <c r="X102">
-        <f t="shared" si="19"/>
-        <v>-3.8290865926657878</v>
-      </c>
-      <c r="Y102">
-        <f t="shared" si="20"/>
-        <v>235.19889291089979</v>
-      </c>
-      <c r="Z102">
-        <f t="shared" si="21"/>
-        <v>50.585743542579628</v>
-      </c>
-      <c r="AA102">
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>0.39487159999999999</v>
       </c>
@@ -10002,54 +5492,10 @@
         <v>5715</v>
       </c>
       <c r="P103">
-        <f t="shared" si="11"/>
-        <v>162.53564778226345</v>
-      </c>
-      <c r="Q103">
-        <f t="shared" si="12"/>
-        <v>1.1999999999999849</v>
-      </c>
-      <c r="R103">
-        <f t="shared" si="13"/>
-        <v>175.19999999999996</v>
-      </c>
-      <c r="S103">
-        <f t="shared" si="14"/>
-        <v>0.43918068877804406</v>
-      </c>
-      <c r="T103">
-        <f t="shared" si="15"/>
-        <v>-2.678059999999971E-2</v>
-      </c>
-      <c r="U103">
-        <f t="shared" si="16"/>
-        <v>0.39373193333333328</v>
-      </c>
-      <c r="V103">
-        <f t="shared" si="17"/>
-        <v>1.1811957999999998</v>
-      </c>
-      <c r="W103">
-        <f t="shared" si="18"/>
-        <v>370.08833023714016</v>
-      </c>
-      <c r="X103">
-        <f t="shared" si="19"/>
-        <v>-44.808555446853241</v>
-      </c>
-      <c r="Y103">
-        <f t="shared" si="20"/>
-        <v>444.97279790530911</v>
-      </c>
-      <c r="Z103">
-        <f t="shared" si="21"/>
-        <v>92.748382613619199</v>
-      </c>
-      <c r="AA103">
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>0.35384593333333297</v>
       </c>
@@ -10096,54 +5542,10 @@
         <v>5717</v>
       </c>
       <c r="P104">
-        <f t="shared" si="11"/>
-        <v>162.53564778226345</v>
-      </c>
-      <c r="Q104">
-        <f t="shared" si="12"/>
-        <v>0.23999999999997879</v>
-      </c>
-      <c r="R104">
-        <f t="shared" si="13"/>
-        <v>175.79999999999998</v>
-      </c>
-      <c r="S104">
-        <f t="shared" si="14"/>
-        <v>0.39575606193030649</v>
-      </c>
-      <c r="T104">
-        <f t="shared" si="15"/>
-        <v>-6.4387508888889403E-2</v>
-      </c>
-      <c r="U104">
-        <f t="shared" si="16"/>
-        <v>0.37492855777777762</v>
-      </c>
-      <c r="V104">
-        <f t="shared" si="17"/>
-        <v>1.1247856733333328</v>
-      </c>
-      <c r="W104">
-        <f t="shared" si="18"/>
-        <v>410.69654622469517</v>
-      </c>
-      <c r="X104">
-        <f t="shared" si="19"/>
-        <v>-3.7274310521026037</v>
-      </c>
-      <c r="Y104">
-        <f t="shared" si="20"/>
-        <v>468.88932932176823</v>
-      </c>
-      <c r="Z104">
-        <f t="shared" si="21"/>
-        <v>96.788217151959941</v>
-      </c>
-      <c r="AA104">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>0.24957247333333299</v>
       </c>
@@ -10190,54 +5592,10 @@
         <v>5658</v>
       </c>
       <c r="P105">
-        <f t="shared" si="11"/>
-        <v>152.9747273244833</v>
-      </c>
-      <c r="Q105">
-        <f t="shared" si="12"/>
-        <v>0.95999999999999086</v>
-      </c>
-      <c r="R105">
-        <f t="shared" si="13"/>
-        <v>165.00000000000003</v>
-      </c>
-      <c r="S105">
-        <f t="shared" si="14"/>
-        <v>0.3967430999505131</v>
-      </c>
-      <c r="T105">
-        <f t="shared" si="15"/>
-        <v>-7.1794975555556029E-2</v>
-      </c>
-      <c r="U105">
-        <f t="shared" si="16"/>
-        <v>0.37948709111111095</v>
-      </c>
-      <c r="V105">
-        <f t="shared" si="17"/>
-        <v>1.1384612733333328</v>
-      </c>
-      <c r="W105">
-        <f t="shared" si="18"/>
-        <v>385.57627679867471</v>
-      </c>
-      <c r="X105">
-        <f t="shared" si="19"/>
-        <v>-13.371409246558326</v>
-      </c>
-      <c r="Y105">
-        <f t="shared" si="20"/>
-        <v>434.79739855416921</v>
-      </c>
-      <c r="Z105">
-        <f t="shared" si="21"/>
-        <v>91.969751147910458</v>
-      </c>
-      <c r="AA105">
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>0.42948713124999999</v>
       </c>
@@ -10284,54 +5642,10 @@
         <v>14058</v>
       </c>
       <c r="P106">
-        <f t="shared" si="11"/>
-        <v>349.57115423758864</v>
-      </c>
-      <c r="Q106">
-        <f t="shared" si="12"/>
-        <v>0.2249999999999697</v>
-      </c>
-      <c r="R106">
-        <f t="shared" si="13"/>
-        <v>378.28125</v>
-      </c>
-      <c r="S106">
-        <f t="shared" si="14"/>
-        <v>0.47279791255051568</v>
-      </c>
-      <c r="T106">
-        <f t="shared" si="15"/>
-        <v>-9.0811645833333756E-3</v>
-      </c>
-      <c r="U106">
-        <f t="shared" si="16"/>
-        <v>0.41399558541666664</v>
-      </c>
-      <c r="V106">
-        <f t="shared" si="17"/>
-        <v>1.24198675625</v>
-      </c>
-      <c r="W106">
-        <f t="shared" si="18"/>
-        <v>739.36695775965177</v>
-      </c>
-      <c r="X106">
-        <f t="shared" si="19"/>
-        <v>-24.776557889162287</v>
-      </c>
-      <c r="Y106">
-        <f t="shared" si="20"/>
-        <v>913.73256944099569</v>
-      </c>
-      <c r="Z106">
-        <f t="shared" si="21"/>
-        <v>182.66197192390555</v>
-      </c>
-      <c r="AA106">
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>0.41987168749999998</v>
       </c>
@@ -10378,54 +5692,10 @@
         <v>12262</v>
       </c>
       <c r="P107">
-        <f t="shared" si="11"/>
-        <v>347.62259707907373</v>
-      </c>
-      <c r="Q107">
-        <f t="shared" si="12"/>
-        <v>2.2499999999999698</v>
-      </c>
-      <c r="R107">
-        <f t="shared" si="13"/>
-        <v>374.90625</v>
-      </c>
-      <c r="S107">
-        <f t="shared" si="14"/>
-        <v>0.44689115591617501</v>
-      </c>
-      <c r="T107">
-        <f t="shared" si="15"/>
-        <v>-8.6004437500000017E-2</v>
-      </c>
-      <c r="U107">
-        <f t="shared" si="16"/>
-        <v>0.43002131250000003</v>
-      </c>
-      <c r="V107">
-        <f t="shared" si="17"/>
-        <v>1.2900639375</v>
-      </c>
-      <c r="W107">
-        <f t="shared" si="18"/>
-        <v>777.86859837583927</v>
-      </c>
-      <c r="X107">
-        <f t="shared" si="19"/>
-        <v>-26.161440797749179</v>
-      </c>
-      <c r="Y107">
-        <f t="shared" si="20"/>
-        <v>871.83178856978157</v>
-      </c>
-      <c r="Z107">
-        <f t="shared" si="21"/>
-        <v>172.7516121657342</v>
-      </c>
-      <c r="AA107">
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>0.2003204375</v>
       </c>
@@ -10472,54 +5742,10 @@
         <v>6867</v>
       </c>
       <c r="P108">
-        <f t="shared" si="11"/>
-        <v>176.14956712975484</v>
-      </c>
-      <c r="Q108">
-        <f t="shared" si="12"/>
-        <v>1.7999999999999849</v>
-      </c>
-      <c r="R108">
-        <f t="shared" si="13"/>
-        <v>189.5625</v>
-      </c>
-      <c r="S108">
-        <f t="shared" si="14"/>
-        <v>0.23778676018060277</v>
-      </c>
-      <c r="T108">
-        <f t="shared" si="15"/>
-        <v>-8.600430416666667E-2</v>
-      </c>
-      <c r="U108">
-        <f t="shared" si="16"/>
-        <v>0.24893152708333333</v>
-      </c>
-      <c r="V108">
-        <f t="shared" si="17"/>
-        <v>0.74679458124999998</v>
-      </c>
-      <c r="W108">
-        <f t="shared" si="18"/>
-        <v>740.78795218020753</v>
-      </c>
-      <c r="X108">
-        <f t="shared" si="19"/>
-        <v>-20.929185084874209</v>
-      </c>
-      <c r="Y108">
-        <f t="shared" si="20"/>
-        <v>761.50458811326575</v>
-      </c>
-      <c r="Z108">
-        <f t="shared" si="21"/>
-        <v>168.07081646188632</v>
-      </c>
-      <c r="AA108">
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>0.50427346666666695</v>
       </c>
@@ -10566,54 +5792,10 @@
         <v>4853</v>
       </c>
       <c r="P109">
-        <f t="shared" si="11"/>
-        <v>1.6627687752661198</v>
-      </c>
-      <c r="Q109">
-        <f t="shared" si="12"/>
-        <v>0.95999999999999841</v>
-      </c>
-      <c r="R109">
-        <f t="shared" si="13"/>
-        <v>1.1999999999999982</v>
-      </c>
-      <c r="S109">
-        <f t="shared" si="14"/>
-        <v>0.49148773789621164</v>
-      </c>
-      <c r="T109">
-        <f t="shared" si="15"/>
-        <v>0.26438736888888908</v>
-      </c>
-      <c r="U109">
-        <f t="shared" si="16"/>
-        <v>0.29344718222222244</v>
-      </c>
-      <c r="V109">
-        <f t="shared" si="17"/>
-        <v>0.88034154666666731</v>
-      </c>
-      <c r="W109">
-        <f t="shared" si="18"/>
-        <v>3.3831337937005657</v>
-      </c>
-      <c r="X109">
-        <f t="shared" si="19"/>
-        <v>3.6310357943137825</v>
-      </c>
-      <c r="Y109">
-        <f t="shared" si="20"/>
-        <v>4.0893219383216266</v>
-      </c>
-      <c r="Z109">
-        <f t="shared" si="21"/>
-        <v>2.0719231154162938</v>
-      </c>
-      <c r="AA109">
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>0.45641013333333302</v>
       </c>
@@ -10660,54 +5842,10 @@
         <v>4870</v>
       </c>
       <c r="P110">
-        <f t="shared" si="11"/>
-        <v>1.6627687752661329</v>
-      </c>
-      <c r="Q110">
-        <f t="shared" si="12"/>
-        <v>1.9200000000000059</v>
-      </c>
-      <c r="R110">
-        <f t="shared" si="13"/>
-        <v>0.60000000000000375</v>
-      </c>
-      <c r="S110">
-        <f t="shared" si="14"/>
-        <v>0.44214153725753946</v>
-      </c>
-      <c r="T110">
-        <f t="shared" si="15"/>
-        <v>0.24957253111111086</v>
-      </c>
-      <c r="U110">
-        <f t="shared" si="16"/>
-        <v>0.25811953777777757</v>
-      </c>
-      <c r="V110">
-        <f t="shared" si="17"/>
-        <v>0.77435861333333267</v>
-      </c>
-      <c r="W110">
-        <f t="shared" si="18"/>
-        <v>3.7607160493894063</v>
-      </c>
-      <c r="X110">
-        <f t="shared" si="19"/>
-        <v>7.6931543365452066</v>
-      </c>
-      <c r="Y110">
-        <f t="shared" si="20"/>
-        <v>2.3245043950007411</v>
-      </c>
-      <c r="Z110">
-        <f t="shared" si="21"/>
-        <v>0.6689407092279881</v>
-      </c>
-      <c r="AA110">
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>0.32991426666666701</v>
       </c>
@@ -10754,54 +5892,10 @@
         <v>4906</v>
       </c>
       <c r="P111">
-        <f t="shared" si="11"/>
-        <v>1.2470765814495866</v>
-      </c>
-      <c r="Q111">
-        <f t="shared" si="12"/>
-        <v>0.23999999999999683</v>
-      </c>
-      <c r="R111">
-        <f t="shared" si="13"/>
-        <v>1.1999999999999982</v>
-      </c>
-      <c r="S111">
-        <f t="shared" si="14"/>
-        <v>0.38292602643930179</v>
-      </c>
-      <c r="T111">
-        <f t="shared" si="15"/>
-        <v>0.21424484444444461</v>
-      </c>
-      <c r="U111">
-        <f t="shared" si="16"/>
-        <v>0.22450124444444466</v>
-      </c>
-      <c r="V111">
-        <f t="shared" si="17"/>
-        <v>0.67350373333333402</v>
-      </c>
-      <c r="W111">
-        <f t="shared" si="18"/>
-        <v>3.2567036329332986</v>
-      </c>
-      <c r="X111">
-        <f t="shared" si="19"/>
-        <v>1.1202136537863376</v>
-      </c>
-      <c r="Y111">
-        <f t="shared" si="20"/>
-        <v>5.3451819519733288</v>
-      </c>
-      <c r="Z111">
-        <f t="shared" si="21"/>
-        <v>0.53154861997300584</v>
-      </c>
-      <c r="AA111">
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>0.24358950625</v>
       </c>
@@ -10848,54 +5942,10 @@
         <v>3261</v>
       </c>
       <c r="P112">
-        <f t="shared" si="11"/>
-        <v>79.890843499114467</v>
-      </c>
-      <c r="Q112">
-        <f t="shared" si="12"/>
-        <v>139.72499999999999</v>
-      </c>
-      <c r="R112">
-        <f t="shared" si="13"/>
-        <v>-0.84375</v>
-      </c>
-      <c r="S112">
-        <f t="shared" si="14"/>
-        <v>0.23408570318967206</v>
-      </c>
-      <c r="T112">
-        <f t="shared" si="15"/>
-        <v>-8.707268125000002E-2</v>
-      </c>
-      <c r="U112">
-        <f t="shared" si="16"/>
-        <v>0.24626050625000004</v>
-      </c>
-      <c r="V112">
-        <f t="shared" si="17"/>
-        <v>0.73878151875000009</v>
-      </c>
-      <c r="W112">
-        <f t="shared" si="18"/>
-        <v>341.28886305534644</v>
-      </c>
-      <c r="X112">
-        <f t="shared" si="19"/>
-        <v>-1604.6938947340611</v>
-      </c>
-      <c r="Y112">
-        <f t="shared" si="20"/>
-        <v>-3.4262497582273199</v>
-      </c>
-      <c r="Z112">
-        <f t="shared" si="21"/>
-        <v>2.035446178045043</v>
-      </c>
-      <c r="AA112">
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>0.19070494374999999</v>
       </c>
@@ -10942,54 +5992,10 @@
         <v>3024</v>
       </c>
       <c r="P113">
-        <f t="shared" si="11"/>
-        <v>81.449689225926463</v>
-      </c>
-      <c r="Q113">
-        <f t="shared" si="12"/>
-        <v>141.07499999999999</v>
-      </c>
-      <c r="R113">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="S113">
-        <f t="shared" si="14"/>
-        <v>0.25259049378815768</v>
-      </c>
-      <c r="T113">
-        <f t="shared" si="15"/>
-        <v>-7.4252185416666686E-2</v>
-      </c>
-      <c r="U113">
-        <f t="shared" si="16"/>
-        <v>0.25587587708333331</v>
-      </c>
-      <c r="V113">
-        <f t="shared" si="17"/>
-        <v>0.76762763124999989</v>
-      </c>
-      <c r="W113">
-        <f t="shared" si="18"/>
-        <v>322.45746070806842</v>
-      </c>
-      <c r="X113">
-        <f t="shared" si="19"/>
-        <v>-1899.9440785258587</v>
-      </c>
-      <c r="Y113">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Z113">
-        <f t="shared" si="21"/>
-        <v>-0.26624237023255282</v>
-      </c>
-      <c r="AA113">
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>0.14102557499999999</v>
       </c>
@@ -11036,54 +6042,10 @@
         <v>1617</v>
       </c>
       <c r="P114">
-        <f t="shared" si="11"/>
-        <v>41.309411760517726</v>
-      </c>
-      <c r="Q114">
-        <f t="shared" si="12"/>
-        <v>71.55</v>
-      </c>
-      <c r="R114">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="S114">
-        <f t="shared" si="14"/>
-        <v>0.15358986516879133</v>
-      </c>
-      <c r="T114">
-        <f t="shared" si="15"/>
-        <v>-6.4102516666666678E-2</v>
-      </c>
-      <c r="U114">
-        <f t="shared" si="16"/>
-        <v>0.1650639833333333</v>
-      </c>
-      <c r="V114">
-        <f t="shared" si="17"/>
-        <v>0.49519194999999994</v>
-      </c>
-      <c r="W114">
-        <f t="shared" si="18"/>
-        <v>268.95922927674781</v>
-      </c>
-      <c r="X114">
-        <f t="shared" si="19"/>
-        <v>-1116.1808259738109</v>
-      </c>
-      <c r="Y114">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="Z114">
-        <f t="shared" si="21"/>
-        <v>3.2222353372263024</v>
-      </c>
-      <c r="AA114">
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>0.165811813333333</v>
       </c>
@@ -11130,54 +6092,10 @@
         <v>7704</v>
       </c>
       <c r="P115">
-        <f t="shared" si="11"/>
-        <v>88.542437282921</v>
-      </c>
-      <c r="Q115">
-        <f t="shared" si="12"/>
-        <v>146.63999999999999</v>
-      </c>
-      <c r="R115">
-        <f t="shared" si="13"/>
-        <v>4.1999999999999984</v>
-      </c>
-      <c r="S115">
-        <f t="shared" si="14"/>
-        <v>0.2378483422848153</v>
-      </c>
-      <c r="T115">
-        <f t="shared" si="15"/>
-        <v>-3.133900000000036E-2</v>
-      </c>
-      <c r="U115">
-        <f t="shared" si="16"/>
-        <v>0.22165220666666666</v>
-      </c>
-      <c r="V115">
-        <f t="shared" si="17"/>
-        <v>0.66495662</v>
-      </c>
-      <c r="W115">
-        <f t="shared" si="18"/>
-        <v>372.26426063081175</v>
-      </c>
-      <c r="X115">
-        <f t="shared" si="19"/>
-        <v>-4679.1537700628069</v>
-      </c>
-      <c r="Y115">
-        <f t="shared" si="20"/>
-        <v>18.948604496936952</v>
-      </c>
-      <c r="Z115">
-        <f t="shared" si="21"/>
-        <v>5.392832964051113</v>
-      </c>
-      <c r="AA115">
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>0.218803206666667</v>
       </c>
@@ -11224,54 +6142,10 @@
         <v>8553</v>
       </c>
       <c r="P116">
-        <f t="shared" si="11"/>
-        <v>86.463976313838373</v>
-      </c>
-      <c r="Q116">
-        <f t="shared" si="12"/>
-        <v>144</v>
-      </c>
-      <c r="R116">
-        <f t="shared" si="13"/>
-        <v>3.6000000000000036</v>
-      </c>
-      <c r="S116">
-        <f t="shared" si="14"/>
-        <v>0.30101138164558966</v>
-      </c>
-      <c r="T116">
-        <f t="shared" si="15"/>
-        <v>-3.0199446666666369E-2</v>
-      </c>
-      <c r="U116">
-        <f t="shared" si="16"/>
-        <v>0.27578322666666666</v>
-      </c>
-      <c r="V116">
-        <f t="shared" si="17"/>
-        <v>0.82734967999999998</v>
-      </c>
-      <c r="W116">
-        <f t="shared" si="18"/>
-        <v>287.24487373584077</v>
-      </c>
-      <c r="X116">
-        <f t="shared" si="19"/>
-        <v>-4768.29928671987</v>
-      </c>
-      <c r="Y116">
-        <f t="shared" si="20"/>
-        <v>13.053730799775025</v>
-      </c>
-      <c r="Z116">
-        <f t="shared" si="21"/>
-        <v>4.4551899772294465</v>
-      </c>
-      <c r="AA116">
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>0.2854698</v>
       </c>
@@ -11318,54 +6192,10 @@
         <v>7973</v>
       </c>
       <c r="P117">
-        <f t="shared" si="11"/>
-        <v>88.542437282921</v>
-      </c>
-      <c r="Q117">
-        <f t="shared" si="12"/>
-        <v>145.19999999999999</v>
-      </c>
-      <c r="R117">
-        <f t="shared" si="13"/>
-        <v>5.0999999999999943</v>
-      </c>
-      <c r="S117">
-        <f t="shared" si="14"/>
-        <v>0.31482829734772805</v>
-      </c>
-      <c r="T117">
-        <f t="shared" si="15"/>
-        <v>3.9885488888889613E-3</v>
-      </c>
-      <c r="U117">
-        <f t="shared" si="16"/>
-        <v>0.27065502888888898</v>
-      </c>
-      <c r="V117">
-        <f t="shared" si="17"/>
-        <v>0.811965086666667</v>
-      </c>
-      <c r="W117">
-        <f t="shared" si="18"/>
-        <v>281.24040319389024</v>
-      </c>
-      <c r="X117">
-        <f t="shared" si="19"/>
-        <v>36404.217183971006</v>
-      </c>
-      <c r="Y117">
-        <f t="shared" si="20"/>
-        <v>18.843174726650577</v>
-      </c>
-      <c r="Z117">
-        <f t="shared" si="21"/>
-        <v>7.0273957509979281</v>
-      </c>
-      <c r="AA117">
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>0.17094002666666699</v>
       </c>
@@ -11412,54 +6242,10 @@
         <v>2883</v>
       </c>
       <c r="P118">
-        <f t="shared" si="11"/>
-        <v>81.059977794223457</v>
-      </c>
-      <c r="Q118">
-        <f t="shared" si="12"/>
-        <v>0.71999999999998943</v>
-      </c>
-      <c r="R118">
-        <f t="shared" si="13"/>
-        <v>87.3</v>
-      </c>
-      <c r="S118">
-        <f t="shared" si="14"/>
-        <v>0.18356762512042557</v>
-      </c>
-      <c r="T118">
-        <f t="shared" si="15"/>
-        <v>-6.7236435555555349E-2</v>
-      </c>
-      <c r="U118">
-        <f t="shared" si="16"/>
-        <v>0.19259244444444468</v>
-      </c>
-      <c r="V118">
-        <f t="shared" si="17"/>
-        <v>0.57777733333333403</v>
-      </c>
-      <c r="W118">
-        <f t="shared" si="18"/>
-        <v>441.58101267064825</v>
-      </c>
-      <c r="X118">
-        <f t="shared" si="19"/>
-        <v>-10.708479621961461</v>
-      </c>
-      <c r="Y118">
-        <f t="shared" si="20"/>
-        <v>453.28881022216115</v>
-      </c>
-      <c r="Z118">
-        <f t="shared" si="21"/>
-        <v>114.00585692758229</v>
-      </c>
-      <c r="AA118">
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>0.31111080000000002</v>
       </c>
@@ -11506,54 +6292,10 @@
         <v>2860</v>
       </c>
       <c r="P119">
-        <f t="shared" si="11"/>
-        <v>78.565824631324304</v>
-      </c>
-      <c r="Q119">
-        <f t="shared" si="12"/>
-        <v>1.2</v>
-      </c>
-      <c r="R119">
-        <f t="shared" si="13"/>
-        <v>84.3</v>
-      </c>
-      <c r="S119">
-        <f t="shared" si="14"/>
-        <v>0.29805061784413278</v>
-      </c>
-      <c r="T119">
-        <f t="shared" si="15"/>
-        <v>-2.2791955555557055E-3</v>
-      </c>
-      <c r="U119">
-        <f t="shared" si="16"/>
-        <v>0.25925900444444433</v>
-      </c>
-      <c r="V119">
-        <f t="shared" si="17"/>
-        <v>0.77777701333333293</v>
-      </c>
-      <c r="W119">
-        <f t="shared" si="18"/>
-        <v>263.59893228743692</v>
-      </c>
-      <c r="X119">
-        <f t="shared" si="19"/>
-        <v>-526.50155317954727</v>
-      </c>
-      <c r="Y119">
-        <f t="shared" si="20"/>
-        <v>325.1574624404775</v>
-      </c>
-      <c r="Z119">
-        <f t="shared" si="21"/>
-        <v>71.807213433375651</v>
-      </c>
-      <c r="AA119">
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>0.27008520666666702</v>
       </c>
@@ -11600,54 +6342,10 @@
         <v>2936</v>
       </c>
       <c r="P120">
-        <f t="shared" si="11"/>
-        <v>81.059977794223457</v>
-      </c>
-      <c r="Q120">
-        <f t="shared" si="12"/>
-        <v>1.1999999999999924</v>
-      </c>
-      <c r="R120">
-        <f t="shared" si="13"/>
-        <v>87</v>
-      </c>
-      <c r="S120">
-        <f t="shared" si="14"/>
-        <v>0.20824067732723869</v>
-      </c>
-      <c r="T120">
-        <f t="shared" si="15"/>
-        <v>-3.0199388888888772E-2</v>
-      </c>
-      <c r="U120">
-        <f t="shared" si="16"/>
-        <v>0.19544141111111124</v>
-      </c>
-      <c r="V120">
-        <f t="shared" si="17"/>
-        <v>0.58632423333333372</v>
-      </c>
-      <c r="W120">
-        <f t="shared" si="18"/>
-        <v>389.26101679376598</v>
-      </c>
-      <c r="X120">
-        <f t="shared" si="19"/>
-        <v>-39.73590341232061</v>
-      </c>
-      <c r="Y120">
-        <f t="shared" si="20"/>
-        <v>445.14619243379929</v>
-      </c>
-      <c r="Z120">
-        <f t="shared" si="21"/>
-        <v>108.01532053340007</v>
-      </c>
-      <c r="AA120">
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>0.31452960000000002</v>
       </c>
@@ -11694,54 +6392,10 @@
         <v>5911</v>
       </c>
       <c r="P121">
-        <f t="shared" si="11"/>
-        <v>167.93964630187835</v>
-      </c>
-      <c r="Q121">
-        <f t="shared" si="12"/>
-        <v>1.919999999999997</v>
-      </c>
-      <c r="R121">
-        <f t="shared" si="13"/>
-        <v>180.6</v>
-      </c>
-      <c r="S121">
-        <f t="shared" si="14"/>
-        <v>0.28127293834053807</v>
-      </c>
-      <c r="T121">
-        <f t="shared" si="15"/>
-        <v>-8.547091111111349E-3</v>
-      </c>
-      <c r="U121">
-        <f t="shared" si="16"/>
-        <v>0.24786305555555566</v>
-      </c>
-      <c r="V121">
-        <f t="shared" si="17"/>
-        <v>0.74358916666666697</v>
-      </c>
-      <c r="W121">
-        <f t="shared" si="18"/>
-        <v>597.07004624296019</v>
-      </c>
-      <c r="X121">
-        <f t="shared" si="19"/>
-        <v>-224.63782999855562</v>
-      </c>
-      <c r="Y121">
-        <f t="shared" si="20"/>
-        <v>728.62815152184135</v>
-      </c>
-      <c r="Z121">
-        <f t="shared" si="21"/>
-        <v>156.8070182123418</v>
-      </c>
-      <c r="AA121">
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>0.32307673999999997</v>
       </c>
@@ -11788,54 +6442,10 @@
         <v>6125</v>
       </c>
       <c r="P122">
-        <f t="shared" si="11"/>
-        <v>165.44549313897917</v>
-      </c>
-      <c r="Q122">
-        <f t="shared" si="12"/>
-        <v>-0.48000000000001819</v>
-      </c>
-      <c r="R122">
-        <f t="shared" si="13"/>
-        <v>179.4</v>
-      </c>
-      <c r="S122">
-        <f t="shared" si="14"/>
-        <v>0.29706377227401631</v>
-      </c>
-      <c r="T122">
-        <f t="shared" si="15"/>
-        <v>2.9059840000000281E-2</v>
-      </c>
-      <c r="U122">
-        <f t="shared" si="16"/>
-        <v>0.24273485333333333</v>
-      </c>
-      <c r="V122">
-        <f t="shared" si="17"/>
-        <v>0.72820456</v>
-      </c>
-      <c r="W122">
-        <f t="shared" si="18"/>
-        <v>556.93594635420448</v>
-      </c>
-      <c r="X122">
-        <f t="shared" si="19"/>
-        <v>-16.517640840418032</v>
-      </c>
-      <c r="Y122">
-        <f t="shared" si="20"/>
-        <v>739.07804147779575</v>
-      </c>
-      <c r="Z122">
-        <f t="shared" si="21"/>
-        <v>166.18956629439398</v>
-      </c>
-      <c r="AA122">
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>0.18803400000000001</v>
       </c>
@@ -11882,54 +6492,10 @@
         <v>5459</v>
       </c>
       <c r="P123">
-        <f t="shared" si="11"/>
-        <v>155.05318829356594</v>
-      </c>
-      <c r="Q123">
-        <f t="shared" si="12"/>
-        <v>-0.24000000000000909</v>
-      </c>
-      <c r="R123">
-        <f t="shared" si="13"/>
-        <v>168</v>
-      </c>
-      <c r="S123">
-        <f t="shared" si="14"/>
-        <v>0.23686141588566112</v>
-      </c>
-      <c r="T123">
-        <f t="shared" si="15"/>
-        <v>9.116802222222312E-3</v>
-      </c>
-      <c r="U123">
-        <f t="shared" si="16"/>
-        <v>0.20056960222222234</v>
-      </c>
-      <c r="V123">
-        <f t="shared" si="17"/>
-        <v>0.60170880666666704</v>
-      </c>
-      <c r="W123">
-        <f t="shared" si="18"/>
-        <v>654.61564397813936</v>
-      </c>
-      <c r="X123">
-        <f t="shared" si="19"/>
-        <v>-26.325019908297044</v>
-      </c>
-      <c r="Y123">
-        <f t="shared" si="20"/>
-        <v>837.61446469771306</v>
-      </c>
-      <c r="Z123">
-        <f t="shared" si="21"/>
-        <v>202.87886540378676</v>
-      </c>
-      <c r="AA123">
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>0.21880327333333299</v>
       </c>
@@ -11976,54 +6542,10 @@
         <v>12466</v>
       </c>
       <c r="P124">
-        <f t="shared" si="11"/>
-        <v>358.74236326366588</v>
-      </c>
-      <c r="Q124">
-        <f t="shared" si="12"/>
-        <v>4.0799999999999876</v>
-      </c>
-      <c r="R124">
-        <f t="shared" si="13"/>
-        <v>385.8</v>
-      </c>
-      <c r="S124">
-        <f t="shared" si="14"/>
-        <v>0.30002457841449209</v>
-      </c>
-      <c r="T124">
-        <f t="shared" si="15"/>
-        <v>1.0256377777777603E-2</v>
-      </c>
-      <c r="U124">
-        <f t="shared" si="16"/>
-        <v>0.25470071777777764</v>
-      </c>
-      <c r="V124">
-        <f t="shared" si="17"/>
-        <v>0.76410215333333298</v>
-      </c>
-      <c r="W124">
-        <f t="shared" si="18"/>
-        <v>1195.7099153658457</v>
-      </c>
-      <c r="X124">
-        <f t="shared" si="19"/>
-        <v>397.80125970399462</v>
-      </c>
-      <c r="Y124">
-        <f t="shared" si="20"/>
-        <v>1514.7189350938713</v>
-      </c>
-      <c r="Z124">
-        <f t="shared" si="21"/>
-        <v>333.37427317637133</v>
-      </c>
-      <c r="AA124">
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>0.27692294000000001</v>
       </c>
@@ -12070,54 +6592,10 @@
         <v>12911</v>
       </c>
       <c r="P125">
-        <f t="shared" si="11"/>
-        <v>357.07959448839978</v>
-      </c>
-      <c r="Q125">
-        <f t="shared" si="12"/>
-        <v>2.1599999999999757</v>
-      </c>
-      <c r="R125">
-        <f t="shared" si="13"/>
-        <v>385.2</v>
-      </c>
-      <c r="S125">
-        <f t="shared" si="14"/>
-        <v>0.30594619454444633</v>
-      </c>
-      <c r="T125">
-        <f t="shared" si="15"/>
-        <v>-4.4444424444444373E-2</v>
-      </c>
-      <c r="U125">
-        <f t="shared" si="16"/>
-        <v>0.28717938888888872</v>
-      </c>
-      <c r="V125">
-        <f t="shared" si="17"/>
-        <v>0.86153816666666616</v>
-      </c>
-      <c r="W125">
-        <f t="shared" si="18"/>
-        <v>1167.1320018217291</v>
-      </c>
-      <c r="X125">
-        <f t="shared" si="19"/>
-        <v>-48.600021870009371</v>
-      </c>
-      <c r="Y125">
-        <f t="shared" si="20"/>
-        <v>1341.3218876548135</v>
-      </c>
-      <c r="Z125">
-        <f t="shared" si="21"/>
-        <v>301.56992464446859</v>
-      </c>
-      <c r="AA125">
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>0.22051268666666701</v>
       </c>
@@ -12164,54 +6642,10 @@
         <v>12389</v>
       </c>
       <c r="P126">
-        <f t="shared" si="11"/>
-        <v>349.18144280588569</v>
-      </c>
-      <c r="Q126">
-        <f t="shared" si="12"/>
-        <v>-0.96000000000003638</v>
-      </c>
-      <c r="R126">
-        <f t="shared" si="13"/>
-        <v>378.59999999999997</v>
-      </c>
-      <c r="S126">
-        <f t="shared" si="14"/>
-        <v>0.31581542774397769</v>
-      </c>
-      <c r="T126">
-        <f t="shared" si="15"/>
-        <v>2.1652380000000287E-2</v>
-      </c>
-      <c r="U126">
-        <f t="shared" si="16"/>
-        <v>0.26267799333333336</v>
-      </c>
-      <c r="V126">
-        <f t="shared" si="17"/>
-        <v>0.78803398000000002</v>
-      </c>
-      <c r="W126">
-        <f t="shared" si="18"/>
-        <v>1105.650364519104</v>
-      </c>
-      <c r="X126">
-        <f t="shared" si="19"/>
-        <v>-44.336927395511424</v>
-      </c>
-      <c r="Y126">
-        <f t="shared" si="20"/>
-        <v>1441.308406523282</v>
-      </c>
-      <c r="Z126">
-        <f t="shared" si="21"/>
-        <v>332.82828742994064</v>
-      </c>
-      <c r="AA126">
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>0.497041384615385</v>
       </c>
@@ -12258,54 +6692,10 @@
         <v>4623</v>
       </c>
       <c r="P127">
-        <f t="shared" si="11"/>
-        <v>2.8778690341143354</v>
-      </c>
-      <c r="Q127">
-        <f t="shared" si="12"/>
-        <v>1.6615384615383995</v>
-      </c>
-      <c r="R127">
-        <f t="shared" si="13"/>
-        <v>2.0769230769229998</v>
-      </c>
-      <c r="S127">
-        <f t="shared" si="14"/>
-        <v>0.57165648524643686</v>
-      </c>
-      <c r="T127">
-        <f t="shared" si="15"/>
-        <v>0.32873110256410254</v>
-      </c>
-      <c r="U127">
-        <f t="shared" si="16"/>
-        <v>0.33070348717948722</v>
-      </c>
-      <c r="V127">
-        <f t="shared" si="17"/>
-        <v>0.99211046153846161</v>
-      </c>
-      <c r="W127">
-        <f t="shared" si="18"/>
-        <v>5.0342628980649238</v>
-      </c>
-      <c r="X127">
-        <f t="shared" si="19"/>
-        <v>5.0543999292382127</v>
-      </c>
-      <c r="Y127">
-        <f t="shared" si="20"/>
-        <v>6.2803180415081714</v>
-      </c>
-      <c r="Z127">
-        <f t="shared" si="21"/>
-        <v>-0.52568588051144471</v>
-      </c>
-      <c r="AA127">
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>0.56213023076923097</v>
       </c>
@@ -12352,54 +6742,10 @@
         <v>3881</v>
       </c>
       <c r="P128">
-        <f t="shared" si="11"/>
-        <v>0.47964483901905158</v>
-      </c>
-      <c r="Q128">
-        <f t="shared" si="12"/>
-        <v>1.3846153846153706</v>
-      </c>
-      <c r="R128">
-        <f t="shared" si="13"/>
-        <v>-0.34615384615385852</v>
-      </c>
-      <c r="S128">
-        <f t="shared" si="14"/>
-        <v>0.66958952465772725</v>
-      </c>
-      <c r="T128">
-        <f t="shared" si="15"/>
-        <v>0.36160414871794871</v>
-      </c>
-      <c r="U128">
-        <f t="shared" si="16"/>
-        <v>0.39907946410256412</v>
-      </c>
-      <c r="V128">
-        <f t="shared" si="17"/>
-        <v>1.1972383923076924</v>
-      </c>
-      <c r="W128">
-        <f t="shared" si="18"/>
-        <v>0.71632667680132944</v>
-      </c>
-      <c r="X128">
-        <f t="shared" si="19"/>
-        <v>3.8290915342770879</v>
-      </c>
-      <c r="Y128">
-        <f t="shared" si="20"/>
-        <v>-0.86738075318477525</v>
-      </c>
-      <c r="Z128">
-        <f t="shared" si="21"/>
-        <v>-0.38164753140128671</v>
-      </c>
-      <c r="AA128">
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>0.34319530769230799</v>
       </c>
@@ -12446,54 +6792,10 @@
         <v>3060</v>
       </c>
       <c r="P129">
-        <f t="shared" si="11"/>
-        <v>1.9185793560764557</v>
-      </c>
-      <c r="Q129">
-        <f t="shared" si="12"/>
-        <v>9.355479354174652E-14</v>
-      </c>
-      <c r="R129">
-        <f t="shared" si="13"/>
-        <v>2.0769230769231939</v>
-      </c>
-      <c r="S129">
-        <f t="shared" si="14"/>
-        <v>0.40425906411160212</v>
-      </c>
-      <c r="T129">
-        <f t="shared" si="15"/>
-        <v>0.2268244589743591</v>
-      </c>
-      <c r="U129">
-        <f t="shared" si="16"/>
-        <v>0.23668638974358991</v>
-      </c>
-      <c r="V129">
-        <f t="shared" si="17"/>
-        <v>0.71005916923076973</v>
-      </c>
-      <c r="W129">
-        <f t="shared" si="18"/>
-        <v>4.7459154942950184</v>
-      </c>
-      <c r="X129">
-        <f t="shared" si="19"/>
-        <v>4.1245460901693249E-13</v>
-      </c>
-      <c r="Y129">
-        <f t="shared" si="20"/>
-        <v>8.7750000292504886</v>
-      </c>
-      <c r="Z129">
-        <f t="shared" si="21"/>
-        <v>-0.9685000357283331</v>
-      </c>
-      <c r="AA129">
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>0.35327611111111101</v>
       </c>
@@ -12540,54 +6842,10 @@
         <v>3928</v>
       </c>
       <c r="P130">
-        <f t="shared" si="11"/>
-        <v>73.785364402434183</v>
-      </c>
-      <c r="Q130">
-        <f t="shared" si="12"/>
-        <v>127</v>
-      </c>
-      <c r="R130">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="S130">
-        <f t="shared" si="14"/>
-        <v>0.38572232624307684</v>
-      </c>
-      <c r="T130">
-        <f t="shared" si="15"/>
-        <v>-0.15242203703703702</v>
-      </c>
-      <c r="U130">
-        <f t="shared" si="16"/>
-        <v>0.410256351851852</v>
-      </c>
-      <c r="V130">
-        <f t="shared" si="17"/>
-        <v>1.2307690555555559</v>
-      </c>
-      <c r="W130">
-        <f t="shared" si="18"/>
-        <v>191.29140156625436</v>
-      </c>
-      <c r="X130">
-        <f t="shared" si="19"/>
-        <v>-833.2128507713112</v>
-      </c>
-      <c r="Y130">
-        <f t="shared" si="20"/>
-        <v>1.2187501735026285</v>
-      </c>
-      <c r="Z130">
-        <f t="shared" si="21"/>
-        <v>-0.22343754535048352</v>
-      </c>
-      <c r="AA130">
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>0.29230766666666702</v>
       </c>
@@ -12634,54 +6892,10 @@
         <v>7508</v>
       </c>
       <c r="P131">
-        <f t="shared" ref="P131:P177" si="22">(4*(L131+J131)*COS(RADIANS(30)))/15</f>
-        <v>86.048284120021833</v>
-      </c>
-      <c r="Q131">
-        <f t="shared" ref="Q131:Q177" si="23">(4*(L131+J131)*SIN(RADIANS(30))-4*K131)/15</f>
-        <v>136.55999999999997</v>
-      </c>
-      <c r="R131">
-        <f t="shared" ref="R131:R177" si="24">(J131+K131+L131)/6</f>
-        <v>7.7999999999999927</v>
-      </c>
-      <c r="S131">
-        <f t="shared" ref="S131:S177" si="25">(2*(A131+C131)*COS(RADIANS(30)))/3</f>
-        <v>0.45398479646046114</v>
-      </c>
-      <c r="T131">
-        <f t="shared" ref="T131:T177" si="26">(2*(A131+C131)*SIN(RADIANS(30))-2*B131)/3</f>
-        <v>-8.2051266666666664E-2</v>
-      </c>
-      <c r="U131">
-        <f t="shared" ref="U131:U177" si="27">(A131+B131+C131)/3</f>
-        <v>0.4341880000000003</v>
-      </c>
-      <c r="V131">
-        <f t="shared" ref="V131:V177" si="28">A131+B131+C131</f>
-        <v>1.3025640000000009</v>
-      </c>
-      <c r="W131">
-        <f t="shared" ref="W131:W177" si="29">P131/S131</f>
-        <v>189.54001277334854</v>
-      </c>
-      <c r="X131">
-        <f t="shared" ref="X131:X177" si="30">Q131/T131</f>
-        <v>-1664.3253120609957</v>
-      </c>
-      <c r="Y131">
-        <f t="shared" ref="Y131:Y177" si="31">R131/U131</f>
-        <v>17.96456834366677</v>
-      </c>
-      <c r="Z131">
-        <f t="shared" ref="Z131:Z177" si="32">F131/U131</f>
-        <v>4.0704333913726973</v>
-      </c>
-      <c r="AA131">
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>9.7435820000000006E-2</v>
       </c>
@@ -12728,54 +6942,10 @@
         <v>8171</v>
       </c>
       <c r="P132">
-        <f t="shared" si="22"/>
-        <v>75.240287080792029</v>
-      </c>
-      <c r="Q132">
-        <f t="shared" si="23"/>
-        <v>126.47999999999999</v>
-      </c>
-      <c r="R132">
-        <f t="shared" si="24"/>
-        <v>2.4000000000000057</v>
-      </c>
-      <c r="S132">
-        <f t="shared" si="25"/>
-        <v>0.3019983888737815</v>
-      </c>
-      <c r="T132">
-        <f t="shared" si="26"/>
-        <v>-0.30313417111111102</v>
-      </c>
-      <c r="U132">
-        <f t="shared" si="27"/>
-        <v>0.41310536222222199</v>
-      </c>
-      <c r="V132">
-        <f t="shared" si="28"/>
-        <v>1.2393160866666659</v>
-      </c>
-      <c r="W132">
-        <f t="shared" si="29"/>
-        <v>249.14135257932875</v>
-      </c>
-      <c r="X132">
-        <f t="shared" si="30"/>
-        <v>-417.24098453301696</v>
-      </c>
-      <c r="Y132">
-        <f t="shared" si="31"/>
-        <v>5.8096558880031495</v>
-      </c>
-      <c r="Z132">
-        <f t="shared" si="32"/>
-        <v>1.4830760286050897</v>
-      </c>
-      <c r="AA132">
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>0.29230753333333298</v>
       </c>
@@ -12822,54 +6992,10 @@
         <v>7386</v>
       </c>
       <c r="P133">
-        <f t="shared" si="22"/>
-        <v>81.475669988039982</v>
-      </c>
-      <c r="Q133">
-        <f t="shared" si="23"/>
-        <v>137.75999999999996</v>
-      </c>
-      <c r="R133">
-        <f t="shared" si="24"/>
-        <v>2.1000000000000036</v>
-      </c>
-      <c r="S133">
-        <f t="shared" si="25"/>
-        <v>0.51912164628052426</v>
-      </c>
-      <c r="T133">
-        <f t="shared" si="26"/>
-        <v>4.3304888888888948E-2</v>
-      </c>
-      <c r="U133">
-        <f t="shared" si="27"/>
-        <v>0.42792008888888899</v>
-      </c>
-      <c r="V133">
-        <f t="shared" si="28"/>
-        <v>1.283760266666667</v>
-      </c>
-      <c r="W133">
-        <f t="shared" si="29"/>
-        <v>156.94909000965055</v>
-      </c>
-      <c r="X133">
-        <f t="shared" si="30"/>
-        <v>3181.165072457813</v>
-      </c>
-      <c r="Y133">
-        <f t="shared" si="31"/>
-        <v>4.9074583188013783</v>
-      </c>
-      <c r="Z133">
-        <f t="shared" si="32"/>
-        <v>4.106685755035044</v>
-      </c>
-      <c r="AA133">
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>0.17628188750000001</v>
       </c>
@@ -12916,54 +7042,10 @@
         <v>2752</v>
       </c>
       <c r="P134">
-        <f t="shared" si="22"/>
-        <v>77.552574908896489</v>
-      </c>
-      <c r="Q134">
-        <f t="shared" si="23"/>
-        <v>1.1249999999999925</v>
-      </c>
-      <c r="R134">
-        <f t="shared" si="24"/>
-        <v>83.25</v>
-      </c>
-      <c r="S134">
-        <f t="shared" si="25"/>
-        <v>0.30162821160731151</v>
-      </c>
-      <c r="T134">
-        <f t="shared" si="26"/>
-        <v>7.4786291666666576E-3</v>
-      </c>
-      <c r="U134">
-        <f t="shared" si="27"/>
-        <v>0.25747837916666666</v>
-      </c>
-      <c r="V134">
-        <f t="shared" si="28"/>
-        <v>0.77243513750000004</v>
-      </c>
-      <c r="W134">
-        <f t="shared" si="29"/>
-        <v>257.11313439693055</v>
-      </c>
-      <c r="X134">
-        <f t="shared" si="30"/>
-        <v>150.42863804696745</v>
-      </c>
-      <c r="Y134">
-        <f t="shared" si="31"/>
-        <v>323.32811892571368</v>
-      </c>
-      <c r="Z134">
-        <f t="shared" si="32"/>
-        <v>69.003366641901366</v>
-      </c>
-      <c r="AA134">
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>0.16346139374999999</v>
       </c>
@@ -13010,54 +7092,10 @@
         <v>2913</v>
       </c>
       <c r="P135">
-        <f t="shared" si="22"/>
-        <v>74.434883455272512</v>
-      </c>
-      <c r="Q135">
-        <f t="shared" si="23"/>
-        <v>0.22499999999999243</v>
-      </c>
-      <c r="R135">
-        <f t="shared" si="24"/>
-        <v>80.4375</v>
-      </c>
-      <c r="S135">
-        <f t="shared" si="25"/>
-        <v>0.29422636825838872</v>
-      </c>
-      <c r="T135">
-        <f t="shared" si="26"/>
-        <v>-1.7093952083333346E-2</v>
-      </c>
-      <c r="U135">
-        <f t="shared" si="27"/>
-        <v>0.26335448541666667</v>
-      </c>
-      <c r="V135">
-        <f t="shared" si="28"/>
-        <v>0.79006345624999996</v>
-      </c>
-      <c r="W135">
-        <f t="shared" si="29"/>
-        <v>252.98508728457682</v>
-      </c>
-      <c r="X135">
-        <f t="shared" si="30"/>
-        <v>-13.16255005882274</v>
-      </c>
-      <c r="Y135">
-        <f t="shared" si="31"/>
-        <v>305.43432694049505</v>
-      </c>
-      <c r="Z135">
-        <f t="shared" si="32"/>
-        <v>75.489980618882711</v>
-      </c>
-      <c r="AA135">
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>0.28365356250000001</v>
       </c>
@@ -13104,54 +7142,10 @@
         <v>2925</v>
       </c>
       <c r="P136">
-        <f t="shared" si="22"/>
-        <v>75.21430631867851</v>
-      </c>
-      <c r="Q136">
-        <f t="shared" si="23"/>
-        <v>2.4749999999999925</v>
-      </c>
-      <c r="R136">
-        <f t="shared" si="24"/>
-        <v>79.875</v>
-      </c>
-      <c r="S136">
-        <f t="shared" si="25"/>
-        <v>0.29237581269962948</v>
-      </c>
-      <c r="T136">
-        <f t="shared" si="26"/>
-        <v>-3.6324745833333373E-2</v>
-      </c>
-      <c r="U136">
-        <f t="shared" si="27"/>
-        <v>0.27136725416666668</v>
-      </c>
-      <c r="V136">
-        <f t="shared" si="28"/>
-        <v>0.81410176249999999</v>
-      </c>
-      <c r="W136">
-        <f t="shared" si="29"/>
-        <v>257.25214963643202</v>
-      </c>
-      <c r="X136">
-        <f t="shared" si="30"/>
-        <v>-68.135370068544589</v>
-      </c>
-      <c r="Y136">
-        <f t="shared" si="31"/>
-        <v>294.34280950841202</v>
-      </c>
-      <c r="Z136">
-        <f t="shared" si="32"/>
-        <v>64.502071385701001</v>
-      </c>
-      <c r="AA136">
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>0.34615357142857101</v>
       </c>
@@ -13198,54 +7192,10 @@
         <v>5701</v>
       </c>
       <c r="P137">
-        <f t="shared" si="22"/>
-        <v>161.22918660169719</v>
-      </c>
-      <c r="Q137">
-        <f t="shared" si="23"/>
-        <v>-0.51428571428574898</v>
-      </c>
-      <c r="R137">
-        <f t="shared" si="24"/>
-        <v>174.8571428571428</v>
-      </c>
-      <c r="S137">
-        <f t="shared" si="25"/>
-        <v>0.33837353649312668</v>
-      </c>
-      <c r="T137">
-        <f t="shared" si="26"/>
-        <v>8.5469999999996382E-3</v>
-      </c>
-      <c r="U137">
-        <f t="shared" si="27"/>
-        <v>0.28876657857142868</v>
-      </c>
-      <c r="V137">
-        <f t="shared" si="28"/>
-        <v>0.86629973571428609</v>
-      </c>
-      <c r="W137">
-        <f t="shared" si="29"/>
-        <v>476.48284872588493</v>
-      </c>
-      <c r="X137">
-        <f t="shared" si="30"/>
-        <v>-60.17148874292392</v>
-      </c>
-      <c r="Y137">
-        <f t="shared" si="31"/>
-        <v>605.53109616142967</v>
-      </c>
-      <c r="Z137">
-        <f t="shared" si="32"/>
-        <v>135.42079624816094</v>
-      </c>
-      <c r="AA137">
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>0.208791007142857</v>
       </c>
@@ -13292,54 +7242,10 @@
         <v>5842</v>
       </c>
       <c r="P138">
-        <f t="shared" si="22"/>
-        <v>160.33841761494745</v>
-      </c>
-      <c r="Q138">
-        <f t="shared" si="23"/>
-        <v>-1.5158245029548804E-14</v>
-      </c>
-      <c r="R138">
-        <f t="shared" si="24"/>
-        <v>173.57142857142853</v>
-      </c>
-      <c r="S138">
-        <f t="shared" si="25"/>
-        <v>0.29078968407965028</v>
-      </c>
-      <c r="T138">
-        <f t="shared" si="26"/>
-        <v>-1.6483550000000385E-2</v>
-      </c>
-      <c r="U138">
-        <f t="shared" si="27"/>
-        <v>0.26007302857142872</v>
-      </c>
-      <c r="V138">
-        <f t="shared" si="28"/>
-        <v>0.78021908571428611</v>
-      </c>
-      <c r="W138">
-        <f t="shared" si="29"/>
-        <v>551.3896344790179</v>
-      </c>
-      <c r="X138">
-        <f t="shared" si="30"/>
-        <v>9.1959832860933786E-13</v>
-      </c>
-      <c r="Y138">
-        <f t="shared" si="31"/>
-        <v>667.39496027269649</v>
-      </c>
-      <c r="Z138">
-        <f t="shared" si="32"/>
-        <v>158.96359220421175</v>
-      </c>
-      <c r="AA138">
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>0.40476179285714298</v>
       </c>
@@ -13386,54 +7292,10 @@
         <v>5918</v>
       </c>
       <c r="P139">
-        <f t="shared" si="22"/>
-        <v>150.9853432540755</v>
-      </c>
-      <c r="Q139">
-        <f t="shared" si="23"/>
-        <v>5.3999999999999853</v>
-      </c>
-      <c r="R139">
-        <f t="shared" si="24"/>
-        <v>160.0714285714285</v>
-      </c>
-      <c r="S139">
-        <f t="shared" si="25"/>
-        <v>0.31934012501915404</v>
-      </c>
-      <c r="T139">
-        <f t="shared" si="26"/>
-        <v>-5.6166130952380731E-2</v>
-      </c>
-      <c r="U139">
-        <f t="shared" si="27"/>
-        <v>0.3046397261904763</v>
-      </c>
-      <c r="V139">
-        <f t="shared" si="28"/>
-        <v>0.9139191785714289</v>
-      </c>
-      <c r="W139">
-        <f t="shared" si="29"/>
-        <v>472.80417155538908</v>
-      </c>
-      <c r="X139">
-        <f t="shared" si="30"/>
-        <v>-96.143350243908756</v>
-      </c>
-      <c r="Y139">
-        <f t="shared" si="31"/>
-        <v>525.44502508955009</v>
-      </c>
-      <c r="Z139">
-        <f t="shared" si="32"/>
-        <v>120.73043189150391</v>
-      </c>
-      <c r="AA139">
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>0.20192288124999999</v>
       </c>
@@ -13480,54 +7342,10 @@
         <v>14168</v>
       </c>
       <c r="P140">
-        <f t="shared" si="22"/>
-        <v>345.67403992055876</v>
-      </c>
-      <c r="Q140">
-        <f t="shared" si="23"/>
-        <v>6.07499999999997</v>
-      </c>
-      <c r="R140">
-        <f t="shared" si="24"/>
-        <v>370.40625</v>
-      </c>
-      <c r="S140">
-        <f t="shared" si="25"/>
-        <v>0.34048846744153499</v>
-      </c>
-      <c r="T140">
-        <f t="shared" si="26"/>
-        <v>-5.9828900000000039E-2</v>
-      </c>
-      <c r="U140">
-        <f t="shared" si="27"/>
-        <v>0.3247861125</v>
-      </c>
-      <c r="V140">
-        <f t="shared" si="28"/>
-        <v>0.9743583375</v>
-      </c>
-      <c r="W140">
-        <f t="shared" si="29"/>
-        <v>1015.2298035759879</v>
-      </c>
-      <c r="X140">
-        <f t="shared" si="30"/>
-        <v>-101.53955696995877</v>
-      </c>
-      <c r="Y140">
-        <f t="shared" si="31"/>
-        <v>1140.4620941112437</v>
-      </c>
-      <c r="Z140">
-        <f t="shared" si="32"/>
-        <v>252.31605307631497</v>
-      </c>
-      <c r="AA140">
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>0.34615374999999998</v>
       </c>
@@ -13574,54 +7392,10 @@
         <v>13898</v>
       </c>
       <c r="P141">
-        <f t="shared" si="22"/>
-        <v>345.28432848885575</v>
-      </c>
-      <c r="Q141">
-        <f t="shared" si="23"/>
-        <v>1.3499999999999697</v>
-      </c>
-      <c r="R141">
-        <f t="shared" si="24"/>
-        <v>372.9375</v>
-      </c>
-      <c r="S141">
-        <f t="shared" si="25"/>
-        <v>0.33771278385362219</v>
-      </c>
-      <c r="T141">
-        <f t="shared" si="26"/>
-        <v>-1.602533333333378E-3</v>
-      </c>
-      <c r="U141">
-        <f t="shared" si="27"/>
-        <v>0.29326911666666666</v>
-      </c>
-      <c r="V141">
-        <f t="shared" si="28"/>
-        <v>0.87980734999999999</v>
-      </c>
-      <c r="W141">
-        <f t="shared" si="29"/>
-        <v>1022.4200711291858</v>
-      </c>
-      <c r="X141">
-        <f t="shared" si="30"/>
-        <v>-842.41617439050594</v>
-      </c>
-      <c r="Y141">
-        <f t="shared" si="31"/>
-        <v>1271.6562324695287</v>
-      </c>
-      <c r="Z141">
-        <f t="shared" si="32"/>
-        <v>280.90666666969764</v>
-      </c>
-      <c r="AA141">
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>1.2111617058823501</v>
       </c>
@@ -13668,54 +7442,10 @@
         <v>4608</v>
       </c>
       <c r="P142">
-        <f t="shared" si="22"/>
-        <v>2.934297838704885</v>
-      </c>
-      <c r="Q142">
-        <f t="shared" si="23"/>
-        <v>1.6941176470588022</v>
-      </c>
-      <c r="R142">
-        <f t="shared" si="24"/>
-        <v>2.1176470588235028</v>
-      </c>
-      <c r="S142">
-        <f t="shared" si="25"/>
-        <v>1.2844527435585809</v>
-      </c>
-      <c r="T142">
-        <f t="shared" si="26"/>
-        <v>0.74157913725489977</v>
-      </c>
-      <c r="U142">
-        <f t="shared" si="27"/>
-        <v>0.74157913725489999</v>
-      </c>
-      <c r="V142">
-        <f t="shared" si="28"/>
-        <v>2.2247374117646999</v>
-      </c>
-      <c r="W142">
-        <f t="shared" si="29"/>
-        <v>2.2844731761601462</v>
-      </c>
-      <c r="X142">
-        <f t="shared" si="30"/>
-        <v>2.2844731761601467</v>
-      </c>
-      <c r="Y142">
-        <f t="shared" si="31"/>
-        <v>2.8555914702001823</v>
-      </c>
-      <c r="Z142">
-        <f t="shared" si="32"/>
-        <v>1.0970230564685839</v>
-      </c>
-      <c r="AA142">
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>1.11010617647059</v>
       </c>
@@ -13762,54 +7492,10 @@
         <v>4125</v>
       </c>
       <c r="P143">
-        <f t="shared" si="22"/>
-        <v>2.2007233790284881</v>
-      </c>
-      <c r="Q143">
-        <f t="shared" si="23"/>
-        <v>1.2705882352940001</v>
-      </c>
-      <c r="R143">
-        <f t="shared" si="24"/>
-        <v>1.5882352941175004</v>
-      </c>
-      <c r="S143">
-        <f t="shared" si="25"/>
-        <v>1.2670365991088919</v>
-      </c>
-      <c r="T143">
-        <f t="shared" si="26"/>
-        <v>0.73152392156862645</v>
-      </c>
-      <c r="U143">
-        <f t="shared" si="27"/>
-        <v>0.73152392156862656</v>
-      </c>
-      <c r="V143">
-        <f t="shared" si="28"/>
-        <v>2.1945717647058798</v>
-      </c>
-      <c r="W143">
-        <f t="shared" si="29"/>
-        <v>1.7369059272449265</v>
-      </c>
-      <c r="X143">
-        <f t="shared" si="30"/>
-        <v>1.7369059272449265</v>
-      </c>
-      <c r="Y143">
-        <f t="shared" si="31"/>
-        <v>2.1711324090561583</v>
-      </c>
-      <c r="Z143">
-        <f t="shared" si="32"/>
-        <v>1.0397311789624255</v>
-      </c>
-      <c r="AA143">
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>0.155354429411765</v>
       </c>
@@ -13856,54 +7542,10 @@
         <v>343</v>
       </c>
       <c r="P144">
-        <f t="shared" si="22"/>
-        <v>0.7335744596762318</v>
-      </c>
-      <c r="Q144">
-        <f t="shared" si="23"/>
-        <v>0.42352941176470654</v>
-      </c>
-      <c r="R144">
-        <f t="shared" si="24"/>
-        <v>0.52941176470588325</v>
-      </c>
-      <c r="S144">
-        <f t="shared" si="25"/>
-        <v>0.15500500671551329</v>
-      </c>
-      <c r="T144">
-        <f t="shared" si="26"/>
-        <v>8.9492182352941319E-2</v>
-      </c>
-      <c r="U144">
-        <f t="shared" si="27"/>
-        <v>8.9492182352941332E-2</v>
-      </c>
-      <c r="V144">
-        <f t="shared" si="28"/>
-        <v>0.26847654705882401</v>
-      </c>
-      <c r="W144">
-        <f t="shared" si="29"/>
-        <v>4.7325855804296015</v>
-      </c>
-      <c r="X144">
-        <f t="shared" si="30"/>
-        <v>4.7325855804296015</v>
-      </c>
-      <c r="Y144">
-        <f t="shared" si="31"/>
-        <v>5.9157319755370015</v>
-      </c>
-      <c r="Z144">
-        <f t="shared" si="32"/>
-        <v>2.3662927902147972</v>
-      </c>
-      <c r="AA144">
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>1.22564133333333</v>
       </c>
@@ -13950,54 +7592,10 @@
         <v>1808</v>
       </c>
       <c r="P145">
-        <f t="shared" si="22"/>
-        <v>37.827989637304285</v>
-      </c>
-      <c r="Q145">
-        <f t="shared" si="23"/>
-        <v>84.24</v>
-      </c>
-      <c r="R145">
-        <f t="shared" si="24"/>
-        <v>-11.699999999999998</v>
-      </c>
-      <c r="S145">
-        <f t="shared" si="25"/>
-        <v>1.3797195341443811</v>
-      </c>
-      <c r="T145">
-        <f t="shared" si="26"/>
-        <v>-0.20854655555555679</v>
-      </c>
-      <c r="U145">
-        <f t="shared" si="27"/>
-        <v>1.2991454444444432</v>
-      </c>
-      <c r="V145">
-        <f t="shared" si="28"/>
-        <v>3.8974363333333297</v>
-      </c>
-      <c r="W145">
-        <f t="shared" si="29"/>
-        <v>27.417158850884086</v>
-      </c>
-      <c r="X145">
-        <f t="shared" si="30"/>
-        <v>-403.93858232560672</v>
-      </c>
-      <c r="Y145">
-        <f t="shared" si="31"/>
-        <v>-9.0059200453905284</v>
-      </c>
-      <c r="Z145">
-        <f t="shared" si="32"/>
-        <v>3.4520127718143669</v>
-      </c>
-      <c r="AA145">
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>1.0290594666666699</v>
       </c>
@@ -14044,54 +7642,10 @@
         <v>1275</v>
       </c>
       <c r="P146">
-        <f t="shared" si="22"/>
-        <v>32.839683311505915</v>
-      </c>
-      <c r="Q146">
-        <f t="shared" si="23"/>
-        <v>73.2</v>
-      </c>
-      <c r="R146">
-        <f t="shared" si="24"/>
-        <v>-10.199999999999998</v>
-      </c>
-      <c r="S146">
-        <f t="shared" si="25"/>
-        <v>1.187269059514332</v>
-      </c>
-      <c r="T146">
-        <f t="shared" si="26"/>
-        <v>-0.21139548888888671</v>
-      </c>
-      <c r="U146">
-        <f t="shared" si="27"/>
-        <v>1.1339029111111134</v>
-      </c>
-      <c r="V146">
-        <f t="shared" si="28"/>
-        <v>3.40170873333334</v>
-      </c>
-      <c r="W146">
-        <f t="shared" si="29"/>
-        <v>27.659849339407039</v>
-      </c>
-      <c r="X146">
-        <f t="shared" si="30"/>
-        <v>-346.27039765486785</v>
-      </c>
-      <c r="Y146">
-        <f t="shared" si="31"/>
-        <v>-8.9954791543880948</v>
-      </c>
-      <c r="Z146">
-        <f t="shared" si="32"/>
-        <v>3.3959403657350125</v>
-      </c>
-      <c r="AA146">
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>3.7606819999999999E-2</v>
       </c>
@@ -14138,54 +7692,10 @@
         <v>-51</v>
       </c>
       <c r="P147">
-        <f t="shared" si="22"/>
-        <v>-1.2470765814495917</v>
-      </c>
-      <c r="Q147">
-        <f t="shared" si="23"/>
-        <v>-1.68</v>
-      </c>
-      <c r="R147">
-        <f t="shared" si="24"/>
-        <v>-0.30000000000000004</v>
-      </c>
-      <c r="S147">
-        <f t="shared" si="25"/>
-        <v>3.8490002549967879E-2</v>
-      </c>
-      <c r="T147">
-        <f t="shared" si="26"/>
-        <v>-1.7663791111111136E-2</v>
-      </c>
-      <c r="U147">
-        <f t="shared" si="27"/>
-        <v>4.2165215555555559E-2</v>
-      </c>
-      <c r="V147">
-        <f t="shared" si="28"/>
-        <v>0.12649564666666668</v>
-      </c>
-      <c r="W147">
-        <f t="shared" si="29"/>
-        <v>-32.400012960005178</v>
-      </c>
-      <c r="X147">
-        <f t="shared" si="30"/>
-        <v>95.109820390891159</v>
-      </c>
-      <c r="Y147">
-        <f t="shared" si="31"/>
-        <v>-7.1148693549243101</v>
-      </c>
-      <c r="Z147">
-        <f t="shared" si="32"/>
-        <v>13.107170433849456</v>
-      </c>
-      <c r="AA147">
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>1.1674204705882401</v>
       </c>
@@ -14232,54 +7742,10 @@
         <v>7561</v>
       </c>
       <c r="P148">
-        <f t="shared" si="22"/>
-        <v>89.496084080500211</v>
-      </c>
-      <c r="Q148">
-        <f t="shared" si="23"/>
-        <v>119.85882352941177</v>
-      </c>
-      <c r="R148">
-        <f t="shared" si="24"/>
-        <v>21.970588235294219</v>
-      </c>
-      <c r="S148">
-        <f t="shared" si="25"/>
-        <v>1.341055111134742</v>
-      </c>
-      <c r="T148">
-        <f t="shared" si="26"/>
-        <v>-9.6531274509800077E-2</v>
-      </c>
-      <c r="U148">
-        <f t="shared" si="27"/>
-        <v>1.2096534313725502</v>
-      </c>
-      <c r="V148">
-        <f t="shared" si="28"/>
-        <v>3.6289602941176504</v>
-      </c>
-      <c r="W148">
-        <f t="shared" si="29"/>
-        <v>66.73557509860467</v>
-      </c>
-      <c r="X148">
-        <f t="shared" si="30"/>
-        <v>-1241.6579407872982</v>
-      </c>
-      <c r="Y148">
-        <f t="shared" si="31"/>
-        <v>18.162713108964592</v>
-      </c>
-      <c r="Z148">
-        <f t="shared" si="32"/>
-        <v>-0.67593497246213263</v>
-      </c>
-      <c r="AA148">
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>1.23982058823529</v>
       </c>
@@ -14326,54 +7792,10 @@
         <v>7933</v>
       </c>
       <c r="P149">
-        <f t="shared" si="22"/>
-        <v>91.696807459528856</v>
-      </c>
-      <c r="Q149">
-        <f t="shared" si="23"/>
-        <v>122.8235294117648</v>
-      </c>
-      <c r="R149">
-        <f t="shared" si="24"/>
-        <v>22.5</v>
-      </c>
-      <c r="S149">
-        <f t="shared" si="25"/>
-        <v>1.3584724442467444</v>
-      </c>
-      <c r="T149">
-        <f t="shared" si="26"/>
-        <v>-9.753615686274679E-2</v>
-      </c>
-      <c r="U149">
-        <f t="shared" si="27"/>
-        <v>1.2252397254901932</v>
-      </c>
-      <c r="V149">
-        <f t="shared" si="28"/>
-        <v>3.6757191764705799</v>
-      </c>
-      <c r="W149">
-        <f t="shared" si="29"/>
-        <v>67.499939250054908</v>
-      </c>
-      <c r="X149">
-        <f t="shared" si="30"/>
-        <v>-1259.2615227253877</v>
-      </c>
-      <c r="Y149">
-        <f t="shared" si="31"/>
-        <v>18.363753257345792</v>
-      </c>
-      <c r="Z149">
-        <f t="shared" si="32"/>
-        <v>-0.50458312871818101</v>
-      </c>
-      <c r="AA149">
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>8.7481088235294102E-2</v>
       </c>
@@ -14420,54 +7842,10 @@
         <v>-72</v>
       </c>
       <c r="P150">
-        <f t="shared" si="22"/>
-        <v>0.7335744596762318</v>
-      </c>
-      <c r="Q150">
-        <f t="shared" si="23"/>
-        <v>-1.6941176470588242</v>
-      </c>
-      <c r="R150">
-        <f t="shared" si="24"/>
-        <v>1.8529411764705899</v>
-      </c>
-      <c r="S150">
-        <f t="shared" si="25"/>
-        <v>8.0114913138586971E-2</v>
-      </c>
-      <c r="T150">
-        <f t="shared" si="26"/>
-        <v>-3.0165901960784078E-3</v>
-      </c>
-      <c r="U150">
-        <f t="shared" si="27"/>
-        <v>7.0889845098039209E-2</v>
-      </c>
-      <c r="V150">
-        <f t="shared" si="28"/>
-        <v>0.21266953529411761</v>
-      </c>
-      <c r="W150">
-        <f t="shared" si="29"/>
-        <v>9.1565281785584194</v>
-      </c>
-      <c r="X150">
-        <f t="shared" si="30"/>
-        <v>561.60019656007341</v>
-      </c>
-      <c r="Y150">
-        <f t="shared" si="31"/>
-        <v>26.138316057934816</v>
-      </c>
-      <c r="Z150">
-        <f t="shared" si="32"/>
-        <v>7.426600911698932</v>
-      </c>
-      <c r="AA150">
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>0.956731</v>
       </c>
@@ -14514,54 +7892,10 @@
         <v>1884</v>
       </c>
       <c r="P151">
-        <f t="shared" si="22"/>
-        <v>46.765371804359688</v>
-      </c>
-      <c r="Q151">
-        <f t="shared" si="23"/>
-        <v>1.7999999999999963</v>
-      </c>
-      <c r="R151">
-        <f t="shared" si="24"/>
-        <v>49.5</v>
-      </c>
-      <c r="S151">
-        <f t="shared" si="25"/>
-        <v>1.1278686537157576</v>
-      </c>
-      <c r="T151">
-        <f t="shared" si="26"/>
-        <v>-0.10950914583333342</v>
-      </c>
-      <c r="U151">
-        <f t="shared" si="27"/>
-        <v>1.0315174791666666</v>
-      </c>
-      <c r="V151">
-        <f t="shared" si="28"/>
-        <v>3.0945524375</v>
-      </c>
-      <c r="W151">
-        <f t="shared" si="29"/>
-        <v>41.463491028225143</v>
-      </c>
-      <c r="X151">
-        <f t="shared" si="30"/>
-        <v>-16.436983288496215</v>
-      </c>
-      <c r="Y151">
-        <f t="shared" si="31"/>
-        <v>47.987553288956029</v>
-      </c>
-      <c r="Z151">
-        <f t="shared" si="32"/>
-        <v>9.5593387404022643</v>
-      </c>
-      <c r="AA151">
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>0.91987081250000002</v>
       </c>
@@ -14608,54 +7942,10 @@
         <v>1759</v>
       </c>
       <c r="P152">
-        <f t="shared" si="22"/>
-        <v>49.883063257983665</v>
-      </c>
-      <c r="Q152">
-        <f t="shared" si="23"/>
-        <v>4.0499999999999963</v>
-      </c>
-      <c r="R152">
-        <f t="shared" si="24"/>
-        <v>51.46875</v>
-      </c>
-      <c r="S152">
-        <f t="shared" si="25"/>
-        <v>1.1232420573336064</v>
-      </c>
-      <c r="T152">
-        <f t="shared" si="26"/>
-        <v>-8.8675395833333434E-2</v>
-      </c>
-      <c r="U152">
-        <f t="shared" si="27"/>
-        <v>1.0170938541666665</v>
-      </c>
-      <c r="V152">
-        <f t="shared" si="28"/>
-        <v>3.0512815624999998</v>
-      </c>
-      <c r="W152">
-        <f t="shared" si="29"/>
-        <v>44.409896275071759</v>
-      </c>
-      <c r="X152">
-        <f t="shared" si="30"/>
-        <v>-45.672195336032381</v>
-      </c>
-      <c r="Y152">
-        <f t="shared" si="31"/>
-        <v>50.603737097762512</v>
-      </c>
-      <c r="Z152">
-        <f t="shared" si="32"/>
-        <v>9.3882683106207132</v>
-      </c>
-      <c r="AA152">
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>0.30448720000000001</v>
       </c>
@@ -14702,54 +7992,10 @@
         <v>542</v>
       </c>
       <c r="P153">
-        <f t="shared" si="22"/>
-        <v>13.639900109604911</v>
-      </c>
-      <c r="Q153">
-        <f t="shared" si="23"/>
-        <v>0.67499999999999905</v>
-      </c>
-      <c r="R153">
-        <f t="shared" si="24"/>
-        <v>14.34375</v>
-      </c>
-      <c r="S153">
-        <f t="shared" si="25"/>
-        <v>0.36547030533619457</v>
-      </c>
-      <c r="T153">
-        <f t="shared" si="26"/>
-        <v>-5.8226637500000046E-2</v>
-      </c>
-      <c r="U153">
-        <f t="shared" si="27"/>
-        <v>0.3456198875</v>
-      </c>
-      <c r="V153">
-        <f t="shared" si="28"/>
-        <v>1.0368596624999999</v>
-      </c>
-      <c r="W153">
-        <f t="shared" si="29"/>
-        <v>37.321500298246185</v>
-      </c>
-      <c r="X153">
-        <f t="shared" si="30"/>
-        <v>-11.592632323994298</v>
-      </c>
-      <c r="Y153">
-        <f t="shared" si="31"/>
-        <v>41.501518051388175</v>
-      </c>
-      <c r="Z153">
-        <f t="shared" si="32"/>
-        <v>11.801259555701927</v>
-      </c>
-      <c r="AA153">
         <v>4</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>0.82393166666666695</v>
       </c>
@@ -14796,54 +8042,10 @@
         <v>5302</v>
       </c>
       <c r="P154">
-        <f t="shared" si="22"/>
-        <v>140.50396150998733</v>
-      </c>
-      <c r="Q154">
-        <f t="shared" si="23"/>
-        <v>6.7199999999999971</v>
-      </c>
-      <c r="R154">
-        <f t="shared" si="24"/>
-        <v>147.9</v>
-      </c>
-      <c r="S154">
-        <f t="shared" si="25"/>
-        <v>0.91981281748282651</v>
-      </c>
-      <c r="T154">
-        <f t="shared" si="26"/>
-        <v>-0.18575484444444204</v>
-      </c>
-      <c r="U154">
-        <f t="shared" si="27"/>
-        <v>0.88945868888888791</v>
-      </c>
-      <c r="V154">
-        <f t="shared" si="28"/>
-        <v>2.6683760666666636</v>
-      </c>
-      <c r="W154">
-        <f t="shared" si="29"/>
-        <v>152.7527762599488</v>
-      </c>
-      <c r="X154">
-        <f t="shared" si="30"/>
-        <v>-36.176714637501156</v>
-      </c>
-      <c r="Y154">
-        <f t="shared" si="31"/>
-        <v>166.28090977980858</v>
-      </c>
-      <c r="Z154">
-        <f t="shared" si="32"/>
-        <v>31.678443325867111</v>
-      </c>
-      <c r="AA154">
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>0.88376053333333304</v>
       </c>
@@ -14890,54 +8092,10 @@
         <v>4885</v>
       </c>
       <c r="P155">
-        <f t="shared" si="22"/>
-        <v>138.8411927347212</v>
-      </c>
-      <c r="Q155">
-        <f t="shared" si="23"/>
-        <v>5.2799999999999878</v>
-      </c>
-      <c r="R155">
-        <f t="shared" si="24"/>
-        <v>147.00000000000003</v>
-      </c>
-      <c r="S155">
-        <f t="shared" si="25"/>
-        <v>0.97310659670105615</v>
-      </c>
-      <c r="T155">
-        <f t="shared" si="26"/>
-        <v>-0.15384597777777809</v>
-      </c>
-      <c r="U155">
-        <f t="shared" si="27"/>
-        <v>0.91965802222222193</v>
-      </c>
-      <c r="V155">
-        <f t="shared" si="28"/>
-        <v>2.7589740666666658</v>
-      </c>
-      <c r="W155">
-        <f t="shared" si="29"/>
-        <v>142.67829773779039</v>
-      </c>
-      <c r="X155">
-        <f t="shared" si="30"/>
-        <v>-34.320039277378136</v>
-      </c>
-      <c r="Y155">
-        <f t="shared" si="31"/>
-        <v>159.84202436987999</v>
-      </c>
-      <c r="Z155">
-        <f t="shared" si="32"/>
-        <v>30.838274642716875</v>
-      </c>
-      <c r="AA155">
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>0.84444453333333303</v>
       </c>
@@ -14984,54 +8142,10 @@
         <v>5038</v>
       </c>
       <c r="P156">
-        <f t="shared" si="22"/>
-        <v>127.6175035016749</v>
-      </c>
-      <c r="Q156">
-        <f t="shared" si="23"/>
-        <v>4.5599999999999907</v>
-      </c>
-      <c r="R156">
-        <f t="shared" si="24"/>
-        <v>135.29999999999998</v>
-      </c>
-      <c r="S156">
-        <f t="shared" si="25"/>
-        <v>0.93856426895569245</v>
-      </c>
-      <c r="T156">
-        <f t="shared" si="26"/>
-        <v>-0.16695157777778014</v>
-      </c>
-      <c r="U156">
-        <f t="shared" si="27"/>
-        <v>0.89629628888889001</v>
-      </c>
-      <c r="V156">
-        <f t="shared" si="28"/>
-        <v>2.6888888666666699</v>
-      </c>
-      <c r="W156">
-        <f t="shared" si="29"/>
-        <v>135.97098006263377</v>
-      </c>
-      <c r="X156">
-        <f t="shared" si="30"/>
-        <v>-27.31330880903414</v>
-      </c>
-      <c r="Y156">
-        <f t="shared" si="31"/>
-        <v>150.95454670210347</v>
-      </c>
-      <c r="Z156">
-        <f t="shared" si="32"/>
-        <v>29.887438263532509</v>
-      </c>
-      <c r="AA156">
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>0.835165357142857</v>
       </c>
@@ -15078,54 +8192,10 @@
         <v>11659</v>
       </c>
       <c r="P157">
-        <f t="shared" si="22"/>
-        <v>321.12221972326989</v>
-      </c>
-      <c r="Q157">
-        <f t="shared" si="23"/>
-        <v>4.8857142857143723</v>
-      </c>
-      <c r="R157">
-        <f t="shared" si="24"/>
-        <v>344.5714285714285</v>
-      </c>
-      <c r="S157">
-        <f t="shared" si="25"/>
-        <v>0.97388247573352427</v>
-      </c>
-      <c r="T157">
-        <f t="shared" si="26"/>
-        <v>-0.22771616666666397</v>
-      </c>
-      <c r="U157">
-        <f t="shared" si="27"/>
-        <v>0.95726504761904607</v>
-      </c>
-      <c r="V157">
-        <f t="shared" si="28"/>
-        <v>2.8717951428571382</v>
-      </c>
-      <c r="W157">
-        <f t="shared" si="29"/>
-        <v>329.73405695733663</v>
-      </c>
-      <c r="X157">
-        <f t="shared" si="30"/>
-        <v>-21.455280743708418</v>
-      </c>
-      <c r="Y157">
-        <f t="shared" si="31"/>
-        <v>359.95404765739909</v>
-      </c>
-      <c r="Z157">
-        <f t="shared" si="32"/>
-        <v>69.129980719874396</v>
-      </c>
-      <c r="AA157">
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>0.92490871428571397</v>
       </c>
@@ -15172,54 +8242,10 @@
         <v>11302</v>
       </c>
       <c r="P158">
-        <f t="shared" si="22"/>
-        <v>318.44991276302068</v>
-      </c>
-      <c r="Q158">
-        <f t="shared" si="23"/>
-        <v>2.8285714285713159</v>
-      </c>
-      <c r="R158">
-        <f t="shared" si="24"/>
-        <v>342.96428571428561</v>
-      </c>
-      <c r="S158">
-        <f t="shared" si="25"/>
-        <v>1.0130067816823791</v>
-      </c>
-      <c r="T158">
-        <f t="shared" si="26"/>
-        <v>-0.1501824523809554</v>
-      </c>
-      <c r="U158">
-        <f t="shared" si="27"/>
-        <v>0.95238083333333456</v>
-      </c>
-      <c r="V158">
-        <f t="shared" si="28"/>
-        <v>2.8571425000000037</v>
-      </c>
-      <c r="W158">
-        <f t="shared" si="29"/>
-        <v>314.36108673837913</v>
-      </c>
-      <c r="X158">
-        <f t="shared" si="30"/>
-        <v>-18.834233851743964</v>
-      </c>
-      <c r="Y158">
-        <f t="shared" si="31"/>
-        <v>360.11254501406756</v>
-      </c>
-      <c r="Z158">
-        <f t="shared" si="32"/>
-        <v>69.684008710501018</v>
-      </c>
-      <c r="AA158">
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>0.85348000000000002</v>
       </c>
@@ -15266,54 +8292,10 @@
         <v>11255</v>
       </c>
       <c r="P159">
-        <f t="shared" si="22"/>
-        <v>320.67683522989489</v>
-      </c>
-      <c r="Q159">
-        <f t="shared" si="23"/>
-        <v>3.0857142857140993</v>
-      </c>
-      <c r="R159">
-        <f t="shared" si="24"/>
-        <v>345.21428571428572</v>
-      </c>
-      <c r="S159">
-        <f t="shared" si="25"/>
-        <v>1.0087769898923813</v>
-      </c>
-      <c r="T159">
-        <f t="shared" si="26"/>
-        <v>-9.6458666666666693E-2</v>
-      </c>
-      <c r="U159">
-        <f t="shared" si="27"/>
-        <v>0.92185583333333332</v>
-      </c>
-      <c r="V159">
-        <f t="shared" si="28"/>
-        <v>2.7655675</v>
-      </c>
-      <c r="W159">
-        <f t="shared" si="29"/>
-        <v>317.88674646921265</v>
-      </c>
-      <c r="X159">
-        <f t="shared" si="30"/>
-        <v>-31.990015955512192</v>
-      </c>
-      <c r="Y159">
-        <f t="shared" si="31"/>
-        <v>374.47751940347041</v>
-      </c>
-      <c r="Z159">
-        <f t="shared" si="32"/>
-        <v>72.143291695879029</v>
-      </c>
-      <c r="AA159">
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>0.77264980000000005</v>
       </c>
@@ -15360,54 +8342,10 @@
         <v>4126</v>
       </c>
       <c r="P160">
-        <f t="shared" si="22"/>
-        <v>0.83138438763306644</v>
-      </c>
-      <c r="Q160">
-        <f t="shared" si="23"/>
-        <v>0.96000000000000296</v>
-      </c>
-      <c r="R160">
-        <f t="shared" si="24"/>
-        <v>0.30000000000000188</v>
-      </c>
-      <c r="S160">
-        <f t="shared" si="25"/>
-        <v>0.87342761158571902</v>
-      </c>
-      <c r="T160">
-        <f t="shared" si="26"/>
-        <v>0.50427366666666662</v>
-      </c>
-      <c r="U160">
-        <f t="shared" si="27"/>
-        <v>0.50427366666666673</v>
-      </c>
-      <c r="V160">
-        <f t="shared" si="28"/>
-        <v>1.5128210000000002</v>
-      </c>
-      <c r="W160">
-        <f t="shared" si="29"/>
-        <v>0.95186410024716006</v>
-      </c>
-      <c r="X160">
-        <f t="shared" si="30"/>
-        <v>1.9037282004943143</v>
-      </c>
-      <c r="Y160">
-        <f t="shared" si="31"/>
-        <v>0.59491506265447502</v>
-      </c>
-      <c r="Z160">
-        <f t="shared" si="32"/>
-        <v>1.4053215813371183</v>
-      </c>
-      <c r="AA160">
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>0.82906000000000002</v>
       </c>
@@ -15454,54 +8392,10 @@
         <v>4124</v>
       </c>
       <c r="P161">
-        <f t="shared" si="22"/>
-        <v>5.4039985196148992</v>
-      </c>
-      <c r="Q161">
-        <f t="shared" si="23"/>
-        <v>2.64</v>
-      </c>
-      <c r="R161">
-        <f t="shared" si="24"/>
-        <v>4.2000000000000028</v>
-      </c>
-      <c r="S161">
-        <f t="shared" si="25"/>
-        <v>0.93757750036561172</v>
-      </c>
-      <c r="T161">
-        <f t="shared" si="26"/>
-        <v>0.53675221333333345</v>
-      </c>
-      <c r="U161">
-        <f t="shared" si="27"/>
-        <v>0.54358982666666678</v>
-      </c>
-      <c r="V161">
-        <f t="shared" si="28"/>
-        <v>1.6307694800000003</v>
-      </c>
-      <c r="W161">
-        <f t="shared" si="29"/>
-        <v>5.7637886121494919</v>
-      </c>
-      <c r="X161">
-        <f t="shared" si="30"/>
-        <v>4.9184706358360355</v>
-      </c>
-      <c r="Y161">
-        <f t="shared" si="31"/>
-        <v>7.7264139135103305</v>
-      </c>
-      <c r="Z161">
-        <f t="shared" si="32"/>
-        <v>1.171226211567314</v>
-      </c>
-      <c r="AA161">
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>0.72991479999999997</v>
       </c>
@@ -15548,54 +8442,10 @@
         <v>4157</v>
       </c>
       <c r="P162">
-        <f t="shared" si="22"/>
-        <v>0.41569219381653322</v>
-      </c>
-      <c r="Q162">
-        <f t="shared" si="23"/>
-        <v>0.24000000000000149</v>
-      </c>
-      <c r="R162">
-        <f t="shared" si="24"/>
-        <v>0.30000000000000188</v>
-      </c>
-      <c r="S162">
-        <f t="shared" si="25"/>
-        <v>0.85171531548235846</v>
-      </c>
-      <c r="T162">
-        <f t="shared" si="26"/>
-        <v>0.48262126222222212</v>
-      </c>
-      <c r="U162">
-        <f t="shared" si="27"/>
-        <v>0.49629646888888884</v>
-      </c>
-      <c r="V162">
-        <f t="shared" si="28"/>
-        <v>1.4888894066666665</v>
-      </c>
-      <c r="W162">
-        <f t="shared" si="29"/>
-        <v>0.48806471629679582</v>
-      </c>
-      <c r="X162">
-        <f t="shared" si="30"/>
-        <v>0.49728434859029047</v>
-      </c>
-      <c r="Y162">
-        <f t="shared" si="31"/>
-        <v>0.60447740172651931</v>
-      </c>
-      <c r="Z162">
-        <f t="shared" si="32"/>
-        <v>1.8859694933867288</v>
-      </c>
-      <c r="AA162">
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>0.47521353333333299</v>
       </c>
@@ -15642,54 +8492,10 @@
         <v>2426</v>
       </c>
       <c r="P163">
-        <f t="shared" si="22"/>
-        <v>69.004904173544077</v>
-      </c>
-      <c r="Q163">
-        <f t="shared" si="23"/>
-        <v>122.4</v>
-      </c>
-      <c r="R163">
-        <f t="shared" si="24"/>
-        <v>-1.8000000000000018</v>
-      </c>
-      <c r="S163">
-        <f t="shared" si="25"/>
-        <v>0.5309646399023209</v>
-      </c>
-      <c r="T163">
-        <f t="shared" si="26"/>
-        <v>-0.2894588000000004</v>
-      </c>
-      <c r="U163">
-        <f t="shared" si="27"/>
-        <v>0.60455826666666668</v>
-      </c>
-      <c r="V163">
-        <f t="shared" si="28"/>
-        <v>1.8136748</v>
-      </c>
-      <c r="W163">
-        <f t="shared" si="29"/>
-        <v>129.96139288341044</v>
-      </c>
-      <c r="X163">
-        <f t="shared" si="30"/>
-        <v>-422.85810623135256</v>
-      </c>
-      <c r="Y163">
-        <f t="shared" si="31"/>
-        <v>-2.9773805094496573</v>
-      </c>
-      <c r="Z163">
-        <f t="shared" si="32"/>
-        <v>-0.48851096128148219</v>
-      </c>
-      <c r="AA163">
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>0.398290266666667</v>
       </c>
@@ -15736,54 +8542,10 @@
         <v>2580</v>
       </c>
       <c r="P164">
-        <f t="shared" si="22"/>
-        <v>68.589211979727537</v>
-      </c>
-      <c r="Q164">
-        <f t="shared" si="23"/>
-        <v>123.11999999999998</v>
-      </c>
-      <c r="R164">
-        <f t="shared" si="24"/>
-        <v>-2.699999999999998</v>
-      </c>
-      <c r="S164">
-        <f t="shared" si="25"/>
-        <v>0.47076224887295015</v>
-      </c>
-      <c r="T164">
-        <f t="shared" si="26"/>
-        <v>-0.28091186666666668</v>
-      </c>
-      <c r="U164">
-        <f t="shared" si="27"/>
-        <v>0.54814800000000041</v>
-      </c>
-      <c r="V164">
-        <f t="shared" si="28"/>
-        <v>1.6444440000000011</v>
-      </c>
-      <c r="W164">
-        <f t="shared" si="29"/>
-        <v>145.69819934358941</v>
-      </c>
-      <c r="X164">
-        <f t="shared" si="30"/>
-        <v>-438.28693127476748</v>
-      </c>
-      <c r="Y164">
-        <f t="shared" si="31"/>
-        <v>-4.9256770069397238</v>
-      </c>
-      <c r="Z164">
-        <f t="shared" si="32"/>
-        <v>1.0325678466399577</v>
-      </c>
-      <c r="AA164">
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>0.42393154</v>
       </c>
@@ -15830,54 +8592,10 @@
         <v>2265</v>
       </c>
       <c r="P165">
-        <f t="shared" si="22"/>
-        <v>66.926443204461421</v>
-      </c>
-      <c r="Q165">
-        <f t="shared" si="23"/>
-        <v>118.31999999999998</v>
-      </c>
-      <c r="R165">
-        <f t="shared" si="24"/>
-        <v>-1.5000000000000047</v>
-      </c>
-      <c r="S165">
-        <f t="shared" si="25"/>
-        <v>0.47470998141258064</v>
-      </c>
-      <c r="T165">
-        <f t="shared" si="26"/>
-        <v>-0.22735073111111107</v>
-      </c>
-      <c r="U165">
-        <f t="shared" si="27"/>
-        <v>0.52478626888888902</v>
-      </c>
-      <c r="V165">
-        <f t="shared" si="28"/>
-        <v>1.5743588066666672</v>
-      </c>
-      <c r="W165">
-        <f t="shared" si="29"/>
-        <v>140.98385503778613</v>
-      </c>
-      <c r="X165">
-        <f t="shared" si="30"/>
-        <v>-520.42937984736238</v>
-      </c>
-      <c r="Y165">
-        <f t="shared" si="31"/>
-        <v>-2.8583064933766282</v>
-      </c>
-      <c r="Z165">
-        <f t="shared" si="32"/>
-        <v>-0.79270366749644905</v>
-      </c>
-      <c r="AA165">
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>0.36698687499999999</v>
       </c>
@@ -15924,54 +8642,10 @@
         <v>7826</v>
       </c>
       <c r="P166">
-        <f t="shared" si="22"/>
-        <v>79.890843499114467</v>
-      </c>
-      <c r="Q166">
-        <f t="shared" si="23"/>
-        <v>129.82499999999999</v>
-      </c>
-      <c r="R166">
-        <f t="shared" si="24"/>
-        <v>5.34375</v>
-      </c>
-      <c r="S166">
-        <f t="shared" si="25"/>
-        <v>0.65877137957722742</v>
-      </c>
-      <c r="T166">
-        <f t="shared" si="26"/>
-        <v>-0.10576941666666673</v>
-      </c>
-      <c r="U166">
-        <f t="shared" si="27"/>
-        <v>0.62339745833333338</v>
-      </c>
-      <c r="V166">
-        <f t="shared" si="28"/>
-        <v>1.870192375</v>
-      </c>
-      <c r="W166">
-        <f t="shared" si="29"/>
-        <v>121.27248689884668</v>
-      </c>
-      <c r="X166">
-        <f t="shared" si="30"/>
-        <v>-1227.4342063277577</v>
-      </c>
-      <c r="Y166">
-        <f t="shared" si="31"/>
-        <v>8.5719791259441962</v>
-      </c>
-      <c r="Z166">
-        <f t="shared" si="32"/>
-        <v>2.4412595522425868</v>
-      </c>
-      <c r="AA166">
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>0.33173043749999997</v>
       </c>
@@ -16018,54 +8692,10 @@
         <v>7713</v>
       </c>
       <c r="P167">
-        <f t="shared" si="22"/>
-        <v>76.383440613787499</v>
-      </c>
-      <c r="Q167">
-        <f t="shared" si="23"/>
-        <v>128.69999999999999</v>
-      </c>
-      <c r="R167">
-        <f t="shared" si="24"/>
-        <v>2.25</v>
-      </c>
-      <c r="S167">
-        <f t="shared" si="25"/>
-        <v>0.64859366860999346</v>
-      </c>
-      <c r="T167">
-        <f t="shared" si="26"/>
-        <v>-0.11057718750000012</v>
-      </c>
-      <c r="U167">
-        <f t="shared" si="27"/>
-        <v>0.61698718750000003</v>
-      </c>
-      <c r="V167">
-        <f t="shared" si="28"/>
-        <v>1.8509615625000002</v>
-      </c>
-      <c r="W167">
-        <f t="shared" si="29"/>
-        <v>117.76778638232084</v>
-      </c>
-      <c r="X167">
-        <f t="shared" si="30"/>
-        <v>-1163.8928689518339</v>
-      </c>
-      <c r="Y167">
-        <f t="shared" si="31"/>
-        <v>3.6467531993928155</v>
-      </c>
-      <c r="Z167">
-        <f t="shared" si="32"/>
-        <v>2.0300259476620006</v>
-      </c>
-      <c r="AA167">
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>0.14583319375000001</v>
       </c>
@@ -16112,54 +8742,10 @@
         <v>4621</v>
       </c>
       <c r="P168">
-        <f t="shared" si="22"/>
-        <v>42.868257487329714</v>
-      </c>
-      <c r="Q168">
-        <f t="shared" si="23"/>
-        <v>70.650000000000006</v>
-      </c>
-      <c r="R168">
-        <f t="shared" si="24"/>
-        <v>2.25</v>
-      </c>
-      <c r="S168">
-        <f t="shared" si="25"/>
-        <v>0.37194676806522109</v>
-      </c>
-      <c r="T168">
-        <f t="shared" si="26"/>
-        <v>-8.3333437500000038E-2</v>
-      </c>
-      <c r="U168">
-        <f t="shared" si="27"/>
-        <v>0.36378206874999997</v>
-      </c>
-      <c r="V168">
-        <f t="shared" si="28"/>
-        <v>1.0913462062499999</v>
-      </c>
-      <c r="W168">
-        <f t="shared" si="29"/>
-        <v>115.25374372876051</v>
-      </c>
-      <c r="X168">
-        <f t="shared" si="30"/>
-        <v>-847.79894025132432</v>
-      </c>
-      <c r="Y168">
-        <f t="shared" si="31"/>
-        <v>6.1850217294416883</v>
-      </c>
-      <c r="Z168">
-        <f t="shared" si="32"/>
-        <v>3.3038324404767687</v>
-      </c>
-      <c r="AA168">
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>0.199999806666667</v>
       </c>
@@ -16206,54 +8792,10 @@
         <v>2440</v>
       </c>
       <c r="P169">
-        <f t="shared" si="22"/>
-        <v>74.824594886975504</v>
-      </c>
-      <c r="Q169">
-        <f t="shared" si="23"/>
-        <v>1.439999999999994</v>
-      </c>
-      <c r="R169">
-        <f t="shared" si="24"/>
-        <v>80.100000000000009</v>
-      </c>
-      <c r="S169">
-        <f t="shared" si="25"/>
-        <v>0.39378233230005538</v>
-      </c>
-      <c r="T169">
-        <f t="shared" si="26"/>
-        <v>1.1965935555555621E-2</v>
-      </c>
-      <c r="U169">
-        <f t="shared" si="27"/>
-        <v>0.33504253555555569</v>
-      </c>
-      <c r="V169">
-        <f t="shared" si="28"/>
-        <v>1.005127606666667</v>
-      </c>
-      <c r="W169">
-        <f t="shared" si="29"/>
-        <v>190.01511431437316</v>
-      </c>
-      <c r="X169">
-        <f t="shared" si="30"/>
-        <v>120.34161418589802</v>
-      </c>
-      <c r="Y169">
-        <f t="shared" si="31"/>
-        <v>239.07412193852051</v>
-      </c>
-      <c r="Z169">
-        <f t="shared" si="32"/>
-        <v>55.161155292381629</v>
-      </c>
-      <c r="AA169">
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>0.48034186666666701</v>
       </c>
@@ -16300,54 +8842,10 @@
         <v>2817</v>
       </c>
       <c r="P170">
-        <f t="shared" si="22"/>
-        <v>74.408902693158993</v>
-      </c>
-      <c r="Q170">
-        <f t="shared" si="23"/>
-        <v>-0.24000000000000152</v>
-      </c>
-      <c r="R170">
-        <f t="shared" si="24"/>
-        <v>80.7</v>
-      </c>
-      <c r="S170">
-        <f t="shared" si="25"/>
-        <v>0.40266467374144832</v>
-      </c>
-      <c r="T170">
-        <f t="shared" si="26"/>
-        <v>-3.4187311111106844E-3</v>
-      </c>
-      <c r="U170">
-        <f t="shared" si="27"/>
-        <v>0.35042720222222234</v>
-      </c>
-      <c r="V170">
-        <f t="shared" si="28"/>
-        <v>1.051281606666667</v>
-      </c>
-      <c r="W170">
-        <f t="shared" si="29"/>
-        <v>184.7912358483602</v>
-      </c>
-      <c r="X170">
-        <f t="shared" si="30"/>
-        <v>70.201484761411905</v>
-      </c>
-      <c r="Y170">
-        <f t="shared" si="31"/>
-        <v>230.29034129840281</v>
-      </c>
-      <c r="Z170">
-        <f t="shared" si="32"/>
-        <v>50.509777459500981</v>
-      </c>
-      <c r="AA170">
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>0.41367506666666698</v>
       </c>
@@ -16394,54 +8892,10 @@
         <v>2771</v>
       </c>
       <c r="P171">
-        <f t="shared" si="22"/>
-        <v>69.836288561177128</v>
-      </c>
-      <c r="Q171">
-        <f t="shared" si="23"/>
-        <v>-3.3600000000000136</v>
-      </c>
-      <c r="R171">
-        <f t="shared" si="24"/>
-        <v>77.7</v>
-      </c>
-      <c r="S171">
-        <f t="shared" si="25"/>
-        <v>0.44608918511913148</v>
-      </c>
-      <c r="T171">
-        <f t="shared" si="26"/>
-        <v>4.7863266666666626E-2</v>
-      </c>
-      <c r="U171">
-        <f t="shared" si="27"/>
-        <v>0.36239293333333361</v>
-      </c>
-      <c r="V171">
-        <f t="shared" si="28"/>
-        <v>1.0871788000000009</v>
-      </c>
-      <c r="W171">
-        <f t="shared" si="29"/>
-        <v>156.55230140252519</v>
-      </c>
-      <c r="X171">
-        <f t="shared" si="30"/>
-        <v>-70.199972421439753</v>
-      </c>
-      <c r="Y171">
-        <f t="shared" si="31"/>
-        <v>214.40815439005971</v>
-      </c>
-      <c r="Z171">
-        <f t="shared" si="32"/>
-        <v>46.395312344206737</v>
-      </c>
-      <c r="AA171">
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>0.2786322</v>
       </c>
@@ -16488,54 +8942,10 @@
         <v>5626</v>
       </c>
       <c r="P172">
-        <f t="shared" si="22"/>
-        <v>160.87287900699729</v>
-      </c>
-      <c r="Q172">
-        <f t="shared" si="23"/>
-        <v>2.6399999999999788</v>
-      </c>
-      <c r="R172">
-        <f t="shared" si="24"/>
-        <v>172.5</v>
-      </c>
-      <c r="S172">
-        <f t="shared" si="25"/>
-        <v>0.33456674835078304</v>
-      </c>
-      <c r="T172">
-        <f t="shared" si="26"/>
-        <v>-0.13846166444444433</v>
-      </c>
-      <c r="U172">
-        <f t="shared" si="27"/>
-        <v>0.35897413555555563</v>
-      </c>
-      <c r="V172">
-        <f t="shared" si="28"/>
-        <v>1.0769224066666669</v>
-      </c>
-      <c r="W172">
-        <f t="shared" si="29"/>
-        <v>480.8394133607294</v>
-      </c>
-      <c r="X172">
-        <f t="shared" si="30"/>
-        <v>-19.066649318369556</v>
-      </c>
-      <c r="Y172">
-        <f t="shared" si="31"/>
-        <v>480.53601336217582</v>
-      </c>
-      <c r="Z172">
-        <f t="shared" si="32"/>
-        <v>111.77035527802596</v>
-      </c>
-      <c r="AA172">
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>0.28888873333333298</v>
       </c>
@@ -16582,54 +8992,10 @@
         <v>5901</v>
       </c>
       <c r="P173">
-        <f t="shared" si="22"/>
-        <v>163.3670321698965</v>
-      </c>
-      <c r="Q173">
-        <f t="shared" si="23"/>
-        <v>3.599999999999985</v>
-      </c>
-      <c r="R173">
-        <f t="shared" si="24"/>
-        <v>174.6</v>
-      </c>
-      <c r="S173">
-        <f t="shared" si="25"/>
-        <v>0.3227237932190033</v>
-      </c>
-      <c r="T173">
-        <f t="shared" si="26"/>
-        <v>-0.1133903533333334</v>
-      </c>
-      <c r="U173">
-        <f t="shared" si="27"/>
-        <v>0.33618217999999961</v>
-      </c>
-      <c r="V173">
-        <f t="shared" si="28"/>
-        <v>1.0085465399999989</v>
-      </c>
-      <c r="W173">
-        <f t="shared" si="29"/>
-        <v>506.21316309031528</v>
-      </c>
-      <c r="X173">
-        <f t="shared" si="30"/>
-        <v>-31.74873253474281</v>
-      </c>
-      <c r="Y173">
-        <f t="shared" si="31"/>
-        <v>519.36125823206987</v>
-      </c>
-      <c r="Z173">
-        <f t="shared" si="32"/>
-        <v>119.3995469956202</v>
-      </c>
-      <c r="AA173">
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>0.31452967333333298</v>
       </c>
@@ -16676,54 +9042,10 @@
         <v>6005</v>
       </c>
       <c r="P174">
-        <f t="shared" si="22"/>
-        <v>163.3670321698965</v>
-      </c>
-      <c r="Q174">
-        <f t="shared" si="23"/>
-        <v>2.6399999999999788</v>
-      </c>
-      <c r="R174">
-        <f t="shared" si="24"/>
-        <v>175.20000000000002</v>
-      </c>
-      <c r="S174">
-        <f t="shared" si="25"/>
-        <v>0.378978417067728</v>
-      </c>
-      <c r="T174">
-        <f t="shared" si="26"/>
-        <v>-2.2791533333336909E-3</v>
-      </c>
-      <c r="U174">
-        <f t="shared" si="27"/>
-        <v>0.32934451333333331</v>
-      </c>
-      <c r="V174">
-        <f t="shared" si="28"/>
-        <v>0.98803353999999999</v>
-      </c>
-      <c r="W174">
-        <f t="shared" si="29"/>
-        <v>431.07212657099905</v>
-      </c>
-      <c r="X174">
-        <f t="shared" si="30"/>
-        <v>-1158.3248750265002</v>
-      </c>
-      <c r="Y174">
-        <f t="shared" si="31"/>
-        <v>531.96574683082122</v>
-      </c>
-      <c r="Z174">
-        <f t="shared" si="32"/>
-        <v>113.63581847636458</v>
-      </c>
-      <c r="AA174">
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>0.28717934000000001</v>
       </c>
@@ -16770,54 +9092,10 @@
         <v>12049</v>
       </c>
       <c r="P175">
-        <f t="shared" si="22"/>
-        <v>343.77744428627079</v>
-      </c>
-      <c r="Q175">
-        <f t="shared" si="23"/>
-        <v>1.1999999999999698</v>
-      </c>
-      <c r="R175">
-        <f t="shared" si="24"/>
-        <v>371.40000000000003</v>
-      </c>
-      <c r="S175">
-        <f t="shared" si="25"/>
-        <v>0.39180845255873376</v>
-      </c>
-      <c r="T175">
-        <f t="shared" si="26"/>
-        <v>-2.5641151111111055E-2</v>
-      </c>
-      <c r="U175">
-        <f t="shared" si="27"/>
-        <v>0.35213664888888901</v>
-      </c>
-      <c r="V175">
-        <f t="shared" si="28"/>
-        <v>1.056409946666667</v>
-      </c>
-      <c r="W175">
-        <f t="shared" si="29"/>
-        <v>877.41201610431585</v>
-      </c>
-      <c r="X175">
-        <f t="shared" si="30"/>
-        <v>-46.79977099311953</v>
-      </c>
-      <c r="Y175">
-        <f t="shared" si="31"/>
-        <v>1054.7041927385105</v>
-      </c>
-      <c r="Z175">
-        <f t="shared" si="32"/>
-        <v>235.59982636033726</v>
-      </c>
-      <c r="AA175">
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>0.37094000666666699</v>
       </c>
@@ -16864,54 +9142,10 @@
         <v>12564</v>
       </c>
       <c r="P176">
-        <f t="shared" si="22"/>
-        <v>342.11467551100469</v>
-      </c>
-      <c r="Q176">
-        <f t="shared" si="23"/>
-        <v>-1.2000000000000304</v>
-      </c>
-      <c r="R176">
-        <f t="shared" si="24"/>
-        <v>371.09999999999997</v>
-      </c>
-      <c r="S176">
-        <f t="shared" si="25"/>
-        <v>0.40858620904236481</v>
-      </c>
-      <c r="T176">
-        <f t="shared" si="26"/>
-        <v>-4.9002820000000002E-2</v>
-      </c>
-      <c r="U176">
-        <f t="shared" si="27"/>
-        <v>0.37834744666666698</v>
-      </c>
-      <c r="V176">
-        <f t="shared" si="28"/>
-        <v>1.1350423400000009</v>
-      </c>
-      <c r="W176">
-        <f t="shared" si="29"/>
-        <v>837.31332076245405</v>
-      </c>
-      <c r="X176">
-        <f t="shared" si="30"/>
-        <v>24.48838658673175</v>
-      </c>
-      <c r="Y176">
-        <f t="shared" si="31"/>
-        <v>980.84446788125899</v>
-      </c>
-      <c r="Z176">
-        <f t="shared" si="32"/>
-        <v>220.12923324076147</v>
-      </c>
-      <c r="AA176">
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>0.38461519999999999</v>
       </c>
@@ -16958,50 +9192,6 @@
         <v>11327</v>
       </c>
       <c r="P177">
-        <f t="shared" si="22"/>
-        <v>316.34175949437974</v>
-      </c>
-      <c r="Q177">
-        <f t="shared" si="23"/>
-        <v>-0.24000000000002425</v>
-      </c>
-      <c r="R177">
-        <f t="shared" si="24"/>
-        <v>342.59999999999997</v>
-      </c>
-      <c r="S177">
-        <f t="shared" si="25"/>
-        <v>0.41450770970226447</v>
-      </c>
-      <c r="T177">
-        <f t="shared" si="26"/>
-        <v>-7.6353333333333717E-2</v>
-      </c>
-      <c r="U177">
-        <f t="shared" si="27"/>
-        <v>0.39715087333333332</v>
-      </c>
-      <c r="V177">
-        <f t="shared" si="28"/>
-        <v>1.19145262</v>
-      </c>
-      <c r="W177">
-        <f t="shared" si="29"/>
-        <v>763.1746095183704</v>
-      </c>
-      <c r="X177">
-        <f t="shared" si="30"/>
-        <v>3.1432812363575882</v>
-      </c>
-      <c r="Y177">
-        <f t="shared" si="31"/>
-        <v>862.64445832516606</v>
-      </c>
-      <c r="Z177">
-        <f t="shared" si="32"/>
-        <v>191.79109279225892</v>
-      </c>
-      <c r="AA177">
         <v>5</v>
       </c>
     </row>
